--- a/PTBR/Lang/PTBR/Dialog/Drama/_tutorial.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/_tutorial.xlsx
@@ -1750,7 +1750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K373"/>
+  <dimension ref="A1:K374"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.83" customWidth="1" style="15" min="1" max="3"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="K12" s="15" t="n"/>
     </row>
-    <row r="13" ht="35.05" customHeight="1" s="17">
+    <row r="13" ht="12.8" customHeight="1" s="17">
       <c r="I13" s="19" t="inlineStr">
         <is>
           <t>…</t>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="22.35" customHeight="1" s="17">
+    <row r="18" ht="12.8" customHeight="1" s="17">
       <c r="H18" s="15" t="n">
         <v>327</v>
       </c>
@@ -4600,41 +4600,31 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="23.85" customFormat="1" customHeight="1" s="15">
+    <row r="154" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="A154" s="19" t="n"/>
       <c r="B154" s="19" t="n"/>
       <c r="C154" s="19" t="inlineStr">
         <is>
-          <t>nerun_nadenade2</t>
-        </is>
-      </c>
-      <c r="D154" s="19" t="n"/>
-      <c r="E154" s="19" t="n"/>
+          <t>nerun_nadenade</t>
+        </is>
+      </c>
+      <c r="D154" s="19" t="inlineStr">
+        <is>
+          <t>getAchievement</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>NERUN2</t>
+        </is>
+      </c>
       <c r="F154" s="19" t="n"/>
       <c r="G154" s="19" t="n"/>
-      <c r="H154" s="15" t="n">
-        <v>231</v>
-      </c>
-      <c r="I154" s="26" t="inlineStr">
-        <is>
-          <t>この期間にキミが死んだ回数は実に#1回…
-一体、何をしていたの？</t>
-        </is>
-      </c>
-      <c r="J154" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The number of times you died during this period is actually #1...
-What on earth were you doing? </t>
-        </is>
-      </c>
-      <c r="K154" s="19" t="inlineStr">
-        <is>
-          <t>O número de vezes que você morreu durante este período é, na verdade, #1...
-O que diabos você estava fazendo?</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="I154" s="26" t="n"/>
+      <c r="J154" s="25" t="n"/>
+      <c r="K154" s="19" t="n"/>
+    </row>
+    <row r="155" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A155" s="19" t="n"/>
       <c r="B155" s="19" t="n"/>
       <c r="C155" s="19" t="inlineStr">
@@ -4647,55 +4637,59 @@
       <c r="F155" s="19" t="n"/>
       <c r="G155" s="19" t="n"/>
       <c r="H155" s="15" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I155" s="26" t="inlineStr">
         <is>
-          <t>さすがの私も、キミみたいな冒険者は初めてよ…</t>
+          <t>この期間にキミが死んだ回数は実に#1回…
+一体、何をしていたの？</t>
         </is>
       </c>
       <c r="J155" s="25" t="inlineStr">
         <is>
-          <t>Even for me, I’ve never seen an adventurer quite like you...</t>
+          <t xml:space="preserve">The number of times you died during this period is actually #1...
+What on earth were you doing? </t>
         </is>
       </c>
       <c r="K155" s="19" t="inlineStr">
         <is>
-          <t>Até para mim, nunca vi um aventureiro como você...</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>O número de vezes que você morreu durante este período é, na verdade, #1...
+O que diabos você estava fazendo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="A156" s="19" t="n"/>
       <c r="B156" s="19" t="n"/>
-      <c r="C156" s="19" t="n"/>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>nerun_nadenade2</t>
+        </is>
+      </c>
       <c r="D156" s="19" t="n"/>
       <c r="E156" s="19" t="n"/>
       <c r="F156" s="19" t="n"/>
       <c r="G156" s="19" t="n"/>
       <c r="H156" s="15" t="n">
-        <v>128</v>
-      </c>
-      <c r="I156" s="28" t="inlineStr">
-        <is>
-          <t>これからは死んだら
-デスペナルティが発生するから気をつけていってね。</t>
-        </is>
-      </c>
-      <c r="J156" s="19" t="inlineStr">
-        <is>
-          <t>From now on, when you die, you'll incur death penalties.
-So be careful.</t>
+        <v>232</v>
+      </c>
+      <c r="I156" s="26" t="inlineStr">
+        <is>
+          <t>さすがの私も、キミみたいな冒険者は初めてよ…</t>
+        </is>
+      </c>
+      <c r="J156" s="25" t="inlineStr">
+        <is>
+          <t>Even for me, I’ve never seen an adventurer quite like you...</t>
         </is>
       </c>
       <c r="K156" s="19" t="inlineStr">
         <is>
-          <t>De agora em diante, quando você morrer, incorrerá em uma penalidade de morte.
-Portanto, tenha cuidado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Até para mim, nunca vi um aventureiro como você...</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A157" s="19" t="n"/>
       <c r="B157" s="19" t="n"/>
       <c r="C157" s="19" t="n"/>
@@ -4703,17 +4697,31 @@
       <c r="E157" s="19" t="n"/>
       <c r="F157" s="19" t="n"/>
       <c r="G157" s="19" t="n"/>
-      <c r="I157" s="19" t="n"/>
-      <c r="J157" s="19" t="n"/>
-      <c r="K157" s="19" t="n"/>
+      <c r="H157" s="15" t="n">
+        <v>128</v>
+      </c>
+      <c r="I157" s="28" t="inlineStr">
+        <is>
+          <t>これからは死んだら
+デスペナルティが発生するから気をつけていってね。</t>
+        </is>
+      </c>
+      <c r="J157" s="19" t="inlineStr">
+        <is>
+          <t>From now on, when you die, you'll incur death penalties.
+So be careful.</t>
+        </is>
+      </c>
+      <c r="K157" s="19" t="inlineStr">
+        <is>
+          <t>De agora em diante, quando você morrer, incorrerá em uma penalidade de morte.
+Portanto, tenha cuidado.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A158" s="19" t="n"/>
-      <c r="B158" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B158" s="19" t="n"/>
       <c r="C158" s="19" t="n"/>
       <c r="D158" s="19" t="n"/>
       <c r="E158" s="19" t="n"/>
@@ -4725,7 +4733,11 @@
     </row>
     <row r="159" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A159" s="19" t="n"/>
-      <c r="B159" s="19" t="n"/>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C159" s="19" t="n"/>
       <c r="D159" s="19" t="n"/>
       <c r="E159" s="19" t="n"/>
@@ -4736,11 +4748,7 @@
       <c r="K159" s="19" t="n"/>
     </row>
     <row r="160" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A160" s="19" t="inlineStr">
-        <is>
-          <t>garbage</t>
-        </is>
-      </c>
+      <c r="A160" s="19" t="n"/>
       <c r="B160" s="19" t="n"/>
       <c r="C160" s="19" t="n"/>
       <c r="D160" s="19" t="n"/>
@@ -4751,34 +4759,23 @@
       <c r="J160" s="19" t="n"/>
       <c r="K160" s="19" t="n"/>
     </row>
-    <row r="161" ht="13.8" customFormat="1" customHeight="1" s="15">
-      <c r="A161" s="19" t="n"/>
+    <row r="161" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>garbage</t>
+        </is>
+      </c>
       <c r="B161" s="19" t="n"/>
       <c r="C161" s="19" t="n"/>
       <c r="D161" s="19" t="n"/>
       <c r="E161" s="19" t="n"/>
       <c r="F161" s="19" t="n"/>
       <c r="G161" s="19" t="n"/>
-      <c r="H161" s="15" t="n">
-        <v>129</v>
-      </c>
-      <c r="I161" s="26" t="inlineStr">
-        <is>
-          <t>やだ、ゴミまみれ！</t>
-        </is>
-      </c>
-      <c r="J161" s="25" t="inlineStr">
-        <is>
-          <t>Oh no, there's trash everywhere!</t>
-        </is>
-      </c>
-      <c r="K161" s="19" t="inlineStr">
-        <is>
-          <t>Ah não, tem lixo por toda parte!</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="I161" s="19" t="n"/>
+      <c r="J161" s="19" t="n"/>
+      <c r="K161" s="19" t="n"/>
+    </row>
+    <row r="162" ht="13.8" customFormat="1" customHeight="1" s="15">
       <c r="A162" s="19" t="n"/>
       <c r="B162" s="19" t="n"/>
       <c r="C162" s="19" t="n"/>
@@ -4787,24 +4784,21 @@
       <c r="F162" s="19" t="n"/>
       <c r="G162" s="19" t="n"/>
       <c r="H162" s="15" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I162" s="26" t="inlineStr">
         <is>
-          <t>キミって、噂の…片づけられない冒険者なの？
-ゴミはちゃんと掃除しないと大問題になるわよ？</t>
-        </is>
-      </c>
-      <c r="J162" s="19" t="inlineStr">
-        <is>
-          <t>Are you the rumored... messy adventurer?
-If you don't clean up, it could become a big problem!</t>
+          <t>やだ、ゴミまみれ！</t>
+        </is>
+      </c>
+      <c r="J162" s="25" t="inlineStr">
+        <is>
+          <t>Oh no, there's trash everywhere!</t>
         </is>
       </c>
       <c r="K162" s="19" t="inlineStr">
         <is>
-          <t>Você é um daqueles aventureiros... Bagunceiros?
-Sabe, se você não limpar seu lixo, vai se meter em grandes problemas.</t>
+          <t>Ah não, tem lixo por toda parte!</t>
         </is>
       </c>
     </row>
@@ -4817,23 +4811,24 @@
       <c r="F163" s="19" t="n"/>
       <c r="G163" s="19" t="n"/>
       <c r="H163" s="15" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I163" s="26" t="inlineStr">
         <is>
-          <t>といっても、住民が増えてくるとゴミも多くなるから
-何らかの対策が必要ね！</t>
+          <t>キミって、噂の…片づけられない冒険者なの？
+ゴミはちゃんと掃除しないと大問題になるわよ？</t>
         </is>
       </c>
       <c r="J163" s="19" t="inlineStr">
         <is>
-          <t>As the population grows, more trash will accumulate,
-so you'll need to come up with some measures.</t>
+          <t>Are you the rumored... messy adventurer?
+If you don't clean up, it could become a big problem!</t>
         </is>
       </c>
       <c r="K163" s="19" t="inlineStr">
         <is>
-          <t>À medida que a população crescer, mais lixo se acumulará, portanto, você precisará tomar algumas medidas.</t>
+          <t>Você é um daqueles aventureiros... Bagunceiros?
+Sabe, se você não limpar seu lixo, vai se meter em grandes problemas.</t>
         </is>
       </c>
     </row>
@@ -4846,28 +4841,27 @@
       <c r="F164" s="19" t="n"/>
       <c r="G164" s="19" t="n"/>
       <c r="H164" s="15" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I164" s="26" t="inlineStr">
         <is>
-          <t>一番手っ取り早い解決方法は
-「ポイ捨て厳罰法」を施行することかな。</t>
+          <t>といっても、住民が増えてくるとゴミも多くなるから
+何らかの対策が必要ね！</t>
         </is>
       </c>
       <c r="J164" s="19" t="inlineStr">
         <is>
-          <t>The quickest solution is to
-implement the "Strict Anti-Littering Law".</t>
+          <t>As the population grows, more trash will accumulate,
+so you'll need to come up with some measures.</t>
         </is>
       </c>
       <c r="K164" s="19" t="inlineStr">
         <is>
-          <t>A solução mais rápida é implementar a
-"Lei Rigorosa Contra o Descarte de Lixo".</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>À medida que a população crescer, mais lixo se acumulará, portanto, você precisará tomar algumas medidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A165" s="19" t="n"/>
       <c r="B165" s="19" t="n"/>
       <c r="C165" s="19" t="n"/>
@@ -4876,27 +4870,24 @@
       <c r="F165" s="19" t="n"/>
       <c r="G165" s="19" t="n"/>
       <c r="H165" s="15" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I165" s="26" t="inlineStr">
         <is>
-          <t>このポリシーを施行すると、ゴミはほとんど発生しなくなるわ。
-ただし、民度が下がってしまうので、いつかはもっと
-良いゴミ対策方法に移行したい所ね。</t>
+          <t>一番手っ取り早い解決方法は
+「ポイ捨て厳罰法」を施行することかな。</t>
         </is>
       </c>
       <c r="J165" s="19" t="inlineStr">
         <is>
-          <t>With this policy, trash will mostly disappear.
-However, since it lowers the public morality,
-you'll eventually want to switch to a better waste management solution.</t>
+          <t>The quickest solution is to
+implement the "Strict Anti-Littering Law".</t>
         </is>
       </c>
       <c r="K165" s="19" t="inlineStr">
         <is>
-          <t>Com essa política, o lixo praticamente desaparecerá._x000D_
-No entanto, como isso reduz a moral pública,_x000D_
-eventualmente você vai querer mudar para uma solução melhor de gestão de resíduos.</t>
+          <t>A solução mais rápida é implementar a
+"Lei Rigorosa Contra o Descarte de Lixo".</t>
         </is>
       </c>
     </row>
@@ -4909,29 +4900,31 @@
       <c r="F166" s="19" t="n"/>
       <c r="G166" s="19" t="n"/>
       <c r="H166" s="15" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I166" s="26" t="inlineStr">
         <is>
-          <t>ゴミ捨て場の立札を立てたり、ゴミのコンテナを置けば
-住人は民度の高さに応じて
-自動的にゴミを出してくれるわ。</t>
+          <t>このポリシーを施行すると、ゴミはほとんど発生しなくなるわ。
+ただし、民度が下がってしまうので、いつかはもっと
+良いゴミ対策方法に移行したい所ね。</t>
         </is>
       </c>
       <c r="J166" s="19" t="inlineStr">
         <is>
-          <t>Putting up garbage dump signs and placing garbage containers
-will encourage residents to dispose of trash according to the public morality.</t>
+          <t>With this policy, trash will mostly disappear.
+However, since it lowers the public morality,
+you'll eventually want to switch to a better waste management solution.</t>
         </is>
       </c>
       <c r="K166" s="19" t="inlineStr">
         <is>
-          <t>Colocar placas de descarte e posicionar lixeiras
-incentivará os moradores a jogarem o lixo no lugar certo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>Com essa política, o lixo praticamente desaparecerá._x000D_
+No entanto, como isso reduz a moral pública,_x000D_
+eventualmente você vai querer mudar para uma solução melhor de gestão de resíduos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A167" s="19" t="n"/>
       <c r="B167" s="19" t="n"/>
       <c r="C167" s="19" t="n"/>
@@ -4940,23 +4933,25 @@
       <c r="F167" s="19" t="n"/>
       <c r="G167" s="19" t="n"/>
       <c r="H167" s="15" t="n">
-        <v>135</v>
-      </c>
-      <c r="I167" s="28" t="inlineStr">
-        <is>
-          <t>それに、掃除をしてくれる住民がいれば
-ゴミを分別して出す確率も大幅に上昇するの。</t>
+        <v>134</v>
+      </c>
+      <c r="I167" s="26" t="inlineStr">
+        <is>
+          <t>ゴミ捨て場の立札を立てたり、ゴミのコンテナを置けば
+住人は民度の高さに応じて
+自動的にゴミを出してくれるわ。</t>
         </is>
       </c>
       <c r="J167" s="19" t="inlineStr">
         <is>
-          <t>And if you have residents who clean up,
-the chances of them sorting the trash increase significantly.</t>
+          <t>Putting up garbage dump signs and placing garbage containers
+will encourage residents to dispose of trash according to the public morality.</t>
         </is>
       </c>
       <c r="K167" s="19" t="inlineStr">
         <is>
-          <t>Além disso, a probabilidade de separar e descartar o lixo aumenta consideravelmente quando há moradores dispostos a fazer a limpeza.</t>
+          <t>Colocar placas de descarte e posicionar lixeiras
+incentivará os moradores a jogarem o lixo no lugar certo.</t>
         </is>
       </c>
     </row>
@@ -4969,46 +4964,63 @@
       <c r="F168" s="19" t="n"/>
       <c r="G168" s="19" t="n"/>
       <c r="H168" s="15" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I168" s="28" t="inlineStr">
         <is>
-          <t>ゴミは解体することで貴重な資源になるから
-有効に活用していきたいところね！</t>
+          <t>それに、掃除をしてくれる住民がいれば
+ゴミを分別して出す確率も大幅に上昇するの。</t>
         </is>
       </c>
       <c r="J168" s="19" t="inlineStr">
         <is>
-          <t>Garbages can be dismantled into valuable resources,
-so you'll want to use them effectively!</t>
+          <t>And if you have residents who clean up,
+the chances of them sorting the trash increase significantly.</t>
         </is>
       </c>
       <c r="K168" s="19" t="inlineStr">
         <is>
-          <t>Os lixos podem ser desmontados em recursos valiosos,_x000D_
-então use-os de forma eficiente!</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Além disso, a probabilidade de separar e descartar o lixo aumenta consideravelmente quando há moradores dispostos a fazer a limpeza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A169" s="19" t="n"/>
-      <c r="B169" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B169" s="19" t="n"/>
       <c r="C169" s="19" t="n"/>
       <c r="D169" s="19" t="n"/>
       <c r="E169" s="19" t="n"/>
       <c r="F169" s="19" t="n"/>
       <c r="G169" s="19" t="n"/>
-      <c r="I169" s="19" t="n"/>
-      <c r="J169" s="19" t="n"/>
-      <c r="K169" s="19" t="n"/>
+      <c r="H169" s="15" t="n">
+        <v>136</v>
+      </c>
+      <c r="I169" s="28" t="inlineStr">
+        <is>
+          <t>ゴミは解体することで貴重な資源になるから
+有効に活用していきたいところね！</t>
+        </is>
+      </c>
+      <c r="J169" s="19" t="inlineStr">
+        <is>
+          <t>Garbages can be dismantled into valuable resources,
+so you'll want to use them effectively!</t>
+        </is>
+      </c>
+      <c r="K169" s="19" t="inlineStr">
+        <is>
+          <t>Os lixos podem ser desmontados em recursos valiosos,_x000D_
+então use-os de forma eficiente!</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A170" s="19" t="n"/>
-      <c r="B170" s="19" t="n"/>
+      <c r="B170" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C170" s="19" t="n"/>
       <c r="D170" s="19" t="n"/>
       <c r="E170" s="19" t="n"/>
@@ -5019,11 +5031,7 @@
       <c r="K170" s="19" t="n"/>
     </row>
     <row r="171" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A171" s="19" t="inlineStr">
-        <is>
-          <t>eq</t>
-        </is>
-      </c>
+      <c r="A171" s="19" t="n"/>
       <c r="B171" s="19" t="n"/>
       <c r="C171" s="19" t="n"/>
       <c r="D171" s="19" t="n"/>
@@ -5034,37 +5042,23 @@
       <c r="J171" s="19" t="n"/>
       <c r="K171" s="19" t="n"/>
     </row>
-    <row r="172" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="A172" s="19" t="n"/>
+    <row r="172" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A172" s="19" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
       <c r="B172" s="19" t="n"/>
       <c r="C172" s="19" t="n"/>
       <c r="D172" s="19" t="n"/>
       <c r="E172" s="19" t="n"/>
       <c r="F172" s="19" t="n"/>
       <c r="G172" s="19" t="n"/>
-      <c r="H172" s="15" t="n">
-        <v>137</v>
-      </c>
-      <c r="I172" s="26" t="inlineStr">
-        <is>
-          <t>ん、洞窟の探索？
-キミも冒険者らしくなってきたわね！</t>
-        </is>
-      </c>
-      <c r="J172" s="25" t="inlineStr">
-        <is>
-          <t>Huh, exploring a cave already?
-You're becoming like a real adventurer!</t>
-        </is>
-      </c>
-      <c r="K172" s="19" t="inlineStr">
-        <is>
-          <t>Já está explorando uma caverna?
-Você está se tornando um verdadeiro aventureiro!</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="13.8" customFormat="1" customHeight="1" s="15">
+      <c r="I172" s="19" t="n"/>
+      <c r="J172" s="19" t="n"/>
+      <c r="K172" s="19" t="n"/>
+    </row>
+    <row r="173" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A173" s="19" t="n"/>
       <c r="B173" s="19" t="n"/>
       <c r="C173" s="19" t="n"/>
@@ -5073,21 +5067,24 @@
       <c r="F173" s="19" t="n"/>
       <c r="G173" s="19" t="n"/>
       <c r="H173" s="15" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I173" s="26" t="inlineStr">
         <is>
-          <t>でも、奥に進む前にちょっと自分の姿を確認してみて。</t>
+          <t>ん、洞窟の探索？
+キミも冒険者らしくなってきたわね！</t>
         </is>
       </c>
       <c r="J173" s="25" t="inlineStr">
         <is>
-          <t>But before you go deeper, take a look at yourself.</t>
+          <t>Huh, exploring a cave already?
+You're becoming like a real adventurer!</t>
         </is>
       </c>
       <c r="K173" s="19" t="inlineStr">
         <is>
-          <t>Mas antes de ir mais fundo, dê uma olhada em si mesmo.</t>
+          <t>Já está explorando uma caverna?
+Você está se tornando um verdadeiro aventureiro!</t>
         </is>
       </c>
     </row>
@@ -5100,25 +5097,25 @@
       <c r="F174" s="19" t="n"/>
       <c r="G174" s="19" t="n"/>
       <c r="H174" s="15" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I174" s="26" t="inlineStr">
         <is>
-          <t>…そんな装備で大丈夫か？</t>
+          <t>でも、奥に進む前にちょっと自分の姿を確認してみて。</t>
         </is>
       </c>
       <c r="J174" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">...You sure that's enough armor? </t>
+          <t>But before you go deeper, take a look at yourself.</t>
         </is>
       </c>
       <c r="K174" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">... Tem certeza de que essa armadura é suficiente? </t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>Mas antes de ir mais fundo, dê uma olhada em si mesmo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="13.8" customFormat="1" customHeight="1" s="15">
       <c r="A175" s="19" t="n"/>
       <c r="B175" s="19" t="n"/>
       <c r="C175" s="19" t="n"/>
@@ -5127,31 +5124,25 @@
       <c r="F175" s="19" t="n"/>
       <c r="G175" s="19" t="n"/>
       <c r="H175" s="15" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I175" s="26" t="inlineStr">
         <is>
-          <t>洞窟ともなると、敵もたくさん出てくるわ。
-もし装備を身につけていない部位が３つも４つもあるなら
-たぶん出直した方がキミの命のためよ。</t>
+          <t>…そんな装備で大丈夫か？</t>
         </is>
       </c>
       <c r="J175" s="25" t="inlineStr">
         <is>
-          <t>Caves have lots of enemies.
-If you have an unequipped slot or two,
-you might want to turn back for your own safety.</t>
+          <t xml:space="preserve">...You sure that's enough armor? </t>
         </is>
       </c>
       <c r="K175" s="19" t="inlineStr">
         <is>
-          <t>As cavernas estão cheias de inimigos._x000D_
-Se você tiver um ou dois espaços de equipamento vazios,_x000D_
-talvez seja melhor voltar para sua própria segurança.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t xml:space="preserve">... Tem certeza de que essa armadura é suficiente? </t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A176" s="19" t="n"/>
       <c r="B176" s="19" t="n"/>
       <c r="C176" s="19" t="n"/>
@@ -5160,28 +5151,31 @@
       <c r="F176" s="19" t="n"/>
       <c r="G176" s="19" t="n"/>
       <c r="H176" s="15" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I176" s="26" t="inlineStr">
         <is>
-          <t>拠点では、簡単な武器や防具を製作することもできるし
-街に赴いて店で物色してもいい。</t>
+          <t>洞窟ともなると、敵もたくさん出てくるわ。
+もし装備を身につけていない部位が３つも４つもあるなら
+たぶん出直した方がキミの命のためよ。</t>
         </is>
       </c>
       <c r="J176" s="25" t="inlineStr">
         <is>
-          <t>At your base, you can craft simple weapons and armor,
-or you can browse the shops in town.</t>
+          <t>Caves have lots of enemies.
+If you have an unequipped slot or two,
+you might want to turn back for your own safety.</t>
         </is>
       </c>
       <c r="K176" s="19" t="inlineStr">
         <is>
-          <t>Na sua base, você pode fabricar armas e armaduras simples,_x000D_
-ou dar uma olhada nas lojas da cidade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>As cavernas estão cheias de inimigos._x000D_
+Se você tiver um ou dois espaços de equipamento vazios,_x000D_
+talvez seja melhor voltar para sua própria segurança.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A177" s="19" t="n"/>
       <c r="B177" s="19" t="n"/>
       <c r="C177" s="19" t="n"/>
@@ -5190,53 +5184,67 @@
       <c r="F177" s="19" t="n"/>
       <c r="G177" s="19" t="n"/>
       <c r="H177" s="15" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I177" s="26" t="inlineStr">
         <is>
-          <t>特に防御力(PV）は、敵からのダメージを軽減する
-重要なステータスだから、敵からの攻撃が辛いと感じたら
-防御力をあげてみてね。</t>
+          <t>拠点では、簡単な武器や防具を製作することもできるし
+街に赴いて店で物色してもいい。</t>
         </is>
       </c>
       <c r="J177" s="25" t="inlineStr">
         <is>
-          <t>Protection Value (PV) is especially a crucial stat that
-reduces the damage you take from enemies.
-If you find enemy attacks too harsh, try increasing your defense.</t>
+          <t>At your base, you can craft simple weapons and armor,
+or you can browse the shops in town.</t>
         </is>
       </c>
       <c r="K177" s="19" t="inlineStr">
         <is>
-          <t>O Valor de Proteção (VP ou PV) é um atributo crucial que
-reduz o dano recebido dos inimigos.
-Se os ataques dos inimigos estiverem muito fortes, tente aumentar sua defesa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Na sua base, você pode fabricar armas e armaduras simples,_x000D_
+ou dar uma olhada nas lojas da cidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A178" s="19" t="n"/>
-      <c r="B178" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B178" s="19" t="n"/>
       <c r="C178" s="19" t="n"/>
       <c r="D178" s="19" t="n"/>
       <c r="E178" s="19" t="n"/>
       <c r="F178" s="19" t="n"/>
       <c r="G178" s="19" t="n"/>
-      <c r="I178" s="19" t="n"/>
-      <c r="J178" s="19" t="n"/>
-      <c r="K178" s="19" t="n"/>
+      <c r="H178" s="15" t="n">
+        <v>142</v>
+      </c>
+      <c r="I178" s="26" t="inlineStr">
+        <is>
+          <t>特に防御力(PV）は、敵からのダメージを軽減する
+重要なステータスだから、敵からの攻撃が辛いと感じたら
+防御力をあげてみてね。</t>
+        </is>
+      </c>
+      <c r="J178" s="25" t="inlineStr">
+        <is>
+          <t>Protection Value (PV) is especially a crucial stat that
+reduces the damage you take from enemies.
+If you find enemy attacks too harsh, try increasing your defense.</t>
+        </is>
+      </c>
+      <c r="K178" s="19" t="inlineStr">
+        <is>
+          <t>O Valor de Proteção (VP ou PV) é um atributo crucial que
+reduz o dano recebido dos inimigos.
+Se os ataques dos inimigos estiverem muito fortes, tente aumentar sua defesa.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A179" s="19" t="inlineStr">
-        <is>
-          <t>stone</t>
-        </is>
-      </c>
-      <c r="B179" s="19" t="n"/>
+      <c r="A179" s="19" t="n"/>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C179" s="19" t="n"/>
       <c r="D179" s="19" t="n"/>
       <c r="E179" s="19" t="n"/>
@@ -5246,34 +5254,23 @@
       <c r="J179" s="19" t="n"/>
       <c r="K179" s="19" t="n"/>
     </row>
-    <row r="180" ht="13.8" customFormat="1" customHeight="1" s="15">
-      <c r="A180" s="19" t="n"/>
+    <row r="180" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A180" s="19" t="inlineStr">
+        <is>
+          <t>stone</t>
+        </is>
+      </c>
       <c r="B180" s="19" t="n"/>
       <c r="C180" s="19" t="n"/>
       <c r="D180" s="19" t="n"/>
       <c r="E180" s="19" t="n"/>
       <c r="F180" s="19" t="n"/>
       <c r="G180" s="19" t="n"/>
-      <c r="H180" s="15" t="n">
-        <v>143</v>
-      </c>
-      <c r="I180" s="26" t="inlineStr">
-        <is>
-          <t>よしよし、盟約の石も育ってきたわ。</t>
-        </is>
-      </c>
-      <c r="J180" s="25" t="inlineStr">
-        <is>
-          <t>Well done, your Hearth Stone is growing.</t>
-        </is>
-      </c>
-      <c r="K180" s="19" t="inlineStr">
-        <is>
-          <t>Muito bem, sua Pedra do Lar está crescendo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="35.05" customFormat="1" customHeight="1" s="15">
+      <c r="I180" s="19" t="n"/>
+      <c r="J180" s="19" t="n"/>
+      <c r="K180" s="19" t="n"/>
+    </row>
+    <row r="181" ht="13.8" customFormat="1" customHeight="1" s="15">
       <c r="A181" s="19" t="n"/>
       <c r="B181" s="19" t="n"/>
       <c r="C181" s="19" t="n"/>
@@ -5282,27 +5279,21 @@
       <c r="F181" s="19" t="n"/>
       <c r="G181" s="19" t="n"/>
       <c r="H181" s="15" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I181" s="26" t="inlineStr">
         <is>
-          <t>そう、この謎の石は、なんと成長するのよ。
-石の成長とともに、キミの拠点は様々な恩恵を受けるの。
-住民の最大数があがったり、新しいポリシーを覚えたりね。</t>
-        </is>
-      </c>
-      <c r="J181" s="19" t="inlineStr">
-        <is>
-          <t>Yes, this mysterious stone actually grows.
-And as it grows, your base receives various benefits,
-like an increased maximum number of residents or new policies.</t>
+          <t>よしよし、盟約の石も育ってきたわ。</t>
+        </is>
+      </c>
+      <c r="J181" s="25" t="inlineStr">
+        <is>
+          <t>Well done, your Hearth Stone is growing.</t>
         </is>
       </c>
       <c r="K181" s="19" t="inlineStr">
         <is>
-          <t>Sim, essa pedra misteriosa realmente cresce.
-E conforme cresce, sua base recebe vários benefícios,
-como um aumento no número máximo de residentes ou novas políticas.</t>
+          <t>Muito bem, sua Pedra do Lar está crescendo.</t>
         </is>
       </c>
     </row>
@@ -5315,25 +5306,27 @@
       <c r="F182" s="19" t="n"/>
       <c r="G182" s="19" t="n"/>
       <c r="H182" s="15" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I182" s="26" t="inlineStr">
         <is>
-          <t>敵の中には、属性攻撃でアイテムや装備を破壊してくる厄介なのもいるけど
-石のレベルがあがれば、その破壊だって防いでくれるのよ？
-まあ…拠点の中だけだけどね。</t>
+          <t>そう、この謎の石は、なんと成長するのよ。
+石の成長とともに、キミの拠点は様々な恩恵を受けるの。
+住民の最大数があがったり、新しいポリシーを覚えたりね。</t>
         </is>
       </c>
       <c r="J182" s="19" t="inlineStr">
         <is>
-          <t>Some enemies can use elemental attacks to destroy your items and equipment,
-but if the stone levels up, it can even prevent that within your base.</t>
+          <t>Yes, this mysterious stone actually grows.
+And as it grows, your base receives various benefits,
+like an increased maximum number of residents or new policies.</t>
         </is>
       </c>
       <c r="K182" s="19" t="inlineStr">
         <is>
-          <t>Alguns inimigos podem usar ataques elementais para destruir seus itens e equipamentos,
-mas se a pedra subir de nível, ela pode até impedir isso dentro da sua base.</t>
+          <t>Sim, essa pedra misteriosa realmente cresce.
+E conforme cresce, sua base recebe vários benefícios,
+como um aumento no número máximo de residentes ou novas políticas.</t>
         </is>
       </c>
     </row>
@@ -5346,31 +5339,29 @@
       <c r="F183" s="19" t="n"/>
       <c r="G183" s="19" t="n"/>
       <c r="H183" s="15" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I183" s="26" t="inlineStr">
         <is>
-          <t>出荷や日数の経過で、石は自動的に育っていくわ。
-…ただ、注意したいのは、石のレベルがあがると
-拠点の危険度もあがる…つまり、強い敵が襲ってくるということね。</t>
+          <t>敵の中には、属性攻撃でアイテムや装備を破壊してくる厄介なのもいるけど
+石のレベルがあがれば、その破壊だって防いでくれるのよ？
+まあ…拠点の中だけだけどね。</t>
         </is>
       </c>
       <c r="J183" s="19" t="inlineStr">
         <is>
-          <t>The stone grows automatically through shipments and the passage of days.
-...But beware, as the stone levels up, the danger level of your base
-also increases... meaning stronger enemies will appear.</t>
+          <t>Some enemies can use elemental attacks to destroy your items and equipment,
+but if the stone levels up, it can even prevent that within your base.</t>
         </is>
       </c>
       <c r="K183" s="19" t="inlineStr">
         <is>
-          <t>A pedra cresce automaticamente com remessas e com a passagem dos dias.
-... Mas cuidado, à medida que a pedra sobe de nível, o nível de perigo da sua base
-também aumenta... Ou seja, inimigos mais fortes aparecerão.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="46.25" customFormat="1" customHeight="1" s="15">
+          <t>Alguns inimigos podem usar ataques elementais para destruir seus itens e equipamentos,
+mas se a pedra subir de nível, ela pode até impedir isso dentro da sua base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A184" s="19" t="n"/>
       <c r="B184" s="19" t="n"/>
       <c r="C184" s="19" t="n"/>
@@ -5379,32 +5370,31 @@
       <c r="F184" s="19" t="n"/>
       <c r="G184" s="19" t="n"/>
       <c r="H184" s="15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I184" s="26" t="inlineStr">
         <is>
-          <t>「成長抑止」のポリシーを施行すれば、石の成長に
-ストップをかけることができる。
-もし今拠点に現れる敵に手こずるようだったら
-このポリシーを使って成長を止めておいた方がいいわね。</t>
+          <t>出荷や日数の経過で、石は自動的に育っていくわ。
+…ただ、注意したいのは、石のレベルがあがると
+拠点の危険度もあがる…つまり、強い敵が襲ってくるということね。</t>
         </is>
       </c>
       <c r="J184" s="19" t="inlineStr">
         <is>
-          <t>You can use the "Growth Suppression" policy to stop the stone's growth.
-If you're struggling with the enemies currently appearing at your base,
-it might be a good idea to use this policy to halt the growth for a while.</t>
+          <t>The stone grows automatically through shipments and the passage of days.
+...But beware, as the stone levels up, the danger level of your base
+also increases... meaning stronger enemies will appear.</t>
         </is>
       </c>
       <c r="K184" s="19" t="inlineStr">
         <is>
-          <t>Você pode usar a política "Supressão de Crescimento" para impedir o crescimento da pedra.
-Se estiver tendo dificuldades com os inimigos que estão aparecendo na sua base,
-talvez seja uma boa ideia usar essa política para interromper o crescimento por um tempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>A pedra cresce automaticamente com remessas e com a passagem dos dias.
+... Mas cuidado, à medida que a pedra sobe de nível, o nível de perigo da sua base
+também aumenta... Ou seja, inimigos mais fortes aparecerão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="46.25" customFormat="1" customHeight="1" s="15">
       <c r="A185" s="19" t="n"/>
       <c r="B185" s="19" t="n"/>
       <c r="C185" s="19" t="n"/>
@@ -5412,9 +5402,31 @@
       <c r="E185" s="19" t="n"/>
       <c r="F185" s="19" t="n"/>
       <c r="G185" s="19" t="n"/>
-      <c r="I185" s="19" t="n"/>
-      <c r="J185" s="19" t="n"/>
-      <c r="K185" s="19" t="n"/>
+      <c r="H185" s="15" t="n">
+        <v>147</v>
+      </c>
+      <c r="I185" s="26" t="inlineStr">
+        <is>
+          <t>「成長抑止」のポリシーを施行すれば、石の成長に
+ストップをかけることができる。
+もし今拠点に現れる敵に手こずるようだったら
+このポリシーを使って成長を止めておいた方がいいわね。</t>
+        </is>
+      </c>
+      <c r="J185" s="19" t="inlineStr">
+        <is>
+          <t>You can use the "Growth Suppression" policy to stop the stone's growth.
+If you're struggling with the enemies currently appearing at your base,
+it might be a good idea to use this policy to halt the growth for a while.</t>
+        </is>
+      </c>
+      <c r="K185" s="19" t="inlineStr">
+        <is>
+          <t>Você pode usar a política "Supressão de Crescimento" para impedir o crescimento da pedra.
+Se estiver tendo dificuldades com os inimigos que estão aparecendo na sua base,
+talvez seja uma boa ideia usar essa política para interromper o crescimento por um tempo.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A186" s="19" t="n"/>
@@ -5430,11 +5442,7 @@
     </row>
     <row r="187" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A187" s="19" t="n"/>
-      <c r="B187" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B187" s="19" t="n"/>
       <c r="C187" s="19" t="n"/>
       <c r="D187" s="19" t="n"/>
       <c r="E187" s="19" t="n"/>
@@ -5445,12 +5453,12 @@
       <c r="K187" s="19" t="n"/>
     </row>
     <row r="188" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A188" s="19" t="inlineStr">
-        <is>
-          <t>feat</t>
-        </is>
-      </c>
-      <c r="B188" s="19" t="n"/>
+      <c r="A188" s="19" t="n"/>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C188" s="19" t="n"/>
       <c r="D188" s="19" t="n"/>
       <c r="E188" s="19" t="n"/>
@@ -5461,31 +5469,20 @@
       <c r="K188" s="19" t="n"/>
     </row>
     <row r="189" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A189" s="19" t="n"/>
+      <c r="A189" s="19" t="inlineStr">
+        <is>
+          <t>feat</t>
+        </is>
+      </c>
       <c r="B189" s="19" t="n"/>
       <c r="C189" s="19" t="n"/>
       <c r="D189" s="19" t="n"/>
       <c r="E189" s="19" t="n"/>
       <c r="F189" s="19" t="n"/>
       <c r="G189" s="19" t="n"/>
-      <c r="H189" s="15" t="n">
-        <v>148</v>
-      </c>
-      <c r="I189" s="19" t="inlineStr">
-        <is>
-          <t>フィートポイントの獲得おめでとう！</t>
-        </is>
-      </c>
-      <c r="J189" s="25" t="inlineStr">
-        <is>
-          <t>Congratulations on earning a Feat Point!</t>
-        </is>
-      </c>
-      <c r="K189" s="19" t="inlineStr">
-        <is>
-          <t>Parabéns por ganhar um Ponto de Talento!</t>
-        </is>
-      </c>
+      <c r="I189" s="19" t="n"/>
+      <c r="J189" s="19" t="n"/>
+      <c r="K189" s="19" t="n"/>
     </row>
     <row r="190" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A190" s="19" t="n"/>
@@ -5496,25 +5493,25 @@
       <c r="F190" s="19" t="n"/>
       <c r="G190" s="19" t="n"/>
       <c r="H190" s="15" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I190" s="19" t="inlineStr">
         <is>
-          <t>…え？　フィート、知らないの？</t>
-        </is>
-      </c>
-      <c r="J190" s="19" t="inlineStr">
-        <is>
-          <t>...Huh? You don’t know about Feats?</t>
+          <t>フィートポイントの獲得おめでとう！</t>
+        </is>
+      </c>
+      <c r="J190" s="25" t="inlineStr">
+        <is>
+          <t>Congratulations on earning a Feat Point!</t>
         </is>
       </c>
       <c r="K190" s="19" t="inlineStr">
         <is>
-          <t>Você não conhece os talentos?</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="32.8" customFormat="1" customHeight="1" s="15">
+          <t>Parabéns por ganhar um Ponto de Talento!</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A191" s="19" t="n"/>
       <c r="B191" s="19" t="n"/>
       <c r="C191" s="19" t="n"/>
@@ -5523,26 +5520,21 @@
       <c r="F191" s="19" t="n"/>
       <c r="G191" s="19" t="n"/>
       <c r="H191" s="15" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I191" s="19" t="inlineStr">
         <is>
-          <t>足が速かったり、力が強かったり
-そういうキミの特徴をフィートっていって
-フィートポイントを消費することで獲得できるの。</t>
+          <t>…え？　フィート、知らないの？</t>
         </is>
       </c>
       <c r="J191" s="19" t="inlineStr">
         <is>
-          <t>Feats are special traits you have,
-like being really fast or super strong.
-You can earn them by using Feat Points.</t>
+          <t>...Huh? You don’t know about Feats?</t>
         </is>
       </c>
       <c r="K191" s="19" t="inlineStr">
         <is>
-          <t>Talentos são características especiais que você tem, como ser muito rápido ou superforte.
-Você pode certas características usando Pontos de Talentos.</t>
+          <t>Você não conhece os talentos?</t>
         </is>
       </c>
     </row>
@@ -5555,31 +5547,30 @@
       <c r="F192" s="19" t="n"/>
       <c r="G192" s="19" t="n"/>
       <c r="H192" s="15" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I192" s="19" t="inlineStr">
         <is>
-          <t>画面の下に、青い羽マークのアイコンのゲージが見える？
-キミが何か行動して成長すると、このゲージは増えていく。
-ゲージが満杯になると、フィートポイントを貰えるわ。</t>
+          <t>足が速かったり、力が強かったり
+そういうキミの特徴をフィートっていって
+フィートポイントを消費することで獲得できるの。</t>
         </is>
       </c>
       <c r="J192" s="19" t="inlineStr">
         <is>
-          <t>Do you see the blue feather icon at the bottom of your screen?
-When you perform actions and grow, this gauge fills up.
-Once it’s full, you earn a Feat Point.</t>
+          <t>Feats are special traits you have,
+like being really fast or super strong.
+You can earn them by using Feat Points.</t>
         </is>
       </c>
       <c r="K192" s="19" t="inlineStr">
         <is>
-          <t>Você vê o ícone de pena azul na parte inferior da tela?
-Quando você realiza ações e cresce, esse medidor se enche.
-Quando ele estiver cheio, você ganha um Ponto de Talento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="43.25" customFormat="1" customHeight="1" s="15">
+          <t>Talentos são características especiais que você tem, como ser muito rápido ou superforte.
+Você pode certas características usando Pontos de Talentos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="A193" s="19" t="n"/>
       <c r="B193" s="19" t="n"/>
       <c r="C193" s="19" t="n"/>
@@ -5588,30 +5579,31 @@
       <c r="F193" s="19" t="n"/>
       <c r="G193" s="19" t="n"/>
       <c r="H193" s="15" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I193" s="19" t="inlineStr">
         <is>
-          <t>ゲージをクリックすると、キミが獲得できる
-フィートの一覧が表示されるでしょ？
-この中から、キミが役に立ちそうと思うフィートを
-選択して見るといいわ。</t>
+          <t>画面の下に、青い羽マークのアイコンのゲージが見える？
+キミが何か行動して成長すると、このゲージは増えていく。
+ゲージが満杯になると、フィートポイントを貰えるわ。</t>
         </is>
       </c>
       <c r="J193" s="19" t="inlineStr">
         <is>
-          <t>Click on the gauge to see a list of Feats you can acquire.
-Choose the ones you think will be useful to you.</t>
+          <t>Do you see the blue feather icon at the bottom of your screen?
+When you perform actions and grow, this gauge fills up.
+Once it’s full, you earn a Feat Point.</t>
         </is>
       </c>
       <c r="K193" s="19" t="inlineStr">
         <is>
-          <t>Clique no medidor para ver uma lista de Talentos que você pode adquirir.
-Escolha os que achar que serão úteis para você.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="32.8" customFormat="1" customHeight="1" s="15">
+          <t>Você vê o ícone de pena azul na parte inferior da tela?
+Quando você realiza ações e cresce, esse medidor se enche.
+Quando ele estiver cheio, você ganha um Ponto de Talento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="43.25" customFormat="1" customHeight="1" s="15">
       <c r="A194" s="19" t="n"/>
       <c r="B194" s="19" t="n"/>
       <c r="C194" s="19" t="n"/>
@@ -5620,30 +5612,30 @@
       <c r="F194" s="19" t="n"/>
       <c r="G194" s="19" t="n"/>
       <c r="H194" s="15" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I194" s="19" t="inlineStr">
         <is>
-          <t>フィートポイントは、貯めておくこともできるから
-今自分に足りないと思うものが特になければ
-温存しておくのもいい選択ね。</t>
+          <t>ゲージをクリックすると、キミが獲得できる
+フィートの一覧が表示されるでしょ？
+この中から、キミが役に立ちそうと思うフィートを
+選択して見るといいわ。</t>
         </is>
       </c>
       <c r="J194" s="19" t="inlineStr">
         <is>
-          <t>You can also save your Feat Points
-if you don’t need anything specific right now.
-It’s a good strategy to save them for later.</t>
+          <t>Click on the gauge to see a list of Feats you can acquire.
+Choose the ones you think will be useful to you.</t>
         </is>
       </c>
       <c r="K194" s="19" t="inlineStr">
         <is>
-          <t>Você também pode salvar seus Pontos de Talentos se não precisar de nada específico no momento.
-É uma boa estratégia guardá-los para mais tarde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="32.8" customHeight="1" s="17">
+          <t>Clique no medidor para ver uma lista de Talentos que você pode adquirir.
+Escolha os que achar que serão úteis para você.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="A195" s="19" t="n"/>
       <c r="B195" s="19" t="n"/>
       <c r="C195" s="19" t="n"/>
@@ -5652,142 +5644,174 @@
       <c r="F195" s="19" t="n"/>
       <c r="G195" s="19" t="n"/>
       <c r="H195" s="15" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I195" s="19" t="inlineStr">
         <is>
-          <t>ちなみに、獲得に前提条件のあるフィートもあるからね。
-例えば「美食家」のフィートは
-「料理」スキルを覚えていなければ表示されないの。</t>
+          <t>フィートポイントは、貯めておくこともできるから
+今自分に足りないと思うものが特になければ
+温存しておくのもいい選択ね。</t>
         </is>
       </c>
       <c r="J195" s="19" t="inlineStr">
         <is>
-          <t>Note that some Feats have prerequisites.
-For example, the “Gourmet” Feat won’t appear
-unless you’ve learned the “Cooking” skill.</t>
+          <t>You can also save your Feat Points
+if you don’t need anything specific right now.
+It’s a good strategy to save them for later.</t>
         </is>
       </c>
       <c r="K195" s="19" t="inlineStr">
         <is>
-          <t>Observe que alguns Talentos têm pré-requisitos.
-Por exemplo, o Talento “Gourmet” não aparecerá a menos que você tenha aprendido a habilidade “Culinária”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Você também pode salvar seus Pontos de Talentos se não precisar de nada específico no momento.
+É uma boa estratégia guardá-los para mais tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="32.8" customHeight="1" s="17">
       <c r="A196" s="19" t="n"/>
-      <c r="B196" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B196" s="19" t="n"/>
       <c r="C196" s="19" t="n"/>
       <c r="D196" s="19" t="n"/>
       <c r="E196" s="19" t="n"/>
       <c r="F196" s="19" t="n"/>
       <c r="G196" s="19" t="n"/>
-      <c r="I196" s="19" t="n"/>
-      <c r="J196" s="19" t="n"/>
-      <c r="K196" s="19" t="n"/>
+      <c r="H196" s="15" t="n">
+        <v>154</v>
+      </c>
+      <c r="I196" s="19" t="inlineStr">
+        <is>
+          <t>ちなみに、獲得に前提条件のあるフィートもあるからね。
+例えば「美食家」のフィートは
+「料理」スキルを覚えていなければ表示されないの。</t>
+        </is>
+      </c>
+      <c r="J196" s="19" t="inlineStr">
+        <is>
+          <t>Note that some Feats have prerequisites.
+For example, the “Gourmet” Feat won’t appear
+unless you’ve learned the “Cooking” skill.</t>
+        </is>
+      </c>
+      <c r="K196" s="19" t="inlineStr">
+        <is>
+          <t>Observe que alguns Talentos têm pré-requisitos.
+Por exemplo, o Talento “Gourmet” não aparecerá a menos que você tenha aprendido a habilidade “Culinária”.</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B197" s="19" t="n"/>
+      <c r="A197" s="19" t="n"/>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="n"/>
+      <c r="D197" s="19" t="n"/>
+      <c r="E197" s="19" t="n"/>
+      <c r="F197" s="19" t="n"/>
+      <c r="G197" s="19" t="n"/>
+      <c r="I197" s="19" t="n"/>
+      <c r="J197" s="19" t="n"/>
+      <c r="K197" s="19" t="n"/>
     </row>
     <row r="198" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A198" s="19" t="inlineStr">
+      <c r="B198" s="19" t="n"/>
+    </row>
+    <row r="199" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A199" s="19" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="200" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H200" s="15" t="n">
+    <row r="200" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="201" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H201" s="15" t="n">
         <v>105</v>
       </c>
-      <c r="I200" s="19" t="inlineStr">
+      <c r="I201" s="19" t="inlineStr">
         <is>
           <t>よしよし、丸太さんを手に入れたのね。</t>
         </is>
       </c>
-      <c r="J200" s="25" t="inlineStr">
+      <c r="J201" s="25" t="inlineStr">
         <is>
           <t>Alright, you got a log!</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="K201" t="inlineStr">
         <is>
           <t>Muito bem, você conseguiu um tronco!</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H201" s="15" t="n">
+    <row r="202" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H202" s="15" t="n">
         <v>106</v>
       </c>
-      <c r="I201" s="19" t="inlineStr">
+      <c r="I202" s="19" t="inlineStr">
         <is>
           <t>丸太さん、いえ、丸太先生は最も基本的なクラフト素材で
 焚火などの燃料としても使える優れモノよ。</t>
         </is>
       </c>
-      <c r="J201" s="19" t="inlineStr">
+      <c r="J202" s="19" t="inlineStr">
         <is>
           <t>Logs, or should I say, Mr. Log, are the most basic crafting materials.
 They’re also excellent for things like campfire fuel.</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>Os Troncos, ou melhor, o Sr. Tronco, são os materiais de fabricação mais básicos.
 Elas também são excelentes para coisas como combustível para fogueira.</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H202" s="15" t="n">
+    <row r="203" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H203" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="I202" s="19" t="inlineStr">
+      <c r="I203" s="19" t="inlineStr">
         <is>
           <t>でも…それだけじゃない！
 丸太先生は加工することで
 さらに「厚板」へと進化するの。</t>
         </is>
       </c>
-      <c r="J202" s="19" t="inlineStr">
+      <c r="J203" s="19" t="inlineStr">
         <is>
           <t>But... that’s not all!
 By processing Mr. Log, you can upgrade it into "Planks".</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K203" t="inlineStr">
         <is>
           <t>Mas isso não é tudo!
 Ao processar o Sr. Tronco, você pode transformá-lo em "Tábuas".</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H203" s="15" t="n">
+    <row r="204" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H204" s="15" t="n">
         <v>108</v>
       </c>
-      <c r="I203" s="19" t="inlineStr">
+      <c r="I204" s="19" t="inlineStr">
         <is>
           <t>え…？どうやったら加工できる？
 そうね、丸太先生に聞いてみたらどう？
 ヒントは「加工設備」よ。</t>
         </is>
       </c>
-      <c r="J203" s="19" t="inlineStr">
+      <c r="J204" s="19" t="inlineStr">
         <is>
           <t>Huh...? How do you process it?
 Well, why don't you ask Mr. Log yourself?
 The hint is 'processing equipment'.</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="K204" t="inlineStr">
         <is>
           <t>O quê? Como você processa isso?
 Bem, por que você mesmo não pergunta ao Sr. Tronco?
@@ -5795,114 +5819,114 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H204" s="15" t="n">
+    <row r="205" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H205" s="15" t="n">
         <v>109</v>
       </c>
-      <c r="I204" s="19" t="inlineStr">
+      <c r="I205" s="19" t="inlineStr">
         <is>
           <t>…ちなみに、石も「切り石」に加工できるから
 覚えておいてね。</t>
         </is>
       </c>
-      <c r="J204" s="19" t="inlineStr">
+      <c r="J205" s="19" t="inlineStr">
         <is>
           <t>...Oh, and by the way, you can also process stones
 into "Cut Stone", so keep that in mind too.</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="K205" t="inlineStr">
         <is>
           <t>... Ah, e a propósito, você também pode processar pedras em “Pedra Cortada”, portanto, lembre-se disso também.</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B205" s="19" t="inlineStr">
+    <row r="206" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B206" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A206" s="19" t="inlineStr">
+    <row r="207" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A207" s="19" t="inlineStr">
         <is>
           <t>hardness</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="208" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H208" s="15" t="n">
+    <row r="208" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="209" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H209" s="15" t="n">
         <v>110</v>
       </c>
-      <c r="I208" s="19" t="inlineStr">
+      <c r="I209" s="19" t="inlineStr">
         <is>
           <t>よしよ～し、道具を作ったのね。</t>
         </is>
       </c>
-      <c r="J208" s="25" t="inlineStr">
+      <c r="J209" s="25" t="inlineStr">
         <is>
           <t>Good, you made a tool!</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K209" t="inlineStr">
         <is>
           <t>Muito bem, você criou uma ferramenta.</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H209" s="15" t="n">
+    <row r="210" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H210" s="15" t="n">
         <v>111</v>
       </c>
-      <c r="I209" s="19" t="inlineStr">
+      <c r="I210" s="19" t="inlineStr">
         <is>
           <t>全てのアイテムは、何らかの「素材」からできている。
 そして、「素材」にはそれぞれ特徴があるの。</t>
         </is>
       </c>
-      <c r="J209" s="25" t="inlineStr">
+      <c r="J210" s="25" t="inlineStr">
         <is>
           <t>All items are made from some kind of "material".
 And each material has its own characteristics.</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="K210" t="inlineStr">
         <is>
           <t>Todos os itens são feitos de algum tipo de “material”.
 E cada material tem suas próprias características.</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H210" s="15" t="n">
+    <row r="211" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H211" s="15" t="n">
         <v>112</v>
       </c>
-      <c r="I210" s="19" t="inlineStr">
+      <c r="I211" s="19" t="inlineStr">
         <is>
           <t>例えば紙でできたアイテムは軽かったり
 鉄でできたアイテムは、重いけど燃えにくかったりってね。</t>
         </is>
       </c>
-      <c r="J210" s="25" t="inlineStr">
+      <c r="J211" s="25" t="inlineStr">
         <is>
           <t>For example, items made of paper are light,
 while items made of iron are heavy but hard to burn.</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="K211" t="inlineStr">
         <is>
           <t>Por exemplo, itens feitos de papel são leves,
 enquanto itens feitos de ferro são pesados, mas difíceis de queimar.</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="46.25" customFormat="1" customHeight="1" s="15">
-      <c r="H211" s="15" t="n">
+    <row r="212" ht="46.25" customFormat="1" customHeight="1" s="15">
+      <c r="H212" s="15" t="n">
         <v>113</v>
       </c>
-      <c r="I211" s="19" t="inlineStr">
+      <c r="I212" s="19" t="inlineStr">
         <is>
           <t>素材の特徴の一つに「硬さ」というものがあって
 特につるはしのような道具では
@@ -5910,7 +5934,7 @@
 この「硬さ」が重要になってくるの。</t>
         </is>
       </c>
-      <c r="J211" s="25" t="inlineStr">
+      <c r="J212" s="25" t="inlineStr">
         <is>
           <t>One of the characteristics of materials is "hardness",
 which is especially important for tools like pickaxes.
@@ -5918,147 +5942,147 @@
 so this "hardness" is very crucial.</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K212" t="inlineStr">
         <is>
           <t>Uma das características dos materiais é a “dureza”, que é especialmente importante para ferramentas como picaretas.
 A dureza do material determina o tipo de pedra ou minério que você pode minerar, portanto, essa "dureza" é muito importante.</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H212" s="15" t="n">
+    <row r="213" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H213" s="15" t="n">
         <v>114</v>
       </c>
-      <c r="I212" s="19" t="inlineStr">
+      <c r="I213" s="19" t="inlineStr">
         <is>
           <t>もし今のつるはしで掘れない石が出てきたら
 もっと硬い素材でつるはしを作り直してみるといいわ。</t>
         </is>
       </c>
-      <c r="J212" s="25" t="inlineStr">
+      <c r="J213" s="25" t="inlineStr">
         <is>
           <t>If you come across stones that your current pickaxe can’t mine,
 try making a new pickaxe with a harder material.</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>Se você encontrar pedras que sua picareta atual não consegue minerar,
 tente criar uma nova picareta com um material mais duro.</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="23.85" customHeight="1" s="17">
-      <c r="H213" s="15" t="n">
+    <row r="214" ht="23.85" customHeight="1" s="17">
+      <c r="H214" s="15" t="n">
         <v>115</v>
       </c>
-      <c r="I213" s="19" t="inlineStr">
+      <c r="I214" s="19" t="inlineStr">
         <is>
           <t>まあ…採掘のスキルを上げまくって
 力ずくで掘っちゃってもいいんだけどね。</t>
         </is>
       </c>
-      <c r="J213" s="25" t="inlineStr">
+      <c r="J214" s="25" t="inlineStr">
         <is>
           <t>Well... you can actually level up your mining skills a lot and
 just power through it, but anyway, hehe.</t>
         </is>
       </c>
-      <c r="K213" s="15" t="inlineStr">
+      <c r="K214" s="15" t="inlineStr">
         <is>
           <t>Bem... na verdade, você pode aumentar muito o nível de suas habilidades de mineração e simplesmente ignorar isso, mas, de qualquer forma, hehe.</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B214" s="19" t="inlineStr">
+    <row r="215" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B215" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B215" s="19" t="n"/>
-    </row>
-    <row r="216" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="A216" s="19" t="inlineStr">
+    <row r="216" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B216" s="19" t="n"/>
+    </row>
+    <row r="217" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="A217" s="19" t="inlineStr">
         <is>
           <t>middle_click</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="218" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H218" s="15" t="n">
+    <row r="218" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="219" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H219" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="I218" s="19" t="inlineStr">
+      <c r="I219" s="19" t="inlineStr">
         <is>
           <t>よしよし、作業台を作れたのね。</t>
         </is>
       </c>
-      <c r="J218" s="25" t="inlineStr">
+      <c r="J219" s="25" t="inlineStr">
         <is>
           <t>Good, you've made the workbench.</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="K219" t="inlineStr">
         <is>
           <t>Ótimo, você fez a bancada de trabalho.</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H219" s="15" t="n">
+    <row r="220" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H220" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="I219" s="19" t="inlineStr">
+      <c r="I220" s="19" t="inlineStr">
         <is>
           <t>キミに一つ重要なことを教えてあげる。
 一人前の冒険者になるためには、絶対覚えなきゃいけないこと…
 そう、「ミドルクリック」よ。</t>
         </is>
       </c>
-      <c r="J219" s="19" t="inlineStr">
+      <c r="J220" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Let me tell you something crucial for becoming a seasoned adventurer...
 Yes, it's the 'middle click'. </t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="K220" t="inlineStr">
         <is>
           <t>Vou lhe dizer algo crucial para se tornar um aventureiro experiente...
 Sim, é o “clique do meio”.</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H220" s="15" t="n">
+    <row r="221" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H221" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="I220" s="19" t="inlineStr">
+      <c r="I221" s="19" t="inlineStr">
         <is>
           <t>バックパックのアイテムや、マップ上の生物やアイテムは
 ミドルクリックすることで「干渉」することができるの。</t>
         </is>
       </c>
-      <c r="J220" s="19" t="inlineStr">
+      <c r="J221" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">By middle-clicking, you can 'interact' with items in your backpack,
 creatures, or objects on the map. </t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>Ao clicar com o botão do meio, você pode “interagir” com itens da mochila, criaturas ou objetos no mapa.</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="64.15000000000001" customFormat="1" customHeight="1" s="15">
-      <c r="H221" s="15" t="n">
+    <row r="222" ht="64.15000000000001" customFormat="1" customHeight="1" s="15">
+      <c r="H222" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="I221" s="19" t="inlineStr">
+      <c r="I222" s="19" t="inlineStr">
         <is>
           <t>例えば邪魔な生物を蹴って動かしたり
 機械のスイッチを入れたり
@@ -6067,7 +6091,7 @@
 普段できない色々な行動が、ミドルクリックによって解放されるのよ。</t>
         </is>
       </c>
-      <c r="J221" s="19" t="inlineStr">
+      <c r="J222" s="19" t="inlineStr">
         <is>
           <t>You can do various actions like
 kicking away pesky creatures,
@@ -6077,7 +6101,7 @@
 It unleashes a whole range of actions that you can't usually do.</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="K222" t="inlineStr">
         <is>
           <t>Você pode realizar várias ações, como
 chutar criaturas incômodas,
@@ -6088,25 +6112,25 @@
         </is>
       </c>
     </row>
-    <row r="222" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H222" s="15" t="n">
+    <row r="223" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H223" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="I222" s="19" t="inlineStr">
+      <c r="I223" s="19" t="inlineStr">
         <is>
           <t>さらに、家具や壁などを設置する時も
 ミドルクリックすれば、対象物を回転させることができる…
 これを知らない冒険者は、この世界では生きていけないわ。</t>
         </is>
       </c>
-      <c r="J222" s="19" t="inlineStr">
+      <c r="J223" s="19" t="inlineStr">
         <is>
           <t>Moreover, when placing furniture or walls,
 middle-clicking will also let you rotate them...
 Adventurers who don't know this won't survive in this world.</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="K223" t="inlineStr">
         <is>
           <t>Além disso, ao colocar móveis ou paredes,
 clicar com o botão do meio também permitirá que você os gire...
@@ -6114,334 +6138,334 @@
         </is>
       </c>
     </row>
-    <row r="223" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H223" s="15" t="n">
+    <row r="224" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H224" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="I223" s="19" t="inlineStr">
+      <c r="I224" s="19" t="inlineStr">
         <is>
           <t>…いい？ ミドルクリック…覚えた？</t>
         </is>
       </c>
-      <c r="J223" s="19" t="inlineStr">
+      <c r="J224" s="19" t="inlineStr">
         <is>
           <t>Middle click... got it...?</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="K224" t="inlineStr">
         <is>
           <t>Clique do Meio... Entendeu?
 (Dá pra alterar no menu)</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H224" s="15" t="n">
+    <row r="225" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H225" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="I224" s="19" t="inlineStr">
+      <c r="I225" s="19" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="J224" s="19" t="inlineStr">
+      <c r="J225" s="19" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="K225" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H225" s="15" t="n">
+    <row r="226" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H226" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="I225" s="19" t="inlineStr">
+      <c r="I226" s="19" t="inlineStr">
         <is>
           <t>そうそう
 ミドルクリックはキーボードの「R」キーでも代用できるからね。</t>
         </is>
       </c>
-      <c r="J225" s="19" t="inlineStr">
+      <c r="J226" s="19" t="inlineStr">
         <is>
           <t>Yes, you can also use the 'R' key on your keyboard
 as a substitute for middle click...</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="K226" t="inlineStr">
         <is>
           <t>Ah, você também pode usar a tecla "R" do seu teclado
 como substituto do clique do meio...</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="12.8" customHeight="1" s="17">
-      <c r="H226" s="15" t="n">
+    <row r="227" ht="12.8" customHeight="1" s="17">
+      <c r="H227" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="I226" s="19" t="inlineStr">
+      <c r="I227" s="19" t="inlineStr">
         <is>
           <t>それでは、また…</t>
         </is>
       </c>
-      <c r="J226" s="19" t="inlineStr">
+      <c r="J227" s="19" t="inlineStr">
         <is>
           <t>Well then...I'll see you later...</t>
         </is>
       </c>
-      <c r="K226" s="15" t="inlineStr">
+      <c r="K227" s="15" t="inlineStr">
         <is>
           <t>Bem, então... Até mais tarde…</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="12.8" customHeight="1" s="17">
-      <c r="B227" s="19" t="inlineStr">
+    <row r="228" ht="12.8" customHeight="1" s="17">
+      <c r="B228" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K227" s="15" t="n"/>
-    </row>
-    <row r="228" ht="15.65" customHeight="1" s="17"/>
+      <c r="K228" s="15" t="n"/>
+    </row>
     <row r="229" ht="15.65" customHeight="1" s="17"/>
     <row r="230" ht="15.65" customHeight="1" s="17"/>
-    <row r="231" ht="12.8" customHeight="1" s="17">
-      <c r="A231" s="15" t="inlineStr">
+    <row r="231" ht="15.65" customHeight="1" s="17"/>
+    <row r="232" ht="12.8" customHeight="1" s="17">
+      <c r="A232" s="15" t="inlineStr">
         <is>
           <t>food</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="12.8" customHeight="1" s="17">
-      <c r="H233" s="15" t="n">
+    <row r="234" ht="12.8" customHeight="1" s="17">
+      <c r="H234" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="I233" s="19" t="inlineStr">
+      <c r="I234" s="19" t="inlineStr">
         <is>
           <t>わあ…きのこちょーだい？</t>
         </is>
       </c>
-      <c r="J233" s="25" t="inlineStr">
+      <c r="J234" s="25" t="inlineStr">
         <is>
           <t>Wow... Can I have some mushrooms?</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="K234" t="inlineStr">
         <is>
           <t>Nossa! Posso comer alguns cogumelos?</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="12.8" customHeight="1" s="17">
-      <c r="B234" s="15" t="inlineStr">
-        <is>
-          <t>food2</t>
-        </is>
-      </c>
-      <c r="D234" s="15" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="H234" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="I234" s="19" t="inlineStr">
-        <is>
-          <t>ああ</t>
-        </is>
-      </c>
-      <c r="J234" s="25" t="inlineStr">
-        <is>
-          <t>Yes.</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>Sim.</t>
         </is>
       </c>
     </row>
     <row r="235" ht="12.8" customHeight="1" s="17">
       <c r="B235" s="15" t="inlineStr">
         <is>
+          <t>food2</t>
+        </is>
+      </c>
+      <c r="D235" s="15" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="H235" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="I235" s="19" t="inlineStr">
+        <is>
+          <t>ああ</t>
+        </is>
+      </c>
+      <c r="J235" s="25" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Sim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="12.8" customHeight="1" s="17">
+      <c r="B236" s="15" t="inlineStr">
+        <is>
           <t>food3</t>
         </is>
       </c>
-      <c r="D235" s="15" t="inlineStr">
+      <c r="D236" s="15" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="H235" s="15" t="n">
+      <c r="H236" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="I235" s="19" t="inlineStr">
+      <c r="I236" s="19" t="inlineStr">
         <is>
           <t>いや</t>
         </is>
       </c>
-      <c r="J235" s="25" t="inlineStr">
+      <c r="J236" s="25" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="K236" t="inlineStr">
         <is>
           <t>Não.</t>
         </is>
       </c>
     </row>
-    <row r="236" ht="12.8" customHeight="1" s="17">
-      <c r="I236" s="19" t="n"/>
-      <c r="J236" s="25" t="n"/>
-    </row>
     <row r="237" ht="12.8" customHeight="1" s="17">
-      <c r="A237" s="15" t="inlineStr">
-        <is>
-          <t>food2</t>
-        </is>
-      </c>
       <c r="I237" s="19" t="n"/>
       <c r="J237" s="25" t="n"/>
     </row>
-    <row r="238" ht="22.35" customHeight="1" s="17">
-      <c r="H238" s="15" t="n">
+    <row r="238" ht="12.8" customHeight="1" s="17">
+      <c r="A238" s="15" t="inlineStr">
+        <is>
+          <t>food2</t>
+        </is>
+      </c>
+      <c r="I238" s="19" t="n"/>
+      <c r="J238" s="25" t="n"/>
+    </row>
+    <row r="239" ht="22.35" customHeight="1" s="17">
+      <c r="H239" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="I238" s="19" t="inlineStr">
+      <c r="I239" s="19" t="inlineStr">
         <is>
           <t>もぐもぐもぐ。おいしい～。
 これ私の大好物なの。覚えておいてね！</t>
         </is>
       </c>
-      <c r="J238" s="19" t="inlineStr">
+      <c r="J239" s="19" t="inlineStr">
         <is>
           <t>Munch munch munch. Yummy.
 These are my favorite! Remember that, okay?</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="K239" t="inlineStr">
         <is>
           <t>Munch munch munch. Que delícia.
 Estes são os meus favoritos! Lembre-se disso, ok?</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H239" s="15" t="n">
+    <row r="240" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H240" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="I239" s="19" t="inlineStr">
+      <c r="I240" s="19" t="inlineStr">
         <is>
           <t>きのこは美味しいけど、腹持ちがよくないし
 時間がたつと腐ってしまうのが難点ね。</t>
         </is>
       </c>
-      <c r="J239" s="19" t="inlineStr">
+      <c r="J240" s="19" t="inlineStr">
         <is>
           <t>Mushrooms are tasty, but they don't keep you full for long
 and the fact that they spoil over time is a downside.</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="K240" t="inlineStr">
         <is>
           <t>Os cogumelos são saborosos, mas não o mantêm saciado por muito tempo
 e o fato de que eles estragam com o tempo é uma desvantagem.</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="22.35" customHeight="1" s="17">
-      <c r="H240" s="15" t="n">
+    <row r="241" ht="22.35" customHeight="1" s="17">
+      <c r="H241" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="I240" s="19" t="inlineStr">
+      <c r="I241" s="19" t="inlineStr">
         <is>
           <t>そう、食べ物はずっと置いておくと腐ってしまうのよ。
 知らなかった？</t>
         </is>
       </c>
-      <c r="J240" s="19" t="inlineStr">
+      <c r="J241" s="19" t="inlineStr">
         <is>
           <t>Yes, food spoils if you leave it out too long.
 You didn't know that?</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="K241" t="inlineStr">
         <is>
           <t>Sim, os alimentos estragam se você os deixar no "chão" ou na "bolsa" por muito tempo.
 Você não sabia disso?</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="22.35" customHeight="1" s="17">
-      <c r="H241" s="15" t="n">
+    <row r="242" ht="22.35" customHeight="1" s="17">
+      <c r="H242" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="I241" s="19" t="inlineStr">
+      <c r="I242" s="19" t="inlineStr">
         <is>
           <t>当たり前だけど、腐ったものを食べるとお腹を壊すから
 絶対食べてはだめよ。</t>
         </is>
       </c>
-      <c r="J241" s="19" t="inlineStr">
+      <c r="J242" s="19" t="inlineStr">
         <is>
           <t>Of course, eating spoiled food can make you sick
 so you should never eat it.</t>
         </is>
       </c>
-      <c r="K241" s="15" t="inlineStr">
+      <c r="K242" s="15" t="inlineStr">
         <is>
           <t>É claro que comer alimentos estragados pode deixá-lo doente, portanto, você nunca deve comê-los.</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="22.35" customHeight="1" s="17">
-      <c r="H242" s="15" t="n">
+    <row r="243" ht="22.35" customHeight="1" s="17">
+      <c r="H243" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="I242" s="19" t="inlineStr">
+      <c r="I243" s="19" t="inlineStr">
         <is>
           <t>魚や生ものは特に腐りやすいわね。
 逆に、木の実や調理した食料はかなり日持ちするの。</t>
         </is>
       </c>
-      <c r="J242" s="19" t="inlineStr">
+      <c r="J243" s="19" t="inlineStr">
         <is>
           <t>Fish and raw food spoil especially easily
 but nuts and cooked food can last quite a while.</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="K243" t="inlineStr">
         <is>
           <t>Peixes e alimentos crus estragam com facilidade,
 mas nozes e comida cozida duram bastante tempo.</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="32.8" customHeight="1" s="17">
-      <c r="H243" s="15" t="n">
+    <row r="244" ht="32.8" customHeight="1" s="17">
+      <c r="H244" s="15" t="n">
         <v>43</v>
       </c>
-      <c r="I243" s="19" t="inlineStr">
+      <c r="I244" s="19" t="inlineStr">
         <is>
           <t>石臼があれば、キブルみたいな全く腐らない料理も作れるのよ。
 長旅の前には、十分な保存食を用意しておくのが
 冒険者の鉄則ね。</t>
         </is>
       </c>
-      <c r="J243" s="19" t="inlineStr">
+      <c r="J244" s="19" t="inlineStr">
         <is>
           <t>With a millstone, you can even make meals like kibble that never spoil.
 Remember to prepare enough non-perishable food before a long journey.
 It's a golden rule for adventurers.</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="K244" t="inlineStr">
         <is>
           <t>Com um Moinho de Pedra, você pode até fazer refeições como ração que nunca estraga.
 Lembre-se de levar comida não perecível suficiente antes de uma longa jornada.
@@ -6449,99 +6473,99 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="12.8" customHeight="1" s="17">
-      <c r="B244" s="15" t="inlineStr">
+    <row r="245" ht="12.8" customHeight="1" s="17">
+      <c r="B245" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="J244" s="19" t="n"/>
-    </row>
-    <row r="245" ht="12.8" customHeight="1" s="17">
-      <c r="A245" s="15" t="inlineStr">
+      <c r="J245" s="19" t="n"/>
+    </row>
+    <row r="246" ht="12.8" customHeight="1" s="17">
+      <c r="A246" s="15" t="inlineStr">
         <is>
           <t>food3</t>
         </is>
       </c>
-      <c r="J245" s="19" t="n"/>
-    </row>
-    <row r="246" ht="12.8" customHeight="1" s="17">
-      <c r="H246" s="15" t="n">
+      <c r="J246" s="19" t="n"/>
+    </row>
+    <row r="247" ht="12.8" customHeight="1" s="17">
+      <c r="H247" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="I246" s="19" t="inlineStr">
+      <c r="I247" s="19" t="inlineStr">
         <is>
           <t>ケチ！</t>
         </is>
       </c>
-      <c r="J246" s="25" t="inlineStr">
+      <c r="J247" s="25" t="inlineStr">
         <is>
           <t>Cheap!</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="K247" t="inlineStr">
         <is>
           <t>Que barato!</t>
         </is>
       </c>
     </row>
-    <row r="247" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B247" s="15" t="inlineStr">
+    <row r="248" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B248" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="249" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A249" s="19" t="inlineStr">
+    <row r="249" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="250" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A250" s="19" t="inlineStr">
         <is>
           <t>tinker</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H250" s="15" t="n">
+    <row r="251" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H251" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="I250" s="19" t="inlineStr">
+      <c r="I251" s="19" t="inlineStr">
         <is>
           <t>わぁ、見てみて、行商人達がいっぱい！
 色んなものを売ってるよ！</t>
         </is>
       </c>
-      <c r="J250" s="25" t="inlineStr">
+      <c r="J251" s="25" t="inlineStr">
         <is>
           <t>Wow, look at all the tinkers!
 They're selling all kinds of things!</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
+      <c r="K251" t="inlineStr">
         <is>
           <t>Uau, olha quantos mercadores!_x000D_
 Eles estão vendendo todo tipo de coisa!</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H251" s="15" t="n">
+    <row r="252" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H252" s="15" t="n">
         <v>94</v>
       </c>
-      <c r="I251" s="19" t="inlineStr">
+      <c r="I252" s="19" t="inlineStr">
         <is>
           <t>まるで小さな街の一角のようね。
 ほら、あの掲示板
 冒険者向けの依頼も掲載されているみたい。</t>
         </is>
       </c>
-      <c r="J251" s="19" t="inlineStr">
+      <c r="J252" s="19" t="inlineStr">
         <is>
           <t>It's like a little corner of a town.
 Look, that notice board seems to have
 quests for adventurers posted on it.</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K252" t="inlineStr">
         <is>
           <t>Parece um pequeno canto de uma cidade._x000D_
 Olha, aquele quadro de avisos parece ter_x000D_
@@ -6549,25 +6573,25 @@
         </is>
       </c>
     </row>
-    <row r="252" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H252" s="15" t="n">
+    <row r="253" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H253" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="I252" s="19" t="inlineStr">
+      <c r="I253" s="19" t="inlineStr">
         <is>
           <t>依頼を達成すると、様々な報酬がもらえるから
 掲示板を見かけたらこまめにチェック！
 ★の数が多い依頼は難しいから気を付けて。</t>
         </is>
       </c>
-      <c r="J252" s="19" t="inlineStr">
+      <c r="J253" s="19" t="inlineStr">
         <is>
           <t>Completing quests earns you various rewards,
 so make sure to check the notice board regularly!
 Be careful with quests that have many ★. They're more difficult.</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="K253" t="inlineStr">
         <is>
           <t>Completar missões rende várias recompensas,_x000D_
 então certifique-se de verificar o quadro de avisos regularmente!_x000D_
@@ -6575,25 +6599,25 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H253" s="15" t="n">
+    <row r="254" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H254" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="I253" s="19" t="inlineStr">
+      <c r="I254" s="19" t="inlineStr">
         <is>
           <t>あら、この停泊地、癒し手もいるのね。
 癒し手は状態異常を治療してくれるし、あっちの魔術師は
 未鑑定のアイテムを鑑定してくれるわ…まあ、タダじゃないけどね。</t>
         </is>
       </c>
-      <c r="J253" s="19" t="inlineStr">
+      <c r="J254" s="19" t="inlineStr">
         <is>
           <t>Oh, this camp also has a healer.
 The healer can cure status ailments, and the mage there
 can appraise unidentified items...though it does cost money.</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="K254" t="inlineStr">
         <is>
           <t>Oh, este acampamento também tem um curandeiro.
 O curandeiro pode curar estados negativos, e o mago ali
@@ -6601,65 +6625,65 @@
         </is>
       </c>
     </row>
-    <row r="254" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H254" s="15" t="n">
-        <v>97</v>
-      </c>
-      <c r="I254" s="19" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J254" s="19" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-    </row>
     <row r="255" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H255" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="I255" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J255" s="19" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H256" s="15" t="n">
         <v>98</v>
       </c>
-      <c r="I255" s="19" t="inlineStr">
+      <c r="I256" s="19" t="inlineStr">
         <is>
           <t>あのキャラバンの隊長…</t>
         </is>
       </c>
-      <c r="J255" s="19" t="inlineStr">
+      <c r="J256" s="19" t="inlineStr">
         <is>
           <t>That caravan leader...</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
+      <c r="K256" t="inlineStr">
         <is>
           <t>Aquele líder da caravana...</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H256" s="15" t="n">
+    <row r="257" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H257" s="15" t="n">
         <v>99</v>
       </c>
-      <c r="I256" s="19" t="inlineStr">
+      <c r="I257" s="19" t="inlineStr">
         <is>
           <t>か…かわいい！
 猫のかぶりものをかぶってるわ。
 ねえ、ちょっと寄っていこ？</t>
         </is>
       </c>
-      <c r="J256" s="19" t="inlineStr">
+      <c r="J257" s="19" t="inlineStr">
         <is>
           <t>S...so cute!
 He's wearing a cat costume.
 Hey, let's go check him?</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
+      <c r="K257" t="inlineStr">
         <is>
           <t>Tão fofo!
 Ele está vestindo uma fantasia de gato.
@@ -6667,52 +6691,52 @@
         </is>
       </c>
     </row>
-    <row r="257" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="I257" s="19" t="n"/>
-      <c r="J257" s="19" t="n"/>
-    </row>
     <row r="258" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B258" s="19" t="inlineStr">
+      <c r="I258" s="19" t="n"/>
+      <c r="J258" s="19" t="n"/>
+    </row>
+    <row r="259" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B259" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A259" s="19" t="inlineStr">
+    <row r="260" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A260" s="19" t="inlineStr">
         <is>
           <t>town</t>
         </is>
       </c>
     </row>
-    <row r="260" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H260" s="15" t="n">
+    <row r="261" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H261" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="I260" s="19" t="inlineStr">
+      <c r="I261" s="19" t="inlineStr">
         <is>
           <t>街だ～！
 人の往来で辺りに活気があるわね。</t>
         </is>
       </c>
-      <c r="J260" s="25" t="inlineStr">
+      <c r="J261" s="25" t="inlineStr">
         <is>
           <t>It's a town!
 So lively with all the people bustling around.</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="K261" t="inlineStr">
         <is>
           <t>É uma cidade!
 Tão animada com todas as pessoas se movimentando.</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H261" s="15" t="n">
+    <row r="262" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H262" s="15" t="n">
         <v>101</v>
       </c>
-      <c r="I261" s="19" t="inlineStr">
+      <c r="I262" s="19" t="inlineStr">
         <is>
           <t>アイテムの売買、訓練、交易、賭博、依頼、回復…
 街には色々なサービスが揃ってる。
@@ -6720,7 +6744,7 @@
 ガードに話しかければ、道案内をしてもらえるわ。えへへ。</t>
         </is>
       </c>
-      <c r="J261" s="19" t="inlineStr">
+      <c r="J262" s="19" t="inlineStr">
         <is>
           <t>Buying and selling, training, trading, gambling, quests, healing...
 There are so many services here.
@@ -6728,7 +6752,7 @@
 Just talk to a guard, and they'll guide you. Hehe.</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="K262" t="inlineStr">
         <is>
           <t>Comprar e vender, treinar, negociar, apostar, missões, cura...
 Há tantos serviços aqui.
@@ -6737,25 +6761,25 @@
         </is>
       </c>
     </row>
-    <row r="262" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H262" s="15" t="n">
+    <row r="263" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H263" s="15" t="n">
         <v>102</v>
       </c>
-      <c r="I262" s="19" t="inlineStr">
+      <c r="I263" s="19" t="inlineStr">
         <is>
           <t>当然だけど、ノースティリスにある街は
 街ごとに発展度も違えば、売っている物も
 受けられるサービスも、訓練できるスキルも違うの。</t>
         </is>
       </c>
-      <c r="J262" s="19" t="inlineStr">
+      <c r="J263" s="19" t="inlineStr">
         <is>
           <t>Of course, every town in North Tyris is different.
 They vary in development, the items they sell,
 the services they offer, and the skills you can train.</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="K263" t="inlineStr">
         <is>
           <t>Claro, cada cidade em North Tyris é diferente.
 Elas variam no desenvolvimento, nos itens que vendem,
@@ -6763,114 +6787,114 @@
         </is>
       </c>
     </row>
-    <row r="263" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H263" s="15" t="n">
+    <row r="264" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H264" s="15" t="n">
         <v>103</v>
       </c>
-      <c r="I263" s="19" t="inlineStr">
+      <c r="I264" s="19" t="inlineStr">
         <is>
           <t>掲示板に掲載される依頼も、街によって傾向が異なるから
 色んな街を巡ってみるのもいいわね。</t>
         </is>
       </c>
-      <c r="J263" s="19" t="inlineStr">
+      <c r="J264" s="19" t="inlineStr">
         <is>
           <t>The quests posted on the bulletin board also differ from one to another,
 so it will be a good idea to explore various towns.</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K264" t="inlineStr">
         <is>
           <t>As missões postadas no quadro de avisos também diferem de uma cidade para outra, então pode ser uma boa ideia explorar várias cidades.</t>
         </is>
       </c>
     </row>
-    <row r="264" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H264" s="15" t="n">
+    <row r="265" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H265" s="15" t="n">
         <v>104</v>
       </c>
-      <c r="I264" s="19" t="inlineStr">
+      <c r="I265" s="19" t="inlineStr">
         <is>
           <t>今はともかく、この街を探索してみましょ？</t>
         </is>
       </c>
-      <c r="J264" s="19" t="inlineStr">
+      <c r="J265" s="19" t="inlineStr">
         <is>
           <t>But, for now, how about we explore this town?</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="K265" t="inlineStr">
         <is>
           <t>Mas, por enquanto, que tal explorarmos essa cidade?</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="I265" s="19" t="n"/>
-      <c r="J265" s="19" t="n"/>
-    </row>
     <row r="266" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B266" s="19" t="inlineStr">
+      <c r="I266" s="19" t="n"/>
+      <c r="J266" s="19" t="n"/>
+    </row>
+    <row r="267" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B267" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B267" s="19" t="n"/>
-    </row>
     <row r="268" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A268" s="19" t="inlineStr">
+      <c r="B268" s="19" t="n"/>
+    </row>
+    <row r="269" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A269" s="19" t="inlineStr">
         <is>
           <t>karma</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H269" s="15" t="n">
-        <v>79</v>
-      </c>
-      <c r="I269" s="19" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J269" s="25" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>...</t>
         </is>
       </c>
     </row>
     <row r="270" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H270" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="I270" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J270" s="25" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H271" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="I270" s="19" t="inlineStr">
+      <c r="I271" s="19" t="inlineStr">
         <is>
           <t>今、悪いことしたでしょ…？</t>
         </is>
       </c>
-      <c r="J270" s="19" t="inlineStr">
+      <c r="J271" s="19" t="inlineStr">
         <is>
           <t>Did you just do something bad...?</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="K271" t="inlineStr">
         <is>
           <t>Você acabou de fazer algo ruim?</t>
         </is>
       </c>
     </row>
-    <row r="271" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H271" s="15" t="n">
+    <row r="272" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H272" s="15" t="n">
         <v>81</v>
       </c>
-      <c r="I271" s="19" t="inlineStr">
+      <c r="I272" s="19" t="inlineStr">
         <is>
           <t>ええ…キミのカルマが下がるのを感じたのよ。
 この世界では、悪いことをするとカルマが下がって
@@ -6878,7 +6902,7 @@
 …犯罪者になると、生きていくのが大変よ。</t>
         </is>
       </c>
-      <c r="J271" s="19" t="inlineStr">
+      <c r="J272" s="19" t="inlineStr">
         <is>
           <t>Yes... I felt your karma drop.
 In this world, your karma decreases if you do bad things,
@@ -6886,7 +6910,7 @@
 ... Becoming a criminal makes life very difficult.</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="K272" t="inlineStr">
         <is>
           <t>Sim... Eu senti seu carma cair.
 Neste mundo, seu carma diminui se você fizer coisas ruins,
@@ -6895,34 +6919,34 @@
         </is>
       </c>
     </row>
-    <row r="272" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H272" s="15" t="n">
+    <row r="273" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H273" s="15" t="n">
         <v>82</v>
       </c>
-      <c r="I272" s="19" t="inlineStr">
+      <c r="I273" s="19" t="inlineStr">
         <is>
           <t>依頼をこなしたり、落とし物を届けたり
 日ごろから善い行いを心がけて、カルマを高めていってね。</t>
         </is>
       </c>
-      <c r="J272" s="19" t="inlineStr">
+      <c r="J273" s="19" t="inlineStr">
         <is>
           <t>Complete quests, return lost items,
 and always strive to do good deeds to increase your karma.</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="K273" t="inlineStr">
         <is>
           <t>Complete missões, devolva itens perdidos,
 e sempre se esforce para fazer boas ações para aumentar seu carma.</t>
         </is>
       </c>
     </row>
-    <row r="273" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H273" s="15" t="n">
+    <row r="274" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H274" s="15" t="n">
         <v>83</v>
       </c>
-      <c r="I273" s="19" t="inlineStr">
+      <c r="I274" s="19" t="inlineStr">
         <is>
           <t>…ちなみに
 この世界で最も重い罪は税金の滞納よ。
@@ -6930,14 +6954,14 @@
 命を狙われるようになるわ。</t>
         </is>
       </c>
-      <c r="J273" s="19" t="inlineStr">
+      <c r="J274" s="19" t="inlineStr">
         <is>
           <t>...By the way, the most serious crime in this world is tax evasion.
 If you don’t pay your taxes for four months,
 you’ll be immediately wanted, and your life will be in danger.</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K274" t="inlineStr">
         <is>
           <t>... A propósito, o crime mais grave do mundo é a sonegação de impostos.
 Se você não pagar seus impostos por quatro meses,
@@ -6945,129 +6969,129 @@
         </is>
       </c>
     </row>
-    <row r="274" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H274" s="15" t="n">
+    <row r="275" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H275" s="15" t="n">
         <v>84</v>
       </c>
-      <c r="I274" s="19" t="inlineStr">
+      <c r="I275" s="19" t="inlineStr">
         <is>
           <t>くれぐれも気を付けて…</t>
         </is>
       </c>
-      <c r="J274" s="19" t="inlineStr">
+      <c r="J275" s="19" t="inlineStr">
         <is>
           <t>So...be careful, okay?</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="K275" t="inlineStr">
         <is>
           <t>Portanto... Tome cuidado, ok?</t>
         </is>
       </c>
     </row>
-    <row r="275" ht="12.8" customHeight="1" s="17">
-      <c r="I275" s="19" t="n"/>
-      <c r="J275" s="19" t="n"/>
-      <c r="K275" s="15" t="n"/>
-    </row>
     <row r="276" ht="12.8" customHeight="1" s="17">
-      <c r="B276" s="19" t="inlineStr">
+      <c r="I276" s="19" t="n"/>
+      <c r="J276" s="19" t="n"/>
+      <c r="K276" s="15" t="n"/>
+    </row>
+    <row r="277" ht="12.8" customHeight="1" s="17">
+      <c r="B277" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K276" s="15" t="n"/>
-    </row>
-    <row r="277" ht="12.8" customHeight="1" s="17">
-      <c r="B277" s="19" t="n"/>
       <c r="K277" s="15" t="n"/>
     </row>
     <row r="278" ht="12.8" customHeight="1" s="17">
-      <c r="A278" s="19" t="inlineStr">
+      <c r="B278" s="19" t="n"/>
+      <c r="K278" s="15" t="n"/>
+    </row>
+    <row r="279" ht="12.8" customHeight="1" s="17">
+      <c r="A279" s="19" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="K278" s="15" t="n"/>
-    </row>
-    <row r="279" ht="12.8" customHeight="1" s="17">
-      <c r="H279" s="15" t="n">
+      <c r="K279" s="15" t="n"/>
+    </row>
+    <row r="280" ht="12.8" customHeight="1" s="17">
+      <c r="H280" s="15" t="n">
         <v>85</v>
       </c>
-      <c r="I279" s="19" t="inlineStr">
+      <c r="I280" s="19" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="J279" s="25" t="inlineStr">
+      <c r="J280" s="25" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="K279" s="15" t="inlineStr">
+      <c r="K280" s="15" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="22.35" customHeight="1" s="17">
-      <c r="H280" s="15" t="n">
+    <row r="281" ht="22.35" customHeight="1" s="17">
+      <c r="H281" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="I280" s="19" t="inlineStr">
+      <c r="I281" s="19" t="inlineStr">
         <is>
           <t>イヤ…！
 近づかないで、変態！</t>
         </is>
       </c>
-      <c r="J280" s="19" t="inlineStr">
+      <c r="J281" s="19" t="inlineStr">
         <is>
           <t>No...!
 Stay away from me, you pervert!</t>
         </is>
       </c>
-      <c r="K280" s="15" t="inlineStr">
+      <c r="K281" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Não...!  _x000D_
 Fique longe de mim, seu pervertido!  </t>
         </is>
       </c>
     </row>
-    <row r="281" ht="22.35" customHeight="1" s="17">
-      <c r="H281" s="15" t="n">
+    <row r="282" ht="22.35" customHeight="1" s="17">
+      <c r="H282" s="15" t="n">
         <v>87</v>
       </c>
-      <c r="I281" s="19" t="inlineStr">
+      <c r="I282" s="19" t="inlineStr">
         <is>
           <t>犯罪者に身を堕としてしまうなんて、
 キミのことを見損なったわ。</t>
         </is>
       </c>
-      <c r="J281" s="19" t="inlineStr">
+      <c r="J282" s="19" t="inlineStr">
         <is>
           <t>I can't believe you've become a criminal.
 I'm really disappointed in you.</t>
         </is>
       </c>
-      <c r="K281" s="15" t="inlineStr">
+      <c r="K282" s="15" t="inlineStr">
         <is>
           <t>Não acredito que você tenha se tornado um criminoso.
 Estou muito decepcionada com você.</t>
         </is>
       </c>
     </row>
-    <row r="282" ht="43.25" customHeight="1" s="17">
-      <c r="H282" s="15" t="n">
+    <row r="283" ht="43.25" customHeight="1" s="17">
+      <c r="H283" s="15" t="n">
         <v>88</v>
       </c>
-      <c r="I282" s="19" t="inlineStr">
+      <c r="I283" s="19" t="inlineStr">
         <is>
           <t>…そう、カルマが0を下回ると、キミは指名手配されてしまう。
 ガードから追いかけられ、商人との取引も断られ、妹達から白い目で見られ
 社会の敵として、一生みじめに暮らすのよ！</t>
         </is>
       </c>
-      <c r="J282" s="19" t="inlineStr">
+      <c r="J283" s="19" t="inlineStr">
         <is>
           <t>…That's right, if your karma drops below zero, you'll be wanted.
 Guards will come chasing you, merchants will refuse to trade with you,
@@ -7075,7 +7099,7 @@
 You'll live a miserable life as an enemy of society!</t>
         </is>
       </c>
-      <c r="K282" s="15" t="inlineStr">
+      <c r="K283" s="15" t="inlineStr">
         <is>
           <t>... É isso mesmo, se o seu carma cair abaixo de zero, você será procurado.
 Os guardas virão atrás de você, os comerciantes se recusarão a negociar com você,
@@ -7084,25 +7108,25 @@
         </is>
       </c>
     </row>
-    <row r="283" ht="32.8" customHeight="1" s="17">
-      <c r="H283" s="15" t="n">
+    <row r="284" ht="32.8" customHeight="1" s="17">
+      <c r="H284" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="I283" s="19" t="inlineStr">
+      <c r="I284" s="19" t="inlineStr">
         <is>
           <t>はぁ…大丈夫、キミにもまだ、更生の道は残されているわ。
 カルマがマイナスの時、カルマは少しずつ上昇していくの。
 悪事を止めて、大人しく待っていれば、いつかはほとぼりも冷める…</t>
         </is>
       </c>
-      <c r="J283" s="19" t="inlineStr">
+      <c r="J284" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Sigh... It's okay, there's still a path to redemption for you.
 When your karma is negative, it will slowly increase over time.
 If you stop committing crimes and patiently wait, things will eventually calm down. </t>
         </is>
       </c>
-      <c r="K283" s="15" t="inlineStr">
+      <c r="K284" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">*suspiro* - Tudo bem, ainda há um caminho para a redenção.  
 Quando seu carma for negativo, ele aumentará lentamente com o tempo.  
@@ -7110,126 +7134,126 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="22.35" customHeight="1" s="17">
-      <c r="H284" s="15" t="n">
+    <row r="285" ht="22.35" customHeight="1" s="17">
+      <c r="H285" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="I284" s="19" t="inlineStr">
+      <c r="I285" s="19" t="inlineStr">
         <is>
           <t>法律が存在しない、ならず者たちの街ダルフィなら
 税金を納めることもできるし、商人も取引をしてくれるわ。</t>
         </is>
       </c>
-      <c r="J284" s="19" t="inlineStr">
+      <c r="J285" s="19" t="inlineStr">
         <is>
           <t>In the rogue town of Derphy, where there are no laws,
 you can pay your taxes, and merchants will still trade with you.</t>
         </is>
       </c>
-      <c r="K284" s="15" t="inlineStr">
+      <c r="K285" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Na cidade dos foras da lei, Derphy, onde não há leis,  _x000D_
 você pode pagar seus impostos, e os mercadores ainda negociarão com você.  </t>
         </is>
       </c>
     </row>
-    <row r="285" ht="22.35" customHeight="1" s="17">
-      <c r="H285" s="15" t="n">
+    <row r="286" ht="22.35" customHeight="1" s="17">
+      <c r="H286" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="I285" s="19" t="inlineStr">
+      <c r="I286" s="19" t="inlineStr">
         <is>
           <t>大丈夫、キミのこと信じてるから
 しっかり罪を償って戻ってきてね。</t>
         </is>
       </c>
-      <c r="J285" s="19" t="inlineStr">
+      <c r="J286" s="19" t="inlineStr">
         <is>
           <t>Don't worry, I believe in you.
 Make sure you atone for your sins and come back.</t>
         </is>
       </c>
-      <c r="K285" s="15" t="inlineStr">
+      <c r="K286" s="15" t="inlineStr">
         <is>
           <t>Não se preocupe, eu acredito em você.
 Certifique-se de arrepender-se de seus pecados e voltar.</t>
         </is>
       </c>
     </row>
-    <row r="286" ht="12.8" customHeight="1" s="17">
-      <c r="H286" s="15" t="n">
+    <row r="287" ht="12.8" customHeight="1" s="17">
+      <c r="H287" s="15" t="n">
         <v>92</v>
       </c>
-      <c r="I286" s="19" t="inlineStr">
+      <c r="I287" s="19" t="inlineStr">
         <is>
           <t>それでは…</t>
         </is>
       </c>
-      <c r="J286" s="19" t="inlineStr">
+      <c r="J287" s="19" t="inlineStr">
         <is>
           <t>Until then...</t>
         </is>
       </c>
-      <c r="K286" s="15" t="inlineStr">
+      <c r="K287" s="15" t="inlineStr">
         <is>
           <t>Até lá...</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="12.8" customHeight="1" s="17">
-      <c r="B287" s="19" t="inlineStr">
+    <row r="288" ht="12.8" customHeight="1" s="17">
+      <c r="B288" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K287" s="15" t="n"/>
-    </row>
-    <row r="289" ht="12.8" customHeight="1" s="17">
-      <c r="A289" s="19" t="inlineStr">
+      <c r="K288" s="15" t="n"/>
+    </row>
+    <row r="290" ht="12.8" customHeight="1" s="17">
+      <c r="A290" s="19" t="inlineStr">
         <is>
           <t>ether</t>
         </is>
       </c>
-      <c r="K289" s="15" t="n"/>
-    </row>
-    <row r="290" ht="12.8" customHeight="1" s="17">
-      <c r="H290" s="15" t="n">
+      <c r="K290" s="15" t="n"/>
+    </row>
+    <row r="291" ht="12.8" customHeight="1" s="17">
+      <c r="H291" s="15" t="n">
         <v>74</v>
       </c>
-      <c r="I290" s="19" t="inlineStr">
+      <c r="I291" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">キミもとうとう病におかされてしまったのね… </t>
         </is>
       </c>
-      <c r="J290" s="25" t="inlineStr">
+      <c r="J291" s="25" t="inlineStr">
         <is>
           <t>So, you've finally been afflicted by the illness...</t>
         </is>
       </c>
-      <c r="K290" s="15" t="inlineStr">
+      <c r="K291" s="15" t="inlineStr">
         <is>
           <t>Você finalmente ficou doente...</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="32.8" customHeight="1" s="17">
-      <c r="H291" s="15" t="n">
+    <row r="292" ht="32.8" customHeight="1" s="17">
+      <c r="H292" s="15" t="n">
         <v>75</v>
       </c>
-      <c r="I291" s="19" t="inlineStr">
+      <c r="I292" s="19" t="inlineStr">
         <is>
           <t>驚かないでいいの。
 何もしないでも、エーテルの侵食は時間と供に緩やかに進んでいくのよ。</t>
         </is>
       </c>
-      <c r="J291" s="19" t="inlineStr">
+      <c r="J292" s="19" t="inlineStr">
         <is>
           <t>Don't be surprised.
 Even if you do nothing, the ether's encroachment
 will gradually progress over time.</t>
         </is>
       </c>
-      <c r="K291" s="15" t="inlineStr">
+      <c r="K292" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Não fique surpreso.  
 Mesmo que você não faça nada, a invasão do éter  
@@ -7237,18 +7261,18 @@
         </is>
       </c>
     </row>
-    <row r="292" ht="43.25" customHeight="1" s="17">
-      <c r="H292" s="15" t="n">
+    <row r="293" ht="43.25" customHeight="1" s="17">
+      <c r="H293" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="I292" s="19" t="inlineStr">
+      <c r="I293" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">キミの症状はまだまだ無視してかまわない程度だけど
 病気を放っておくと、症状はどんどん悪化して最後には死んじゃうの。
 …病を遅らせる何らかの方法を見つけなくてはね。 </t>
         </is>
       </c>
-      <c r="J292" s="19" t="inlineStr">
+      <c r="J293" s="19" t="inlineStr">
         <is>
           <t>Your symptoms are still minor and can be ignored for now,
 but if you leave the illness untreated,
@@ -7256,7 +7280,7 @@
 ...We need to find some way to slow down the disease.</t>
         </is>
       </c>
-      <c r="K292" s="15" t="inlineStr">
+      <c r="K293" s="15" t="inlineStr">
         <is>
           <t>Seus sintomas ainda são leves e podem ser ignorados por enquanto,
 mas se você deixar a doença sem tratamento,
@@ -7265,308 +7289,308 @@
         </is>
       </c>
     </row>
-    <row r="293" ht="22.35" customHeight="1" s="17">
-      <c r="H293" s="15" t="n">
+    <row r="294" ht="22.35" customHeight="1" s="17">
+      <c r="H294" s="15" t="n">
         <v>77</v>
       </c>
-      <c r="I293" s="19" t="inlineStr">
+      <c r="I294" s="19" t="inlineStr">
         <is>
           <t>えへへ、そんなに心配しなくても大丈夫よ。
 時間はたっぷりあるんだから、何か解決策を見つけましょ？</t>
         </is>
       </c>
-      <c r="J293" s="19" t="inlineStr">
+      <c r="J294" s="19" t="inlineStr">
         <is>
           <t>Hehe, don't make that serious face.
 We have plenty of time, so let's find a solution, okay?</t>
         </is>
       </c>
-      <c r="K293" s="15" t="inlineStr">
+      <c r="K294" s="15" t="inlineStr">
         <is>
           <t>Heh heh, não se preocupe tanto.
 Temos muito tempo para encontrar uma solução.</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="32.8" customHeight="1" s="17">
-      <c r="H294" s="15" t="n">
+    <row r="295" ht="32.8" customHeight="1" s="17">
+      <c r="H295" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="I294" s="19" t="inlineStr">
+      <c r="I295" s="19" t="inlineStr">
         <is>
           <t>そういえば、ノイエル南にある雪原の工房で
 奇妙なアイテムを収集している丘の民がいたわね。
 彼ならもしかしたら…</t>
         </is>
       </c>
-      <c r="J294" s="19" t="inlineStr">
+      <c r="J295" s="19" t="inlineStr">
         <is>
           <t>Come to think of it...
 There was a hillfolk in a workshop south of Noyel
 who was collecting strange items. Maybe he could...</t>
         </is>
       </c>
-      <c r="K294" s="15" t="inlineStr">
+      <c r="K295" s="15" t="inlineStr">
         <is>
           <t>Pensando bem...
 Havia um habitante da colina em uma oficina ao sul de Noyel
 que estava coletando itens estranhos. Talvez ele pudesse…</t>
         </is>
       </c>
-    </row>
-    <row r="295" ht="12.8" customHeight="1" s="17">
-      <c r="I295" s="19" t="n"/>
-      <c r="J295" s="19" t="n"/>
-      <c r="K295" s="15" t="n"/>
     </row>
     <row r="296" ht="12.8" customHeight="1" s="17">
       <c r="I296" s="19" t="n"/>
       <c r="J296" s="19" t="n"/>
       <c r="K296" s="15" t="n"/>
     </row>
-    <row r="297" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B297" s="19" t="inlineStr">
+    <row r="297" ht="12.8" customHeight="1" s="17">
+      <c r="I297" s="19" t="n"/>
+      <c r="J297" s="19" t="n"/>
+      <c r="K297" s="15" t="n"/>
+    </row>
+    <row r="298" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B298" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="299" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A299" s="19" t="inlineStr">
+    <row r="299" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="300" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A300" s="19" t="inlineStr">
         <is>
           <t>faith</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H300" s="15" t="n">
+    <row r="301" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H301" s="15" t="n">
         <v>66</v>
       </c>
-      <c r="I300" s="19" t="inlineStr">
+      <c r="I301" s="19" t="inlineStr">
         <is>
           <t>え、神を信仰した…？
 うふふ…</t>
         </is>
       </c>
-      <c r="J300" s="25" t="inlineStr">
+      <c r="J301" s="25" t="inlineStr">
         <is>
           <t>Oh, did you start worshipping a god?
 Hehe...</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
+      <c r="K301" t="inlineStr">
         <is>
           <t>O quê, você acreditava em Deus...?
 Uh-huh…</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H301" s="15" t="n">
+    <row r="302" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H302" s="15" t="n">
         <v>67</v>
       </c>
-      <c r="I301" s="19" t="inlineStr">
+      <c r="I302" s="19" t="inlineStr">
         <is>
           <t>ねえ、教えてよ！誰を信仰したの？
 キミの初信仰の相手は誰？ふふふ。</t>
         </is>
       </c>
-      <c r="J301" s="19" t="inlineStr">
+      <c r="J302" s="19" t="inlineStr">
         <is>
           <t>Come on, tell me! Who did you choose to worship?
 Who's your first god? Hehe.</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
+      <c r="K302" t="inlineStr">
         <is>
           <t>Vamos lá, conte-me! Quem você escolheu para adorar?
 Quem é seu primeiro Deus? Hehe.</t>
         </is>
       </c>
     </row>
-    <row r="302" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H302" s="15" t="n">
+    <row r="303" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H303" s="15" t="n">
         <v>68</v>
       </c>
-      <c r="I302" s="19" t="inlineStr">
+      <c r="I303" s="19" t="inlineStr">
         <is>
           <t>…#god。</t>
         </is>
       </c>
-      <c r="J302" s="19" t="inlineStr">
+      <c r="J303" s="19" t="inlineStr">
         <is>
           <t>...#god.</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="K303" t="inlineStr">
         <is>
           <t xml:space="preserve">...#god.  </t>
         </is>
       </c>
     </row>
-    <row r="303" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H303" s="15" t="n">
+    <row r="304" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H304" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="I303" s="19" t="inlineStr">
+      <c r="I304" s="19" t="inlineStr">
         <is>
           <t>キミって、やっぱりそういう趣味をしてたのね。
 ふ～ん…</t>
         </is>
       </c>
-      <c r="J303" s="19" t="inlineStr">
+      <c r="J304" s="19" t="inlineStr">
         <is>
           <t>I see, so that's your thing, huh?
 Huh...</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
+      <c r="K304" t="inlineStr">
         <is>
           <t xml:space="preserve">Entendo, então é isso que te interessa, hein?  
 Huh...  </t>
         </is>
       </c>
     </row>
-    <row r="304" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H304" s="15" t="n">
+    <row r="305" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H305" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="I304" s="19" t="inlineStr">
+      <c r="I305" s="19" t="inlineStr">
         <is>
           <t>神を信仰すると、信仰の深さによって様々な恩恵が与えられるわ。
 信仰は、捧げものをしたり、時間が経つことで深まっていくの。</t>
         </is>
       </c>
-      <c r="J304" s="19" t="inlineStr">
+      <c r="J305" s="19" t="inlineStr">
         <is>
           <t>When you worship a god, you'll receive various blessings
 depending on the depth of your faith.
 Your faith deepens through offerings and the passage of time.</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
+      <c r="K305" t="inlineStr">
         <is>
           <t>Ao adorar um Deus, você receberá várias bênçãos, dependendo da profundidade de sua fé.
 Sua fé se aprofunda com as oferendas e a passagem do tempo.</t>
         </is>
       </c>
     </row>
-    <row r="305" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H305" s="15" t="n">
+    <row r="306" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H306" s="15" t="n">
         <v>71</v>
       </c>
-      <c r="I305" s="19" t="inlineStr">
+      <c r="I306" s="19" t="inlineStr">
         <is>
           <t>また、一日に一度だけ、神に「祈る」アビリティを使うこともできる。
 体力が回復したり、神様の機嫌にもよるけど、贈り物を賜ることもあるわ。</t>
         </is>
       </c>
-      <c r="J305" s="19" t="inlineStr">
+      <c r="J306" s="19" t="inlineStr">
         <is>
           <t>Once a day, you can use the "Pray" ability to your god.
 It can restore your health, and depending on the god's mood,
 you might receive a gift.</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="K306" t="inlineStr">
         <is>
           <t xml:space="preserve">Uma vez por dia, você pode usar a habilidade "Orar" para seu Deus.  
 Ela pode restaurar sua saúde e, dependendo do humor do Deus, você pode receber um presente.  </t>
         </is>
       </c>
     </row>
-    <row r="306" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H306" s="15" t="n">
+    <row r="307" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H307" s="15" t="n">
         <v>72</v>
       </c>
-      <c r="I306" s="19" t="inlineStr">
+      <c r="I307" s="19" t="inlineStr">
         <is>
           <t>「祈る」ことで、キミの信仰スキルも鍛えられるから
 一日に一度は祈ってみるといいわね。</t>
         </is>
       </c>
-      <c r="J306" s="19" t="inlineStr">
+      <c r="J307" s="19" t="inlineStr">
         <is>
           <t>Praying also helps you develop your faith skill,
 so try to pray at least once a day.</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
+      <c r="K307" t="inlineStr">
         <is>
           <t>A oração também o ajuda a desenvolver sua habilidade de fé,
 portanto, tente orar pelo menos uma vez por dia.</t>
         </is>
       </c>
     </row>
-    <row r="307" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H307" s="15" t="n">
+    <row r="308" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H308" s="15" t="n">
         <v>73</v>
       </c>
-      <c r="I307" s="19" t="inlineStr">
+      <c r="I308" s="19" t="inlineStr">
         <is>
           <t>じゃあ、#godを怒らせないように気を付けてね。</t>
         </is>
       </c>
-      <c r="J307" s="19" t="inlineStr">
+      <c r="J308" s="19" t="inlineStr">
         <is>
           <t>Well, that's it for now.
 Just be careful not to anger #god.</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
+      <c r="K308" t="inlineStr">
         <is>
           <t>Bem, por enquanto é isso.
 Apenas tome cuidado para não irritar #god.</t>
         </is>
       </c>
     </row>
-    <row r="308" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B308" s="19" t="inlineStr">
+    <row r="309" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B309" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="309" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A309" s="19" t="inlineStr">
+    <row r="310" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A310" s="19" t="inlineStr">
         <is>
           <t>healer</t>
         </is>
       </c>
     </row>
-    <row r="310" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H310" s="15" t="n">
+    <row r="311" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H311" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="I310" s="19" t="inlineStr">
+      <c r="I311" s="19" t="inlineStr">
         <is>
           <t>あ…キミ、弱くなっちゃったの？</t>
         </is>
       </c>
-      <c r="J310" s="25" t="inlineStr">
+      <c r="J311" s="25" t="inlineStr">
         <is>
           <t>Oh... Have you become weaker?</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="K311" t="inlineStr">
         <is>
           <t>Oh... Você ficou mais fraco?</t>
         </is>
       </c>
     </row>
-    <row r="311" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H311" s="15" t="n">
+    <row r="312" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H312" s="15" t="n">
         <v>61</v>
       </c>
-      <c r="I311" s="19" t="inlineStr">
+      <c r="I312" s="19" t="inlineStr">
         <is>
           <t>え？どういうことって…
 ちょっと自分の主能力を確認してみてね？
 普段より能力が低下してるでしょ？</t>
         </is>
       </c>
-      <c r="J311" s="19" t="inlineStr">
+      <c r="J312" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">
 What? What do I mean by that... 
@@ -7574,7 +7598,7 @@
 You'll notice they're lower than usual, right?</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
+      <c r="K312" t="inlineStr">
         <is>
           <t xml:space="preserve">  
 O quê? O que quero dizer com isso...  
@@ -7583,92 +7607,92 @@
         </is>
       </c>
     </row>
-    <row r="312" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H312" s="15" t="n">
+    <row r="313" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H313" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="I312" s="19" t="inlineStr">
+      <c r="I313" s="19" t="inlineStr">
         <is>
           <t>一部の敵は、キミの能力を弱体化させる攻撃をしてくるの。
 弱体は、最初は問題ないけど、積み重なってくると厄介よ。</t>
         </is>
       </c>
-      <c r="J312" s="19" t="inlineStr">
+      <c r="J313" s="19" t="inlineStr">
         <is>
           <t>Some enemies can weaken your attributes with their attacks.
 At first, it's not a big deal, but if it piles up, it can become troublesome.</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
+      <c r="K313" t="inlineStr">
         <is>
           <t>Alguns inimigos podem enfraquecer seus atributos com os ataques deles.
 No início, isso não é um grande problema, mas se acumular, pode se tornar incômodo.</t>
         </is>
       </c>
     </row>
-    <row r="313" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H313" s="15" t="n">
+    <row r="314" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H314" s="15" t="n">
         <v>63</v>
       </c>
-      <c r="I313" s="19" t="inlineStr">
+      <c r="I314" s="19" t="inlineStr">
         <is>
           <t>もし肉体復活か精神復活のポーションを持ってるなら
 それを飲めば弱体を回復することができるわ。</t>
         </is>
       </c>
-      <c r="J313" s="19" t="inlineStr">
+      <c r="J314" s="19" t="inlineStr">
         <is>
           <t>If you have a Potion of Restore Body or a Potion of Restore Mind,
 drinking one of those can restore your weakened attributes.</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
+      <c r="K314" t="inlineStr">
         <is>
           <t>Se você tiver uma Potion of Restore Body (Poção de Restauração do Corpo) ou uma Potion of Restore Mind (Poção de Restauração da Mente), beber uma delas pode restaurar seus atributos enfraquecidos.</t>
         </is>
       </c>
     </row>
-    <row r="314" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H314" s="15" t="n">
+    <row r="315" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H315" s="15" t="n">
         <v>64</v>
       </c>
-      <c r="I314" s="19" t="inlineStr">
+      <c r="I315" s="19" t="inlineStr">
         <is>
           <t>回復の手段がない時は、街にいる癒し手に頼めば
 治療費と引き換えに治してもらえるけど…</t>
         </is>
       </c>
-      <c r="J314" s="19" t="inlineStr">
+      <c r="J315" s="19" t="inlineStr">
         <is>
           <t>If you don't have a way to recover, you can ask a healer in town.
 It will cost you some money, but they can treat you...</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
+      <c r="K315" t="inlineStr">
         <is>
           <t>Se você não tiver uma maneira de se recuperar, pode pedir a um curandeiro da cidade.
 Isso lhe custará algum dinheiro, mas ele poderá tratá-lo…</t>
         </is>
       </c>
     </row>
-    <row r="315" ht="32.8" customHeight="1" s="17">
-      <c r="H315" s="15" t="n">
+    <row r="316" ht="32.8" customHeight="1" s="17">
+      <c r="H316" s="15" t="n">
         <v>65</v>
       </c>
-      <c r="I315" s="19" t="inlineStr">
+      <c r="I316" s="19" t="inlineStr">
         <is>
           <t>まあ、攻撃を受けないのが一番ね。
 近づくと厄介な敵には、遠隔から攻撃するといいわ。</t>
         </is>
       </c>
-      <c r="J315" s="19" t="inlineStr">
+      <c r="J316" s="19" t="inlineStr">
         <is>
           <t>Well, it's best not to get hit in the first place.
 For enemies that are troublesome up close,
 it's always better to attack them from a distance.</t>
         </is>
       </c>
-      <c r="K315" s="15" t="inlineStr">
+      <c r="K316" s="15" t="inlineStr">
         <is>
           <t>Bem, é melhor não ser atingido em primeiro lugar.
 Para inimigos que são problemáticos de perto,
@@ -7676,154 +7700,154 @@
         </is>
       </c>
     </row>
-    <row r="316" ht="12.8" customHeight="1" s="17">
-      <c r="B316" s="19" t="inlineStr">
+    <row r="317" ht="12.8" customHeight="1" s="17">
+      <c r="B317" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K316" s="15" t="n"/>
-    </row>
-    <row r="317" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+      <c r="K317" s="15" t="n"/>
+    </row>
     <row r="318" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="319" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A319" s="19" t="inlineStr">
+    <row r="319" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="320" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A320" s="19" t="inlineStr">
         <is>
           <t>fame</t>
         </is>
       </c>
     </row>
-    <row r="320" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H320" s="15" t="n">
+    <row r="321" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H321" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="I320" s="19" t="inlineStr">
+      <c r="I321" s="19" t="inlineStr">
         <is>
           <t>わあ、名声を獲得したのね！
 おめでと～！</t>
         </is>
       </c>
-      <c r="J320" s="25" t="inlineStr">
+      <c r="J321" s="25" t="inlineStr">
         <is>
           <t>Wow, you’ve gained fame!
 Congratulations!</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
+      <c r="K321" t="inlineStr">
         <is>
           <t xml:space="preserve">Uau, você ganhou fama!  _x000D_
 Parabéns!  </t>
         </is>
       </c>
     </row>
-    <row r="321" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H321" s="15" t="n">
+    <row r="322" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H322" s="15" t="n">
         <v>54</v>
       </c>
-      <c r="I321" s="19" t="inlineStr">
+      <c r="I322" s="19" t="inlineStr">
         <is>
           <t>名声は、依頼を達成したり
 ネフィアを踏破することで獲得できるわ。</t>
         </is>
       </c>
-      <c r="J321" s="25" t="inlineStr">
+      <c r="J322" s="25" t="inlineStr">
         <is>
           <t>You can earn fame by completing quests
 and exploring Nefia.</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
+      <c r="K322" t="inlineStr">
         <is>
           <t xml:space="preserve">Você pode ganhar fama completando missões  _x000D_
 e explorando Nefia.  </t>
         </is>
       </c>
     </row>
-    <row r="322" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H322" s="15" t="n">
+    <row r="323" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H323" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="I322" s="19" t="inlineStr">
+      <c r="I323" s="19" t="inlineStr">
         <is>
           <t>名声が上がると、より難易度の高い依頼を頼まれたり
 危険度の高いネフィアが出現するようになるの。</t>
         </is>
       </c>
-      <c r="J322" s="25" t="inlineStr">
+      <c r="J323" s="25" t="inlineStr">
         <is>
           <t>As your fame increases, you’ll be asked to take on more challenging quests,
 and more dangerous Nefia will appear.</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
+      <c r="K323" t="inlineStr">
         <is>
           <t>À medida que sua fama aumenta, você será solicitado a participar de missões mais desafiadoras,
 e a Nefia, mais perigosa, aparecerá.</t>
         </is>
       </c>
     </row>
-    <row r="323" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H323" s="15" t="n">
+    <row r="324" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H324" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="I323" s="19" t="inlineStr">
+      <c r="I324" s="19" t="inlineStr">
         <is>
           <t>いっぱい名声を稼いで
 早く立派な冒険者になってね！</t>
         </is>
       </c>
-      <c r="J323" s="25" t="inlineStr">
+      <c r="J324" s="25" t="inlineStr">
         <is>
           <t>Earn lots of fame and
 become a renowned adventurer soon!</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
+      <c r="K324" t="inlineStr">
         <is>
           <t>Ganhe muita fama e 
 torne-se rapidamente um grande aventureiro!</t>
         </is>
       </c>
     </row>
-    <row r="324" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H324" s="15" t="n">
+    <row r="325" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H325" s="15" t="n">
         <v>57</v>
       </c>
-      <c r="I324" s="19" t="inlineStr">
+      <c r="I325" s="19" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="J324" s="19" t="inlineStr">
+      <c r="J325" s="19" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
+      <c r="K325" t="inlineStr">
         <is>
           <t xml:space="preserve">...  </t>
         </is>
       </c>
     </row>
-    <row r="325" ht="35.05" customFormat="1" customHeight="1" s="15">
-      <c r="H325" s="15" t="n">
+    <row r="326" ht="35.05" customFormat="1" customHeight="1" s="15">
+      <c r="H326" s="15" t="n">
         <v>58</v>
       </c>
-      <c r="I325" s="19" t="inlineStr">
+      <c r="I326" s="19" t="inlineStr">
         <is>
           <t>ちなみに…
 もし名声が高すぎて冒険がきつくなったら
 街の情報屋に名声を売るという手段もあるわ…</t>
         </is>
       </c>
-      <c r="J325" s="25" t="inlineStr">
+      <c r="J326" s="25" t="inlineStr">
         <is>
           <t>By the way...
 if your fame gets too high and the adventures become too tough,
 you can sell your fame to the town’s informant...</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="K326" t="inlineStr">
         <is>
           <t xml:space="preserve">A propósito...  _x000D_
 se sua fama ficar muito alta e as aventuras se tornarem difíceis demais,  _x000D_
@@ -7831,129 +7855,129 @@
         </is>
       </c>
     </row>
-    <row r="326" ht="12.8" customHeight="1" s="17">
-      <c r="H326" s="15" t="n">
+    <row r="327" ht="12.8" customHeight="1" s="17">
+      <c r="H327" s="15" t="n">
         <v>59</v>
       </c>
-      <c r="I326" s="19" t="inlineStr">
+      <c r="I327" s="19" t="inlineStr">
         <is>
           <t>それでは…</t>
         </is>
       </c>
-      <c r="J326" s="25" t="inlineStr">
+      <c r="J327" s="25" t="inlineStr">
         <is>
           <t>Well then...</t>
         </is>
       </c>
-      <c r="K326" s="15" t="inlineStr">
+      <c r="K327" s="15" t="inlineStr">
         <is>
           <t>Então, bem…</t>
         </is>
       </c>
     </row>
-    <row r="327" ht="12.8" customHeight="1" s="17">
-      <c r="B327" s="19" t="inlineStr">
+    <row r="328" ht="12.8" customHeight="1" s="17">
+      <c r="B328" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K327" s="15" t="n"/>
-    </row>
-    <row r="329" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+      <c r="K328" s="15" t="n"/>
+    </row>
     <row r="330" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="331" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A331" s="19" t="inlineStr">
+    <row r="331" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="332" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A332" s="19" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
     </row>
-    <row r="332" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H332" s="15" t="n">
+    <row r="333" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H333" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="I332" s="19" t="inlineStr">
+      <c r="I333" s="19" t="inlineStr">
         <is>
           <t>疲れた顔してるけど大丈夫…？</t>
         </is>
       </c>
-      <c r="J332" s="25" t="inlineStr">
+      <c r="J333" s="25" t="inlineStr">
         <is>
           <t>You look tired, are you okay?</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
+      <c r="K333" t="inlineStr">
         <is>
           <t>Você parece cansado. Está bem?</t>
         </is>
       </c>
     </row>
-    <row r="333" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H333" s="15" t="n">
+    <row r="334" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H334" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="I333" s="19" t="inlineStr">
+      <c r="I334" s="19" t="inlineStr">
         <is>
           <t>疲れをとるには、ふかふかのベッドで
 ぐっすり眠るのが一番。</t>
         </is>
       </c>
-      <c r="J333" s="19" t="inlineStr">
+      <c r="J334" s="19" t="inlineStr">
         <is>
           <t>The best way to recover from fatigue is
 to get a good night's sleep in a comfy bed.</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
+      <c r="K334" t="inlineStr">
         <is>
           <t>A melhor maneira de se recuperar da fadiga é
 ter uma boa noite de sono em uma cama confortável.</t>
         </is>
       </c>
     </row>
-    <row r="334" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H334" s="15" t="n">
+    <row r="335" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H335" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I334" s="19" t="inlineStr">
+      <c r="I335" s="19" t="inlineStr">
         <is>
           <t>しっかり睡眠をとれば
 レシピを閃いたり、潜在能力が鍛えられたり
 夢で魔法を覚えられたり、いいことがあるかも。</t>
         </is>
       </c>
-      <c r="J334" s="19" t="inlineStr">
+      <c r="J335" s="19" t="inlineStr">
         <is>
           <t>When you get enough sleep,
 you might get new recipe ideas, train your potentials,
 or even learn magic in your dreams.</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
+      <c r="K335" t="inlineStr">
         <is>
           <t>Quando você dorme o suficiente, pode ter novas ideias de receitas, treinar seus talentos ou até mesmo aprender magia em seus sonhos.</t>
         </is>
       </c>
     </row>
-    <row r="335" ht="35.05" customFormat="1" customHeight="1" s="15">
-      <c r="H335" s="15" t="n">
+    <row r="336" ht="35.05" customFormat="1" customHeight="1" s="15">
+      <c r="H336" s="15" t="n">
         <v>47</v>
       </c>
-      <c r="I335" s="19" t="inlineStr">
+      <c r="I336" s="19" t="inlineStr">
         <is>
           <t>まだベッドを作っていないなら
 「休憩」のアビリティを使うことで眠ることもできるわ。
 ベッドで眠るより効果はおちるけどね。</t>
         </is>
       </c>
-      <c r="J335" s="25" t="inlineStr">
+      <c r="J336" s="25" t="inlineStr">
         <is>
           <t>If you haven't made a bed yet,
 you can use the "Rest" ability to sleep.
 It's not as effective as sleeping in a bed, though.</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
+      <c r="K336" t="inlineStr">
         <is>
           <t xml:space="preserve">Se você ainda não fez uma cama,  
 pode usar a habilidade "Descansar" para dormir.  
@@ -7961,11 +7985,11 @@
         </is>
       </c>
     </row>
-    <row r="336" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H336" s="15" t="n">
+    <row r="337" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H337" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="I336" s="19" t="inlineStr">
+      <c r="I337" s="19" t="inlineStr">
         <is>
           <t>休憩中は体力や魔力の自然回復量も上がるから
 戦いの後は休憩するのもありね。
@@ -7973,7 +7997,7 @@
 自然回復自体止まってしまうから気を付けて。</t>
         </is>
       </c>
-      <c r="J336" s="19" t="inlineStr">
+      <c r="J337" s="19" t="inlineStr">
         <is>
           <t>When resting, your natural recovery of health and magic power increases,
 so it's good to rest after a battle.
@@ -7981,127 +8005,127 @@
 natural recovery stops altogether.</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
+      <c r="K337" t="inlineStr">
         <is>
           <t>Ao descansar, sua recuperação natural de saúde e poder mágico aumenta, portanto, é bom descansar depois de uma batalha.
 Mas tome cuidado, pois se você estiver sobrecarregado ou faminto, a recuperação natural será interrompida completamente.</t>
         </is>
       </c>
     </row>
-    <row r="337" ht="22.35" customHeight="1" s="17">
-      <c r="H337" s="15" t="n">
+    <row r="338" ht="22.35" customHeight="1" s="17">
+      <c r="H338" s="15" t="n">
         <v>49</v>
       </c>
-      <c r="I337" s="19" t="inlineStr">
+      <c r="I338" s="19" t="inlineStr">
         <is>
           <t>じゃあ、しっかり睡眠をとるのよ！</t>
         </is>
       </c>
-      <c r="J337" s="19" t="inlineStr">
+      <c r="J338" s="19" t="inlineStr">
         <is>
           <t>Okay that's it for now.
 Make sure to get plenty of sleep!</t>
         </is>
       </c>
-      <c r="K337" s="15" t="inlineStr">
+      <c r="K338" s="15" t="inlineStr">
         <is>
           <t>Por enquanto é isso.
 Não deixe de dormir bastante!</t>
         </is>
       </c>
     </row>
-    <row r="338" ht="12.8" customHeight="1" s="17">
-      <c r="B338" s="19" t="inlineStr">
+    <row r="339" ht="12.8" customHeight="1" s="17">
+      <c r="B339" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K338" s="15" t="n"/>
-    </row>
-    <row r="339" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+      <c r="K339" s="15" t="n"/>
+    </row>
     <row r="340" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="341" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A341" s="19" t="inlineStr">
+    <row r="341" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="342" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A342" s="19" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
     </row>
-    <row r="342" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H342" s="15" t="n">
+    <row r="343" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H343" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I342" s="19" t="inlineStr">
+      <c r="I343" s="19" t="inlineStr">
         <is>
           <t>おーい、ちょっとまって。
 …走るなコラ！</t>
         </is>
       </c>
-      <c r="J342" s="19" t="inlineStr">
+      <c r="J343" s="19" t="inlineStr">
         <is>
           <t>Hey, wait a minute.
 ...don't... don't run!</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr">
+      <c r="K343" t="inlineStr">
         <is>
           <t xml:space="preserve">Ei, espere um minuto.  
 E não, não corra!  </t>
         </is>
       </c>
     </row>
-    <row r="343" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H343" s="15" t="n">
+    <row r="344" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H344" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I343" s="19" t="inlineStr">
+      <c r="I344" s="19" t="inlineStr">
         <is>
           <t>はぁはぁ…コホン</t>
         </is>
       </c>
-      <c r="J343" s="19" t="inlineStr">
+      <c r="J344" s="19" t="inlineStr">
         <is>
           <t>*huff* *puff*
 ...*cough*</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
+      <c r="K344" t="inlineStr">
         <is>
           <t xml:space="preserve">*huff* *puff*  
 ...*cof*  </t>
         </is>
       </c>
     </row>
-    <row r="344" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H344" s="15" t="n">
+    <row r="345" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H345" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I344" s="19" t="inlineStr">
+      <c r="I345" s="19" t="inlineStr">
         <is>
           <t>キミが今いるのは「グローバルマップ」よ。
 ワールドマップでは大距離を移動できるかわりに
 時間がとても早く経過するの。</t>
         </is>
       </c>
-      <c r="J344" s="19" t="inlineStr">
+      <c r="J345" s="19" t="inlineStr">
         <is>
           <t>You are now in the "Global Map".
 In the global map, you can travel great distances
 but time also passes very quickly.</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
+      <c r="K345" t="inlineStr">
         <is>
           <t>Agora você está no “Mapa Global”.
 No Mapa Global, você pode viajar grandes distâncias, mas o tempo também passa muito rápido.</t>
         </is>
       </c>
     </row>
-    <row r="345" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H345" s="15" t="n">
+    <row r="346" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H346" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I345" s="19" t="inlineStr">
+      <c r="I346" s="19" t="inlineStr">
         <is>
           <t>食料を十分に持っていないと
 すぐ餓死するから気をつけてね。
@@ -8109,25 +8133,25 @@
 毒にかかってる時に移動なんかしないこと！</t>
         </is>
       </c>
-      <c r="J345" s="19" t="inlineStr">
+      <c r="J346" s="19" t="inlineStr">
         <is>
           <t>You will starve to death if you don't have enough food
 and conditions such as poison progress rapidly.
 So be careful when you move.</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
+      <c r="K346" t="inlineStr">
         <is>
           <t>Você morrerá de fome se não tiver comida suficiente, e doenças como o veneno progridem rapidamente.
 Portanto, tenha cuidado ao se deslocar.</t>
         </is>
       </c>
     </row>
-    <row r="346" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H346" s="15" t="n">
+    <row r="347" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H347" s="15" t="n">
         <v>212</v>
       </c>
-      <c r="I346" s="19" t="inlineStr">
+      <c r="I347" s="19" t="inlineStr">
         <is>
           <t>食べるものがなくてどうしようもない時は
 自分のいる場所をクリックしてみて。
@@ -8135,7 +8159,7 @@
 森や平野なら、野生の食材も豊富にあるはず。</t>
         </is>
       </c>
-      <c r="J346" s="19" t="inlineStr">
+      <c r="J347" s="19" t="inlineStr">
         <is>
           <t>When you have nothing to eat, try clicking on yourself.
 You’ll be able to enter an “Outdoor Map” corresponding
@@ -8143,7 +8167,7 @@
 If you’re in a forest or plains, there should be plenty of wild food available.</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr">
+      <c r="K347" t="inlineStr">
         <is>
           <t>Se você estiver sem comida e sem opções, tente abrir o "Mapa Global".
 Você vai ver um mapa relativo ao seu local atual.
@@ -8152,33 +8176,33 @@
         </is>
       </c>
     </row>
-    <row r="347" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H347" s="15" t="n">
+    <row r="348" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H348" s="15" t="n">
         <v>52</v>
       </c>
-      <c r="I347" s="19" t="inlineStr">
+      <c r="I348" s="19" t="inlineStr">
         <is>
           <t>そうそう、グローバルマップを移動していると
 モンスターに襲撃されることがあるわ。</t>
         </is>
       </c>
-      <c r="J347" s="19" t="inlineStr">
+      <c r="J348" s="19" t="inlineStr">
         <is>
           <t>Oh, and when you're traveling on the global map
 you might get attacked by monsters.</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
+      <c r="K348" t="inlineStr">
         <is>
           <t>Ah, e quando você estiver viajando no mapa global, poderá ser atacado por monstros.</t>
         </is>
       </c>
     </row>
-    <row r="348" ht="74.59999999999999" customFormat="1" customHeight="1" s="15">
-      <c r="H348" s="15" t="n">
+    <row r="349" ht="74.59999999999999" customFormat="1" customHeight="1" s="15">
+      <c r="H349" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="I348" s="19" t="inlineStr">
+      <c r="I349" s="19" t="inlineStr">
         <is>
           <t>右手に街道が見えるでしょ？
 街道の上は襲撃が少なくて比較的安全。
@@ -8186,7 +8210,7 @@
 駆け出しのうちは、街道を利用するといいわ。</t>
         </is>
       </c>
-      <c r="J348" s="19" t="inlineStr">
+      <c r="J349" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">See that road to your right?
 Attacks are less frequent on the road
@@ -8195,7 +8219,7 @@
 So, for beginners, sticking to the road is a good idea. </t>
         </is>
       </c>
-      <c r="K348" t="inlineStr">
+      <c r="K349" t="inlineStr">
         <is>
           <t>Está vendo a estrada da cidade à sua direita?
 A estrada é relativamente segura, com menos ataques.
@@ -8203,81 +8227,81 @@
         </is>
       </c>
     </row>
-    <row r="349" ht="12.8" customHeight="1" s="17">
-      <c r="H349" s="15" t="n">
+    <row r="350" ht="12.8" customHeight="1" s="17">
+      <c r="H350" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="I349" s="19" t="inlineStr">
+      <c r="I350" s="19" t="inlineStr">
         <is>
           <t>それでは…</t>
         </is>
       </c>
-      <c r="J349" s="25" t="inlineStr">
+      <c r="J350" s="25" t="inlineStr">
         <is>
           <t>Well then...</t>
         </is>
       </c>
-      <c r="K349" s="15" t="inlineStr">
+      <c r="K350" s="15" t="inlineStr">
         <is>
           <t>Então, bem…</t>
         </is>
       </c>
     </row>
-    <row r="350" ht="12.8" customHeight="1" s="17">
-      <c r="B350" s="19" t="inlineStr">
+    <row r="351" ht="12.8" customHeight="1" s="17">
+      <c r="B351" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K350" s="15" t="n"/>
-    </row>
-    <row r="352" ht="12.8" customHeight="1" s="17">
-      <c r="A352" s="15" t="inlineStr">
+      <c r="K351" s="15" t="n"/>
+    </row>
+    <row r="353" ht="12.8" customHeight="1" s="17">
+      <c r="A353" s="15" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
     </row>
-    <row r="353" ht="12.8" customHeight="1" s="17">
-      <c r="D353" s="15" t="inlineStr">
+    <row r="354" ht="12.8" customHeight="1" s="17">
+      <c r="D354" s="15" t="inlineStr">
         <is>
           <t>hideUI</t>
         </is>
       </c>
-      <c r="E353" s="15" t="inlineStr">
+      <c r="E354" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="354" ht="22.35" customHeight="1" s="17">
-      <c r="H354" s="15" t="n">
+    <row r="355" ht="22.35" customHeight="1" s="17">
+      <c r="H355" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I354" s="19" t="inlineStr">
+      <c r="I355" s="19" t="inlineStr">
         <is>
           <t>そうそう
 Demoはこれでおしまいよ。</t>
         </is>
       </c>
-      <c r="J354" s="19" t="inlineStr">
+      <c r="J355" s="19" t="inlineStr">
         <is>
           <t>Oh yes.
 This is the end of the Demo.</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr">
+      <c r="K355" t="inlineStr">
         <is>
           <t xml:space="preserve">Oh, sim.  _x000D_
 Este é o fim da Demo.  </t>
         </is>
       </c>
     </row>
-    <row r="355" ht="43.25" customHeight="1" s="17">
-      <c r="H355" s="15" t="n">
+    <row r="356" ht="43.25" customHeight="1" s="17">
+      <c r="H356" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I355" s="19" t="inlineStr">
+      <c r="I356" s="19" t="inlineStr">
         <is>
           <t>この先の街や色々な場所を訪れることもできるけど
 まだ未実装の部分も多いし
@@ -8285,7 +8309,7 @@
 あまりオススメはしないわ。</t>
         </is>
       </c>
-      <c r="J355" s="19" t="inlineStr">
+      <c r="J356" s="19" t="inlineStr">
         <is>
           <t>You can still visit cities and places down the road
 but I don't recommend it as there are
@@ -8293,93 +8317,63 @@
 and it will spoil the fun and surprises later on.</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
+      <c r="K356" t="inlineStr">
         <is>
           <t xml:space="preserve">Você ainda pode visitar cidades e lugares adiante,  
 mas não recomendo, pois há  muitos aspectos não implementados e isso estragaria a diversão e as surpresas futuras.  </t>
         </is>
       </c>
     </row>
-    <row r="356" ht="22.35" customHeight="1" s="17">
-      <c r="B356" s="15" t="inlineStr">
+    <row r="357" ht="22.35" customHeight="1" s="17">
+      <c r="B357" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="H356" s="15" t="n">
+      <c r="H357" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I356" s="19" t="inlineStr">
+      <c r="I357" s="19" t="inlineStr">
         <is>
           <t>少し観光したら
 そっとゲームを閉じていってね。</t>
         </is>
       </c>
-      <c r="J356" s="19" t="inlineStr">
+      <c r="J357" s="19" t="inlineStr">
         <is>
           <t>After a little sightseeing
 please close the game gently.</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
+      <c r="K357" t="inlineStr">
         <is>
           <t xml:space="preserve">Depois de um pequeno passeio,  
 por favor, feche o jogo com cuidado.  </t>
         </is>
       </c>
     </row>
-    <row r="359" ht="12.8" customHeight="1" s="17">
-      <c r="A359" s="15" t="inlineStr">
+    <row r="360" ht="12.8" customHeight="1" s="17">
+      <c r="A360" s="15" t="inlineStr">
         <is>
           <t>9-1</t>
         </is>
       </c>
-      <c r="H359" s="15" t="n">
+      <c r="H360" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="I359" s="15" t="inlineStr">
+      <c r="I360" s="15" t="inlineStr">
         <is>
           <t>なになに？</t>
         </is>
       </c>
-      <c r="J359" s="15" t="inlineStr">
+      <c r="J360" s="15" t="inlineStr">
         <is>
           <t>What?</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr">
+      <c r="K360" t="inlineStr">
         <is>
           <t xml:space="preserve">O quê?  </t>
-        </is>
-      </c>
-    </row>
-    <row r="360" ht="12.8" customHeight="1" s="17">
-      <c r="B360" s="15" t="inlineStr">
-        <is>
-          <t>9-2</t>
-        </is>
-      </c>
-      <c r="D360" s="15" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="H360" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I360" s="15" t="inlineStr">
-        <is>
-          <t>明日の天気は？</t>
-        </is>
-      </c>
-      <c r="J360" s="15" t="inlineStr">
-        <is>
-          <t>What will the weather be tomorrow?</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>Como estará o tempo amanhã?</t>
         </is>
       </c>
     </row>
@@ -8395,28 +8389,28 @@
         </is>
       </c>
       <c r="H361" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I361" s="15" t="inlineStr">
         <is>
-          <t>今日の運勢は？</t>
+          <t>明日の天気は？</t>
         </is>
       </c>
       <c r="J361" s="15" t="inlineStr">
         <is>
-          <t>How is my fortune today?</t>
+          <t>What will the weather be tomorrow?</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qual é a minha sorte hoje?  </t>
+          <t>Como estará o tempo amanhã?</t>
         </is>
       </c>
     </row>
     <row r="362" ht="12.8" customHeight="1" s="17">
       <c r="B362" s="15" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="D362" s="15" t="inlineStr">
@@ -8425,97 +8419,127 @@
         </is>
       </c>
       <c r="H362" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I362" s="15" t="inlineStr">
         <is>
-          <t>なんでもない</t>
+          <t>今日の運勢は？</t>
         </is>
       </c>
       <c r="J362" s="15" t="inlineStr">
         <is>
-          <t>Nothing</t>
+          <t>How is my fortune today?</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nada  </t>
+          <t xml:space="preserve">Qual é a minha sorte hoje?  </t>
         </is>
       </c>
     </row>
     <row r="363" ht="12.8" customHeight="1" s="17">
       <c r="B363" s="15" t="inlineStr">
         <is>
+          <t>9-3</t>
+        </is>
+      </c>
+      <c r="D363" s="15" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="H363" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I363" s="15" t="inlineStr">
+        <is>
+          <t>なんでもない</t>
+        </is>
+      </c>
+      <c r="J363" s="15" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nada  </t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="12.8" customHeight="1" s="17">
+      <c r="B364" s="15" t="inlineStr">
+        <is>
           <t>end</t>
         </is>
       </c>
-      <c r="D363" s="15" t="inlineStr">
+      <c r="D364" s="15" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
     </row>
-    <row r="367" ht="12.8" customHeight="1" s="17">
-      <c r="A367" s="15" t="inlineStr">
+    <row r="368" ht="12.8" customHeight="1" s="17">
+      <c r="A368" s="15" t="inlineStr">
         <is>
           <t>9-2</t>
         </is>
       </c>
-      <c r="H367" s="15" t="n">
+      <c r="H368" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="I367" s="15" t="inlineStr">
+      <c r="I368" s="15" t="inlineStr">
         <is>
           <t>…さあ？</t>
         </is>
       </c>
-      <c r="J367" s="15" t="inlineStr">
+      <c r="J368" s="15" t="inlineStr">
         <is>
           <t>...who knows?</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr">
+      <c r="K368" t="inlineStr">
         <is>
           <t>... E então?</t>
         </is>
       </c>
     </row>
-    <row r="368" ht="12.8" customHeight="1" s="17">
-      <c r="B368" s="15" t="inlineStr">
+    <row r="369" ht="12.8" customHeight="1" s="17">
+      <c r="B369" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="371" ht="12.8" customHeight="1" s="17">
-      <c r="A371" s="15" t="inlineStr">
+    <row r="372" ht="12.8" customHeight="1" s="17">
+      <c r="A372" s="15" t="inlineStr">
         <is>
           <t>9-3</t>
         </is>
       </c>
     </row>
-    <row r="372" ht="12.8" customHeight="1" s="17">
-      <c r="H372" s="15" t="n">
+    <row r="373" ht="12.8" customHeight="1" s="17">
+      <c r="H373" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="I372" s="15" t="inlineStr">
+      <c r="I373" s="15" t="inlineStr">
         <is>
           <t>用事もないのに呼ばないで。</t>
         </is>
       </c>
-      <c r="J372" s="15" t="inlineStr">
+      <c r="J373" s="15" t="inlineStr">
         <is>
           <t>Don't disturb me for nothing.</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr">
+      <c r="K373" t="inlineStr">
         <is>
           <t xml:space="preserve">Não me incomode por nada.  </t>
         </is>
       </c>
     </row>
-    <row r="373" ht="12.8" customHeight="1" s="17">
-      <c r="B373" s="15" t="inlineStr">
+    <row r="374" ht="12.8" customHeight="1" s="17">
+      <c r="B374" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PTBR/Lang/PTBR/Dialog/Drama/_tutorial.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/_tutorial.xlsx
@@ -1750,7 +1750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K374"/>
+  <dimension ref="A1:K373"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.83" customWidth="1" style="15" min="1" max="3"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="K12" s="15" t="n"/>
     </row>
-    <row r="13" ht="12.8" customHeight="1" s="17">
+    <row r="13" ht="35.05" customHeight="1" s="17">
       <c r="I13" s="19" t="inlineStr">
         <is>
           <t>…</t>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="12.8" customHeight="1" s="17">
+    <row r="18" ht="22.35" customHeight="1" s="17">
       <c r="H18" s="15" t="n">
         <v>327</v>
       </c>
@@ -4600,31 +4600,41 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="22.35" customFormat="1" customHeight="1" s="15">
+    <row r="154" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A154" s="19" t="n"/>
       <c r="B154" s="19" t="n"/>
       <c r="C154" s="19" t="inlineStr">
         <is>
-          <t>nerun_nadenade</t>
-        </is>
-      </c>
-      <c r="D154" s="19" t="inlineStr">
-        <is>
-          <t>getAchievement</t>
-        </is>
-      </c>
-      <c r="E154" s="19" t="inlineStr">
-        <is>
-          <t>NERUN2</t>
-        </is>
-      </c>
+          <t>nerun_nadenade2</t>
+        </is>
+      </c>
+      <c r="D154" s="19" t="n"/>
+      <c r="E154" s="19" t="n"/>
       <c r="F154" s="19" t="n"/>
       <c r="G154" s="19" t="n"/>
-      <c r="I154" s="26" t="n"/>
-      <c r="J154" s="25" t="n"/>
-      <c r="K154" s="19" t="n"/>
-    </row>
-    <row r="155" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H154" s="15" t="n">
+        <v>231</v>
+      </c>
+      <c r="I154" s="26" t="inlineStr">
+        <is>
+          <t>この期間にキミが死んだ回数は実に#1回…
+一体、何をしていたの？</t>
+        </is>
+      </c>
+      <c r="J154" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The number of times you died during this period is actually #1...
+What on earth were you doing? </t>
+        </is>
+      </c>
+      <c r="K154" s="19" t="inlineStr">
+        <is>
+          <t>O número de vezes que você morreu durante este período é, na verdade, #1...
+O que diabos você estava fazendo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="A155" s="19" t="n"/>
       <c r="B155" s="19" t="n"/>
       <c r="C155" s="19" t="inlineStr">
@@ -4637,59 +4647,55 @@
       <c r="F155" s="19" t="n"/>
       <c r="G155" s="19" t="n"/>
       <c r="H155" s="15" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I155" s="26" t="inlineStr">
         <is>
-          <t>この期間にキミが死んだ回数は実に#1回…
-一体、何をしていたの？</t>
+          <t>さすがの私も、キミみたいな冒険者は初めてよ…</t>
         </is>
       </c>
       <c r="J155" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">The number of times you died during this period is actually #1...
-What on earth were you doing? </t>
+          <t>Even for me, I’ve never seen an adventurer quite like you...</t>
         </is>
       </c>
       <c r="K155" s="19" t="inlineStr">
         <is>
-          <t>O número de vezes que você morreu durante este período é, na verdade, #1...
-O que diabos você estava fazendo?</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="22.35" customFormat="1" customHeight="1" s="15">
+          <t>Até para mim, nunca vi um aventureiro como você...</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A156" s="19" t="n"/>
       <c r="B156" s="19" t="n"/>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t>nerun_nadenade2</t>
-        </is>
-      </c>
+      <c r="C156" s="19" t="n"/>
       <c r="D156" s="19" t="n"/>
       <c r="E156" s="19" t="n"/>
       <c r="F156" s="19" t="n"/>
       <c r="G156" s="19" t="n"/>
       <c r="H156" s="15" t="n">
-        <v>232</v>
-      </c>
-      <c r="I156" s="26" t="inlineStr">
-        <is>
-          <t>さすがの私も、キミみたいな冒険者は初めてよ…</t>
-        </is>
-      </c>
-      <c r="J156" s="25" t="inlineStr">
-        <is>
-          <t>Even for me, I’ve never seen an adventurer quite like you...</t>
+        <v>128</v>
+      </c>
+      <c r="I156" s="28" t="inlineStr">
+        <is>
+          <t>これからは死んだら
+デスペナルティが発生するから気をつけていってね。</t>
+        </is>
+      </c>
+      <c r="J156" s="19" t="inlineStr">
+        <is>
+          <t>From now on, when you die, you'll incur death penalties.
+So be careful.</t>
         </is>
       </c>
       <c r="K156" s="19" t="inlineStr">
         <is>
-          <t>Até para mim, nunca vi um aventureiro como você...</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>De agora em diante, quando você morrer, incorrerá em uma penalidade de morte.
+Portanto, tenha cuidado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A157" s="19" t="n"/>
       <c r="B157" s="19" t="n"/>
       <c r="C157" s="19" t="n"/>
@@ -4697,31 +4703,17 @@
       <c r="E157" s="19" t="n"/>
       <c r="F157" s="19" t="n"/>
       <c r="G157" s="19" t="n"/>
-      <c r="H157" s="15" t="n">
-        <v>128</v>
-      </c>
-      <c r="I157" s="28" t="inlineStr">
-        <is>
-          <t>これからは死んだら
-デスペナルティが発生するから気をつけていってね。</t>
-        </is>
-      </c>
-      <c r="J157" s="19" t="inlineStr">
-        <is>
-          <t>From now on, when you die, you'll incur death penalties.
-So be careful.</t>
-        </is>
-      </c>
-      <c r="K157" s="19" t="inlineStr">
-        <is>
-          <t>De agora em diante, quando você morrer, incorrerá em uma penalidade de morte.
-Portanto, tenha cuidado.</t>
-        </is>
-      </c>
+      <c r="I157" s="19" t="n"/>
+      <c r="J157" s="19" t="n"/>
+      <c r="K157" s="19" t="n"/>
     </row>
     <row r="158" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A158" s="19" t="n"/>
-      <c r="B158" s="19" t="n"/>
+      <c r="B158" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C158" s="19" t="n"/>
       <c r="D158" s="19" t="n"/>
       <c r="E158" s="19" t="n"/>
@@ -4733,11 +4725,7 @@
     </row>
     <row r="159" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A159" s="19" t="n"/>
-      <c r="B159" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B159" s="19" t="n"/>
       <c r="C159" s="19" t="n"/>
       <c r="D159" s="19" t="n"/>
       <c r="E159" s="19" t="n"/>
@@ -4748,7 +4736,11 @@
       <c r="K159" s="19" t="n"/>
     </row>
     <row r="160" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A160" s="19" t="n"/>
+      <c r="A160" s="19" t="inlineStr">
+        <is>
+          <t>garbage</t>
+        </is>
+      </c>
       <c r="B160" s="19" t="n"/>
       <c r="C160" s="19" t="n"/>
       <c r="D160" s="19" t="n"/>
@@ -4759,23 +4751,34 @@
       <c r="J160" s="19" t="n"/>
       <c r="K160" s="19" t="n"/>
     </row>
-    <row r="161" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A161" s="19" t="inlineStr">
-        <is>
-          <t>garbage</t>
-        </is>
-      </c>
+    <row r="161" ht="13.8" customFormat="1" customHeight="1" s="15">
+      <c r="A161" s="19" t="n"/>
       <c r="B161" s="19" t="n"/>
       <c r="C161" s="19" t="n"/>
       <c r="D161" s="19" t="n"/>
       <c r="E161" s="19" t="n"/>
       <c r="F161" s="19" t="n"/>
       <c r="G161" s="19" t="n"/>
-      <c r="I161" s="19" t="n"/>
-      <c r="J161" s="19" t="n"/>
-      <c r="K161" s="19" t="n"/>
-    </row>
-    <row r="162" ht="13.8" customFormat="1" customHeight="1" s="15">
+      <c r="H161" s="15" t="n">
+        <v>129</v>
+      </c>
+      <c r="I161" s="26" t="inlineStr">
+        <is>
+          <t>やだ、ゴミまみれ！</t>
+        </is>
+      </c>
+      <c r="J161" s="25" t="inlineStr">
+        <is>
+          <t>Oh no, there's trash everywhere!</t>
+        </is>
+      </c>
+      <c r="K161" s="19" t="inlineStr">
+        <is>
+          <t>Ah não, tem lixo por toda parte!</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A162" s="19" t="n"/>
       <c r="B162" s="19" t="n"/>
       <c r="C162" s="19" t="n"/>
@@ -4784,21 +4787,24 @@
       <c r="F162" s="19" t="n"/>
       <c r="G162" s="19" t="n"/>
       <c r="H162" s="15" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I162" s="26" t="inlineStr">
         <is>
-          <t>やだ、ゴミまみれ！</t>
-        </is>
-      </c>
-      <c r="J162" s="25" t="inlineStr">
-        <is>
-          <t>Oh no, there's trash everywhere!</t>
+          <t>キミって、噂の…片づけられない冒険者なの？
+ゴミはちゃんと掃除しないと大問題になるわよ？</t>
+        </is>
+      </c>
+      <c r="J162" s="19" t="inlineStr">
+        <is>
+          <t>Are you the rumored... messy adventurer?
+If you don't clean up, it could become a big problem!</t>
         </is>
       </c>
       <c r="K162" s="19" t="inlineStr">
         <is>
-          <t>Ah não, tem lixo por toda parte!</t>
+          <t>Você é um daqueles aventureiros... Bagunceiros?
+Sabe, se você não limpar seu lixo, vai se meter em grandes problemas.</t>
         </is>
       </c>
     </row>
@@ -4811,24 +4817,23 @@
       <c r="F163" s="19" t="n"/>
       <c r="G163" s="19" t="n"/>
       <c r="H163" s="15" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I163" s="26" t="inlineStr">
         <is>
-          <t>キミって、噂の…片づけられない冒険者なの？
-ゴミはちゃんと掃除しないと大問題になるわよ？</t>
+          <t>といっても、住民が増えてくるとゴミも多くなるから
+何らかの対策が必要ね！</t>
         </is>
       </c>
       <c r="J163" s="19" t="inlineStr">
         <is>
-          <t>Are you the rumored... messy adventurer?
-If you don't clean up, it could become a big problem!</t>
+          <t>As the population grows, more trash will accumulate,
+so you'll need to come up with some measures.</t>
         </is>
       </c>
       <c r="K163" s="19" t="inlineStr">
         <is>
-          <t>Você é um daqueles aventureiros... Bagunceiros?
-Sabe, se você não limpar seu lixo, vai se meter em grandes problemas.</t>
+          <t>À medida que a população crescer, mais lixo se acumulará, portanto, você precisará tomar algumas medidas.</t>
         </is>
       </c>
     </row>
@@ -4841,27 +4846,28 @@
       <c r="F164" s="19" t="n"/>
       <c r="G164" s="19" t="n"/>
       <c r="H164" s="15" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I164" s="26" t="inlineStr">
         <is>
-          <t>といっても、住民が増えてくるとゴミも多くなるから
-何らかの対策が必要ね！</t>
+          <t>一番手っ取り早い解決方法は
+「ポイ捨て厳罰法」を施行することかな。</t>
         </is>
       </c>
       <c r="J164" s="19" t="inlineStr">
         <is>
-          <t>As the population grows, more trash will accumulate,
-so you'll need to come up with some measures.</t>
+          <t>The quickest solution is to
+implement the "Strict Anti-Littering Law".</t>
         </is>
       </c>
       <c r="K164" s="19" t="inlineStr">
         <is>
-          <t>À medida que a população crescer, mais lixo se acumulará, portanto, você precisará tomar algumas medidas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>A solução mais rápida é implementar a
+"Lei Rigorosa Contra o Descarte de Lixo".</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A165" s="19" t="n"/>
       <c r="B165" s="19" t="n"/>
       <c r="C165" s="19" t="n"/>
@@ -4870,24 +4876,27 @@
       <c r="F165" s="19" t="n"/>
       <c r="G165" s="19" t="n"/>
       <c r="H165" s="15" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I165" s="26" t="inlineStr">
         <is>
-          <t>一番手っ取り早い解決方法は
-「ポイ捨て厳罰法」を施行することかな。</t>
+          <t>このポリシーを施行すると、ゴミはほとんど発生しなくなるわ。
+ただし、民度が下がってしまうので、いつかはもっと
+良いゴミ対策方法に移行したい所ね。</t>
         </is>
       </c>
       <c r="J165" s="19" t="inlineStr">
         <is>
-          <t>The quickest solution is to
-implement the "Strict Anti-Littering Law".</t>
+          <t>With this policy, trash will mostly disappear.
+However, since it lowers the public morality,
+you'll eventually want to switch to a better waste management solution.</t>
         </is>
       </c>
       <c r="K165" s="19" t="inlineStr">
         <is>
-          <t>A solução mais rápida é implementar a
-"Lei Rigorosa Contra o Descarte de Lixo".</t>
+          <t>Com essa política, o lixo praticamente desaparecerá._x000D_
+No entanto, como isso reduz a moral pública,_x000D_
+eventualmente você vai querer mudar para uma solução melhor de gestão de resíduos.</t>
         </is>
       </c>
     </row>
@@ -4900,31 +4909,29 @@
       <c r="F166" s="19" t="n"/>
       <c r="G166" s="19" t="n"/>
       <c r="H166" s="15" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I166" s="26" t="inlineStr">
         <is>
-          <t>このポリシーを施行すると、ゴミはほとんど発生しなくなるわ。
-ただし、民度が下がってしまうので、いつかはもっと
-良いゴミ対策方法に移行したい所ね。</t>
+          <t>ゴミ捨て場の立札を立てたり、ゴミのコンテナを置けば
+住人は民度の高さに応じて
+自動的にゴミを出してくれるわ。</t>
         </is>
       </c>
       <c r="J166" s="19" t="inlineStr">
         <is>
-          <t>With this policy, trash will mostly disappear.
-However, since it lowers the public morality,
-you'll eventually want to switch to a better waste management solution.</t>
+          <t>Putting up garbage dump signs and placing garbage containers
+will encourage residents to dispose of trash according to the public morality.</t>
         </is>
       </c>
       <c r="K166" s="19" t="inlineStr">
         <is>
-          <t>Com essa política, o lixo praticamente desaparecerá._x000D_
-No entanto, como isso reduz a moral pública,_x000D_
-eventualmente você vai querer mudar para uma solução melhor de gestão de resíduos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>Colocar placas de descarte e posicionar lixeiras
+incentivará os moradores a jogarem o lixo no lugar certo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A167" s="19" t="n"/>
       <c r="B167" s="19" t="n"/>
       <c r="C167" s="19" t="n"/>
@@ -4933,25 +4940,23 @@
       <c r="F167" s="19" t="n"/>
       <c r="G167" s="19" t="n"/>
       <c r="H167" s="15" t="n">
-        <v>134</v>
-      </c>
-      <c r="I167" s="26" t="inlineStr">
-        <is>
-          <t>ゴミ捨て場の立札を立てたり、ゴミのコンテナを置けば
-住人は民度の高さに応じて
-自動的にゴミを出してくれるわ。</t>
+        <v>135</v>
+      </c>
+      <c r="I167" s="28" t="inlineStr">
+        <is>
+          <t>それに、掃除をしてくれる住民がいれば
+ゴミを分別して出す確率も大幅に上昇するの。</t>
         </is>
       </c>
       <c r="J167" s="19" t="inlineStr">
         <is>
-          <t>Putting up garbage dump signs and placing garbage containers
-will encourage residents to dispose of trash according to the public morality.</t>
+          <t>And if you have residents who clean up,
+the chances of them sorting the trash increase significantly.</t>
         </is>
       </c>
       <c r="K167" s="19" t="inlineStr">
         <is>
-          <t>Colocar placas de descarte e posicionar lixeiras
-incentivará os moradores a jogarem o lixo no lugar certo.</t>
+          <t>Além disso, a probabilidade de separar e descartar o lixo aumenta consideravelmente quando há moradores dispostos a fazer a limpeza.</t>
         </is>
       </c>
     </row>
@@ -4964,63 +4969,46 @@
       <c r="F168" s="19" t="n"/>
       <c r="G168" s="19" t="n"/>
       <c r="H168" s="15" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I168" s="28" t="inlineStr">
         <is>
-          <t>それに、掃除をしてくれる住民がいれば
-ゴミを分別して出す確率も大幅に上昇するの。</t>
+          <t>ゴミは解体することで貴重な資源になるから
+有効に活用していきたいところね！</t>
         </is>
       </c>
       <c r="J168" s="19" t="inlineStr">
         <is>
-          <t>And if you have residents who clean up,
-the chances of them sorting the trash increase significantly.</t>
+          <t>Garbages can be dismantled into valuable resources,
+so you'll want to use them effectively!</t>
         </is>
       </c>
       <c r="K168" s="19" t="inlineStr">
         <is>
-          <t>Além disso, a probabilidade de separar e descartar o lixo aumenta consideravelmente quando há moradores dispostos a fazer a limpeza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>Os lixos podem ser desmontados em recursos valiosos,_x000D_
+então use-os de forma eficiente!</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A169" s="19" t="n"/>
-      <c r="B169" s="19" t="n"/>
+      <c r="B169" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C169" s="19" t="n"/>
       <c r="D169" s="19" t="n"/>
       <c r="E169" s="19" t="n"/>
       <c r="F169" s="19" t="n"/>
       <c r="G169" s="19" t="n"/>
-      <c r="H169" s="15" t="n">
-        <v>136</v>
-      </c>
-      <c r="I169" s="28" t="inlineStr">
-        <is>
-          <t>ゴミは解体することで貴重な資源になるから
-有効に活用していきたいところね！</t>
-        </is>
-      </c>
-      <c r="J169" s="19" t="inlineStr">
-        <is>
-          <t>Garbages can be dismantled into valuable resources,
-so you'll want to use them effectively!</t>
-        </is>
-      </c>
-      <c r="K169" s="19" t="inlineStr">
-        <is>
-          <t>Os lixos podem ser desmontados em recursos valiosos,_x000D_
-então use-os de forma eficiente!</t>
-        </is>
-      </c>
+      <c r="I169" s="19" t="n"/>
+      <c r="J169" s="19" t="n"/>
+      <c r="K169" s="19" t="n"/>
     </row>
     <row r="170" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A170" s="19" t="n"/>
-      <c r="B170" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B170" s="19" t="n"/>
       <c r="C170" s="19" t="n"/>
       <c r="D170" s="19" t="n"/>
       <c r="E170" s="19" t="n"/>
@@ -5031,7 +5019,11 @@
       <c r="K170" s="19" t="n"/>
     </row>
     <row r="171" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A171" s="19" t="n"/>
+      <c r="A171" s="19" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
       <c r="B171" s="19" t="n"/>
       <c r="C171" s="19" t="n"/>
       <c r="D171" s="19" t="n"/>
@@ -5042,23 +5034,37 @@
       <c r="J171" s="19" t="n"/>
       <c r="K171" s="19" t="n"/>
     </row>
-    <row r="172" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A172" s="19" t="inlineStr">
-        <is>
-          <t>eq</t>
-        </is>
-      </c>
+    <row r="172" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="A172" s="19" t="n"/>
       <c r="B172" s="19" t="n"/>
       <c r="C172" s="19" t="n"/>
       <c r="D172" s="19" t="n"/>
       <c r="E172" s="19" t="n"/>
       <c r="F172" s="19" t="n"/>
       <c r="G172" s="19" t="n"/>
-      <c r="I172" s="19" t="n"/>
-      <c r="J172" s="19" t="n"/>
-      <c r="K172" s="19" t="n"/>
-    </row>
-    <row r="173" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H172" s="15" t="n">
+        <v>137</v>
+      </c>
+      <c r="I172" s="26" t="inlineStr">
+        <is>
+          <t>ん、洞窟の探索？
+キミも冒険者らしくなってきたわね！</t>
+        </is>
+      </c>
+      <c r="J172" s="25" t="inlineStr">
+        <is>
+          <t>Huh, exploring a cave already?
+You're becoming like a real adventurer!</t>
+        </is>
+      </c>
+      <c r="K172" s="19" t="inlineStr">
+        <is>
+          <t>Já está explorando uma caverna?
+Você está se tornando um verdadeiro aventureiro!</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="13.8" customFormat="1" customHeight="1" s="15">
       <c r="A173" s="19" t="n"/>
       <c r="B173" s="19" t="n"/>
       <c r="C173" s="19" t="n"/>
@@ -5067,24 +5073,21 @@
       <c r="F173" s="19" t="n"/>
       <c r="G173" s="19" t="n"/>
       <c r="H173" s="15" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I173" s="26" t="inlineStr">
         <is>
-          <t>ん、洞窟の探索？
-キミも冒険者らしくなってきたわね！</t>
+          <t>でも、奥に進む前にちょっと自分の姿を確認してみて。</t>
         </is>
       </c>
       <c r="J173" s="25" t="inlineStr">
         <is>
-          <t>Huh, exploring a cave already?
-You're becoming like a real adventurer!</t>
+          <t>But before you go deeper, take a look at yourself.</t>
         </is>
       </c>
       <c r="K173" s="19" t="inlineStr">
         <is>
-          <t>Já está explorando uma caverna?
-Você está se tornando um verdadeiro aventureiro!</t>
+          <t>Mas antes de ir mais fundo, dê uma olhada em si mesmo.</t>
         </is>
       </c>
     </row>
@@ -5097,25 +5100,25 @@
       <c r="F174" s="19" t="n"/>
       <c r="G174" s="19" t="n"/>
       <c r="H174" s="15" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I174" s="26" t="inlineStr">
         <is>
-          <t>でも、奥に進む前にちょっと自分の姿を確認してみて。</t>
+          <t>…そんな装備で大丈夫か？</t>
         </is>
       </c>
       <c r="J174" s="25" t="inlineStr">
         <is>
-          <t>But before you go deeper, take a look at yourself.</t>
+          <t xml:space="preserve">...You sure that's enough armor? </t>
         </is>
       </c>
       <c r="K174" s="19" t="inlineStr">
         <is>
-          <t>Mas antes de ir mais fundo, dê uma olhada em si mesmo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="13.8" customFormat="1" customHeight="1" s="15">
+          <t xml:space="preserve">... Tem certeza de que essa armadura é suficiente? </t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A175" s="19" t="n"/>
       <c r="B175" s="19" t="n"/>
       <c r="C175" s="19" t="n"/>
@@ -5124,25 +5127,31 @@
       <c r="F175" s="19" t="n"/>
       <c r="G175" s="19" t="n"/>
       <c r="H175" s="15" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I175" s="26" t="inlineStr">
         <is>
-          <t>…そんな装備で大丈夫か？</t>
+          <t>洞窟ともなると、敵もたくさん出てくるわ。
+もし装備を身につけていない部位が３つも４つもあるなら
+たぶん出直した方がキミの命のためよ。</t>
         </is>
       </c>
       <c r="J175" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">...You sure that's enough armor? </t>
+          <t>Caves have lots of enemies.
+If you have an unequipped slot or two,
+you might want to turn back for your own safety.</t>
         </is>
       </c>
       <c r="K175" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">... Tem certeza de que essa armadura é suficiente? </t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>As cavernas estão cheias de inimigos._x000D_
+Se você tiver um ou dois espaços de equipamento vazios,_x000D_
+talvez seja melhor voltar para sua própria segurança.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A176" s="19" t="n"/>
       <c r="B176" s="19" t="n"/>
       <c r="C176" s="19" t="n"/>
@@ -5151,31 +5160,28 @@
       <c r="F176" s="19" t="n"/>
       <c r="G176" s="19" t="n"/>
       <c r="H176" s="15" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I176" s="26" t="inlineStr">
         <is>
-          <t>洞窟ともなると、敵もたくさん出てくるわ。
-もし装備を身につけていない部位が３つも４つもあるなら
-たぶん出直した方がキミの命のためよ。</t>
+          <t>拠点では、簡単な武器や防具を製作することもできるし
+街に赴いて店で物色してもいい。</t>
         </is>
       </c>
       <c r="J176" s="25" t="inlineStr">
         <is>
-          <t>Caves have lots of enemies.
-If you have an unequipped slot or two,
-you might want to turn back for your own safety.</t>
+          <t>At your base, you can craft simple weapons and armor,
+or you can browse the shops in town.</t>
         </is>
       </c>
       <c r="K176" s="19" t="inlineStr">
         <is>
-          <t>As cavernas estão cheias de inimigos._x000D_
-Se você tiver um ou dois espaços de equipamento vazios,_x000D_
-talvez seja melhor voltar para sua própria segurança.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>Na sua base, você pode fabricar armas e armaduras simples,_x000D_
+ou dar uma olhada nas lojas da cidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A177" s="19" t="n"/>
       <c r="B177" s="19" t="n"/>
       <c r="C177" s="19" t="n"/>
@@ -5184,67 +5190,53 @@
       <c r="F177" s="19" t="n"/>
       <c r="G177" s="19" t="n"/>
       <c r="H177" s="15" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I177" s="26" t="inlineStr">
         <is>
-          <t>拠点では、簡単な武器や防具を製作することもできるし
-街に赴いて店で物色してもいい。</t>
+          <t>特に防御力(PV）は、敵からのダメージを軽減する
+重要なステータスだから、敵からの攻撃が辛いと感じたら
+防御力をあげてみてね。</t>
         </is>
       </c>
       <c r="J177" s="25" t="inlineStr">
         <is>
-          <t>At your base, you can craft simple weapons and armor,
-or you can browse the shops in town.</t>
+          <t>Protection Value (PV) is especially a crucial stat that
+reduces the damage you take from enemies.
+If you find enemy attacks too harsh, try increasing your defense.</t>
         </is>
       </c>
       <c r="K177" s="19" t="inlineStr">
         <is>
-          <t>Na sua base, você pode fabricar armas e armaduras simples,_x000D_
-ou dar uma olhada nas lojas da cidade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>O Valor de Proteção (VP ou PV) é um atributo crucial que
+reduz o dano recebido dos inimigos.
+Se os ataques dos inimigos estiverem muito fortes, tente aumentar sua defesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A178" s="19" t="n"/>
-      <c r="B178" s="19" t="n"/>
+      <c r="B178" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C178" s="19" t="n"/>
       <c r="D178" s="19" t="n"/>
       <c r="E178" s="19" t="n"/>
       <c r="F178" s="19" t="n"/>
       <c r="G178" s="19" t="n"/>
-      <c r="H178" s="15" t="n">
-        <v>142</v>
-      </c>
-      <c r="I178" s="26" t="inlineStr">
-        <is>
-          <t>特に防御力(PV）は、敵からのダメージを軽減する
-重要なステータスだから、敵からの攻撃が辛いと感じたら
-防御力をあげてみてね。</t>
-        </is>
-      </c>
-      <c r="J178" s="25" t="inlineStr">
-        <is>
-          <t>Protection Value (PV) is especially a crucial stat that
-reduces the damage you take from enemies.
-If you find enemy attacks too harsh, try increasing your defense.</t>
-        </is>
-      </c>
-      <c r="K178" s="19" t="inlineStr">
-        <is>
-          <t>O Valor de Proteção (VP ou PV) é um atributo crucial que
-reduz o dano recebido dos inimigos.
-Se os ataques dos inimigos estiverem muito fortes, tente aumentar sua defesa.</t>
-        </is>
-      </c>
+      <c r="I178" s="19" t="n"/>
+      <c r="J178" s="19" t="n"/>
+      <c r="K178" s="19" t="n"/>
     </row>
     <row r="179" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A179" s="19" t="n"/>
-      <c r="B179" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="A179" s="19" t="inlineStr">
+        <is>
+          <t>stone</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="n"/>
       <c r="C179" s="19" t="n"/>
       <c r="D179" s="19" t="n"/>
       <c r="E179" s="19" t="n"/>
@@ -5254,23 +5246,34 @@
       <c r="J179" s="19" t="n"/>
       <c r="K179" s="19" t="n"/>
     </row>
-    <row r="180" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A180" s="19" t="inlineStr">
-        <is>
-          <t>stone</t>
-        </is>
-      </c>
+    <row r="180" ht="13.8" customFormat="1" customHeight="1" s="15">
+      <c r="A180" s="19" t="n"/>
       <c r="B180" s="19" t="n"/>
       <c r="C180" s="19" t="n"/>
       <c r="D180" s="19" t="n"/>
       <c r="E180" s="19" t="n"/>
       <c r="F180" s="19" t="n"/>
       <c r="G180" s="19" t="n"/>
-      <c r="I180" s="19" t="n"/>
-      <c r="J180" s="19" t="n"/>
-      <c r="K180" s="19" t="n"/>
-    </row>
-    <row r="181" ht="13.8" customFormat="1" customHeight="1" s="15">
+      <c r="H180" s="15" t="n">
+        <v>143</v>
+      </c>
+      <c r="I180" s="26" t="inlineStr">
+        <is>
+          <t>よしよし、盟約の石も育ってきたわ。</t>
+        </is>
+      </c>
+      <c r="J180" s="25" t="inlineStr">
+        <is>
+          <t>Well done, your Hearth Stone is growing.</t>
+        </is>
+      </c>
+      <c r="K180" s="19" t="inlineStr">
+        <is>
+          <t>Muito bem, sua Pedra do Lar está crescendo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A181" s="19" t="n"/>
       <c r="B181" s="19" t="n"/>
       <c r="C181" s="19" t="n"/>
@@ -5279,21 +5282,27 @@
       <c r="F181" s="19" t="n"/>
       <c r="G181" s="19" t="n"/>
       <c r="H181" s="15" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I181" s="26" t="inlineStr">
         <is>
-          <t>よしよし、盟約の石も育ってきたわ。</t>
-        </is>
-      </c>
-      <c r="J181" s="25" t="inlineStr">
-        <is>
-          <t>Well done, your Hearth Stone is growing.</t>
+          <t>そう、この謎の石は、なんと成長するのよ。
+石の成長とともに、キミの拠点は様々な恩恵を受けるの。
+住民の最大数があがったり、新しいポリシーを覚えたりね。</t>
+        </is>
+      </c>
+      <c r="J181" s="19" t="inlineStr">
+        <is>
+          <t>Yes, this mysterious stone actually grows.
+And as it grows, your base receives various benefits,
+like an increased maximum number of residents or new policies.</t>
         </is>
       </c>
       <c r="K181" s="19" t="inlineStr">
         <is>
-          <t>Muito bem, sua Pedra do Lar está crescendo.</t>
+          <t>Sim, essa pedra misteriosa realmente cresce.
+E conforme cresce, sua base recebe vários benefícios,
+como um aumento no número máximo de residentes ou novas políticas.</t>
         </is>
       </c>
     </row>
@@ -5306,27 +5315,25 @@
       <c r="F182" s="19" t="n"/>
       <c r="G182" s="19" t="n"/>
       <c r="H182" s="15" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I182" s="26" t="inlineStr">
         <is>
-          <t>そう、この謎の石は、なんと成長するのよ。
-石の成長とともに、キミの拠点は様々な恩恵を受けるの。
-住民の最大数があがったり、新しいポリシーを覚えたりね。</t>
+          <t>敵の中には、属性攻撃でアイテムや装備を破壊してくる厄介なのもいるけど
+石のレベルがあがれば、その破壊だって防いでくれるのよ？
+まあ…拠点の中だけだけどね。</t>
         </is>
       </c>
       <c r="J182" s="19" t="inlineStr">
         <is>
-          <t>Yes, this mysterious stone actually grows.
-And as it grows, your base receives various benefits,
-like an increased maximum number of residents or new policies.</t>
+          <t>Some enemies can use elemental attacks to destroy your items and equipment,
+but if the stone levels up, it can even prevent that within your base.</t>
         </is>
       </c>
       <c r="K182" s="19" t="inlineStr">
         <is>
-          <t>Sim, essa pedra misteriosa realmente cresce.
-E conforme cresce, sua base recebe vários benefícios,
-como um aumento no número máximo de residentes ou novas políticas.</t>
+          <t>Alguns inimigos podem usar ataques elementais para destruir seus itens e equipamentos,
+mas se a pedra subir de nível, ela pode até impedir isso dentro da sua base.</t>
         </is>
       </c>
     </row>
@@ -5339,29 +5346,31 @@
       <c r="F183" s="19" t="n"/>
       <c r="G183" s="19" t="n"/>
       <c r="H183" s="15" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I183" s="26" t="inlineStr">
         <is>
-          <t>敵の中には、属性攻撃でアイテムや装備を破壊してくる厄介なのもいるけど
-石のレベルがあがれば、その破壊だって防いでくれるのよ？
-まあ…拠点の中だけだけどね。</t>
+          <t>出荷や日数の経過で、石は自動的に育っていくわ。
+…ただ、注意したいのは、石のレベルがあがると
+拠点の危険度もあがる…つまり、強い敵が襲ってくるということね。</t>
         </is>
       </c>
       <c r="J183" s="19" t="inlineStr">
         <is>
-          <t>Some enemies can use elemental attacks to destroy your items and equipment,
-but if the stone levels up, it can even prevent that within your base.</t>
+          <t>The stone grows automatically through shipments and the passage of days.
+...But beware, as the stone levels up, the danger level of your base
+also increases... meaning stronger enemies will appear.</t>
         </is>
       </c>
       <c r="K183" s="19" t="inlineStr">
         <is>
-          <t>Alguns inimigos podem usar ataques elementais para destruir seus itens e equipamentos,
-mas se a pedra subir de nível, ela pode até impedir isso dentro da sua base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>A pedra cresce automaticamente com remessas e com a passagem dos dias.
+... Mas cuidado, à medida que a pedra sobe de nível, o nível de perigo da sua base
+também aumenta... Ou seja, inimigos mais fortes aparecerão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="46.25" customFormat="1" customHeight="1" s="15">
       <c r="A184" s="19" t="n"/>
       <c r="B184" s="19" t="n"/>
       <c r="C184" s="19" t="n"/>
@@ -5370,31 +5379,32 @@
       <c r="F184" s="19" t="n"/>
       <c r="G184" s="19" t="n"/>
       <c r="H184" s="15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I184" s="26" t="inlineStr">
         <is>
-          <t>出荷や日数の経過で、石は自動的に育っていくわ。
-…ただ、注意したいのは、石のレベルがあがると
-拠点の危険度もあがる…つまり、強い敵が襲ってくるということね。</t>
+          <t>「成長抑止」のポリシーを施行すれば、石の成長に
+ストップをかけることができる。
+もし今拠点に現れる敵に手こずるようだったら
+このポリシーを使って成長を止めておいた方がいいわね。</t>
         </is>
       </c>
       <c r="J184" s="19" t="inlineStr">
         <is>
-          <t>The stone grows automatically through shipments and the passage of days.
-...But beware, as the stone levels up, the danger level of your base
-also increases... meaning stronger enemies will appear.</t>
+          <t>You can use the "Growth Suppression" policy to stop the stone's growth.
+If you're struggling with the enemies currently appearing at your base,
+it might be a good idea to use this policy to halt the growth for a while.</t>
         </is>
       </c>
       <c r="K184" s="19" t="inlineStr">
         <is>
-          <t>A pedra cresce automaticamente com remessas e com a passagem dos dias.
-... Mas cuidado, à medida que a pedra sobe de nível, o nível de perigo da sua base
-também aumenta... Ou seja, inimigos mais fortes aparecerão.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="46.25" customFormat="1" customHeight="1" s="15">
+          <t>Você pode usar a política "Supressão de Crescimento" para impedir o crescimento da pedra.
+Se estiver tendo dificuldades com os inimigos que estão aparecendo na sua base,
+talvez seja uma boa ideia usar essa política para interromper o crescimento por um tempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A185" s="19" t="n"/>
       <c r="B185" s="19" t="n"/>
       <c r="C185" s="19" t="n"/>
@@ -5402,31 +5412,9 @@
       <c r="E185" s="19" t="n"/>
       <c r="F185" s="19" t="n"/>
       <c r="G185" s="19" t="n"/>
-      <c r="H185" s="15" t="n">
-        <v>147</v>
-      </c>
-      <c r="I185" s="26" t="inlineStr">
-        <is>
-          <t>「成長抑止」のポリシーを施行すれば、石の成長に
-ストップをかけることができる。
-もし今拠点に現れる敵に手こずるようだったら
-このポリシーを使って成長を止めておいた方がいいわね。</t>
-        </is>
-      </c>
-      <c r="J185" s="19" t="inlineStr">
-        <is>
-          <t>You can use the "Growth Suppression" policy to stop the stone's growth.
-If you're struggling with the enemies currently appearing at your base,
-it might be a good idea to use this policy to halt the growth for a while.</t>
-        </is>
-      </c>
-      <c r="K185" s="19" t="inlineStr">
-        <is>
-          <t>Você pode usar a política "Supressão de Crescimento" para impedir o crescimento da pedra.
-Se estiver tendo dificuldades com os inimigos que estão aparecendo na sua base,
-talvez seja uma boa ideia usar essa política para interromper o crescimento por um tempo.</t>
-        </is>
-      </c>
+      <c r="I185" s="19" t="n"/>
+      <c r="J185" s="19" t="n"/>
+      <c r="K185" s="19" t="n"/>
     </row>
     <row r="186" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A186" s="19" t="n"/>
@@ -5442,7 +5430,11 @@
     </row>
     <row r="187" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A187" s="19" t="n"/>
-      <c r="B187" s="19" t="n"/>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C187" s="19" t="n"/>
       <c r="D187" s="19" t="n"/>
       <c r="E187" s="19" t="n"/>
@@ -5453,12 +5445,12 @@
       <c r="K187" s="19" t="n"/>
     </row>
     <row r="188" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A188" s="19" t="n"/>
-      <c r="B188" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="A188" s="19" t="inlineStr">
+        <is>
+          <t>feat</t>
+        </is>
+      </c>
+      <c r="B188" s="19" t="n"/>
       <c r="C188" s="19" t="n"/>
       <c r="D188" s="19" t="n"/>
       <c r="E188" s="19" t="n"/>
@@ -5469,20 +5461,31 @@
       <c r="K188" s="19" t="n"/>
     </row>
     <row r="189" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A189" s="19" t="inlineStr">
-        <is>
-          <t>feat</t>
-        </is>
-      </c>
+      <c r="A189" s="19" t="n"/>
       <c r="B189" s="19" t="n"/>
       <c r="C189" s="19" t="n"/>
       <c r="D189" s="19" t="n"/>
       <c r="E189" s="19" t="n"/>
       <c r="F189" s="19" t="n"/>
       <c r="G189" s="19" t="n"/>
-      <c r="I189" s="19" t="n"/>
-      <c r="J189" s="19" t="n"/>
-      <c r="K189" s="19" t="n"/>
+      <c r="H189" s="15" t="n">
+        <v>148</v>
+      </c>
+      <c r="I189" s="19" t="inlineStr">
+        <is>
+          <t>フィートポイントの獲得おめでとう！</t>
+        </is>
+      </c>
+      <c r="J189" s="25" t="inlineStr">
+        <is>
+          <t>Congratulations on earning a Feat Point!</t>
+        </is>
+      </c>
+      <c r="K189" s="19" t="inlineStr">
+        <is>
+          <t>Parabéns por ganhar um Ponto de Talento!</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A190" s="19" t="n"/>
@@ -5493,25 +5496,25 @@
       <c r="F190" s="19" t="n"/>
       <c r="G190" s="19" t="n"/>
       <c r="H190" s="15" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I190" s="19" t="inlineStr">
         <is>
-          <t>フィートポイントの獲得おめでとう！</t>
-        </is>
-      </c>
-      <c r="J190" s="25" t="inlineStr">
-        <is>
-          <t>Congratulations on earning a Feat Point!</t>
+          <t>…え？　フィート、知らないの？</t>
+        </is>
+      </c>
+      <c r="J190" s="19" t="inlineStr">
+        <is>
+          <t>...Huh? You don’t know about Feats?</t>
         </is>
       </c>
       <c r="K190" s="19" t="inlineStr">
         <is>
-          <t>Parabéns por ganhar um Ponto de Talento!</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Você não conhece os talentos?</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="A191" s="19" t="n"/>
       <c r="B191" s="19" t="n"/>
       <c r="C191" s="19" t="n"/>
@@ -5520,21 +5523,26 @@
       <c r="F191" s="19" t="n"/>
       <c r="G191" s="19" t="n"/>
       <c r="H191" s="15" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I191" s="19" t="inlineStr">
         <is>
-          <t>…え？　フィート、知らないの？</t>
+          <t>足が速かったり、力が強かったり
+そういうキミの特徴をフィートっていって
+フィートポイントを消費することで獲得できるの。</t>
         </is>
       </c>
       <c r="J191" s="19" t="inlineStr">
         <is>
-          <t>...Huh? You don’t know about Feats?</t>
+          <t>Feats are special traits you have,
+like being really fast or super strong.
+You can earn them by using Feat Points.</t>
         </is>
       </c>
       <c r="K191" s="19" t="inlineStr">
         <is>
-          <t>Você não conhece os talentos?</t>
+          <t>Talentos são características especiais que você tem, como ser muito rápido ou superforte.
+Você pode certas características usando Pontos de Talentos.</t>
         </is>
       </c>
     </row>
@@ -5547,30 +5555,31 @@
       <c r="F192" s="19" t="n"/>
       <c r="G192" s="19" t="n"/>
       <c r="H192" s="15" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I192" s="19" t="inlineStr">
         <is>
-          <t>足が速かったり、力が強かったり
-そういうキミの特徴をフィートっていって
-フィートポイントを消費することで獲得できるの。</t>
+          <t>画面の下に、青い羽マークのアイコンのゲージが見える？
+キミが何か行動して成長すると、このゲージは増えていく。
+ゲージが満杯になると、フィートポイントを貰えるわ。</t>
         </is>
       </c>
       <c r="J192" s="19" t="inlineStr">
         <is>
-          <t>Feats are special traits you have,
-like being really fast or super strong.
-You can earn them by using Feat Points.</t>
+          <t>Do you see the blue feather icon at the bottom of your screen?
+When you perform actions and grow, this gauge fills up.
+Once it’s full, you earn a Feat Point.</t>
         </is>
       </c>
       <c r="K192" s="19" t="inlineStr">
         <is>
-          <t>Talentos são características especiais que você tem, como ser muito rápido ou superforte.
-Você pode certas características usando Pontos de Talentos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="32.8" customFormat="1" customHeight="1" s="15">
+          <t>Você vê o ícone de pena azul na parte inferior da tela?
+Quando você realiza ações e cresce, esse medidor se enche.
+Quando ele estiver cheio, você ganha um Ponto de Talento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="43.25" customFormat="1" customHeight="1" s="15">
       <c r="A193" s="19" t="n"/>
       <c r="B193" s="19" t="n"/>
       <c r="C193" s="19" t="n"/>
@@ -5579,31 +5588,30 @@
       <c r="F193" s="19" t="n"/>
       <c r="G193" s="19" t="n"/>
       <c r="H193" s="15" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I193" s="19" t="inlineStr">
         <is>
-          <t>画面の下に、青い羽マークのアイコンのゲージが見える？
-キミが何か行動して成長すると、このゲージは増えていく。
-ゲージが満杯になると、フィートポイントを貰えるわ。</t>
+          <t>ゲージをクリックすると、キミが獲得できる
+フィートの一覧が表示されるでしょ？
+この中から、キミが役に立ちそうと思うフィートを
+選択して見るといいわ。</t>
         </is>
       </c>
       <c r="J193" s="19" t="inlineStr">
         <is>
-          <t>Do you see the blue feather icon at the bottom of your screen?
-When you perform actions and grow, this gauge fills up.
-Once it’s full, you earn a Feat Point.</t>
+          <t>Click on the gauge to see a list of Feats you can acquire.
+Choose the ones you think will be useful to you.</t>
         </is>
       </c>
       <c r="K193" s="19" t="inlineStr">
         <is>
-          <t>Você vê o ícone de pena azul na parte inferior da tela?
-Quando você realiza ações e cresce, esse medidor se enche.
-Quando ele estiver cheio, você ganha um Ponto de Talento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="43.25" customFormat="1" customHeight="1" s="15">
+          <t>Clique no medidor para ver uma lista de Talentos que você pode adquirir.
+Escolha os que achar que serão úteis para você.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="A194" s="19" t="n"/>
       <c r="B194" s="19" t="n"/>
       <c r="C194" s="19" t="n"/>
@@ -5612,30 +5620,30 @@
       <c r="F194" s="19" t="n"/>
       <c r="G194" s="19" t="n"/>
       <c r="H194" s="15" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I194" s="19" t="inlineStr">
         <is>
-          <t>ゲージをクリックすると、キミが獲得できる
-フィートの一覧が表示されるでしょ？
-この中から、キミが役に立ちそうと思うフィートを
-選択して見るといいわ。</t>
+          <t>フィートポイントは、貯めておくこともできるから
+今自分に足りないと思うものが特になければ
+温存しておくのもいい選択ね。</t>
         </is>
       </c>
       <c r="J194" s="19" t="inlineStr">
         <is>
-          <t>Click on the gauge to see a list of Feats you can acquire.
-Choose the ones you think will be useful to you.</t>
+          <t>You can also save your Feat Points
+if you don’t need anything specific right now.
+It’s a good strategy to save them for later.</t>
         </is>
       </c>
       <c r="K194" s="19" t="inlineStr">
         <is>
-          <t>Clique no medidor para ver uma lista de Talentos que você pode adquirir.
-Escolha os que achar que serão úteis para você.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="32.8" customFormat="1" customHeight="1" s="15">
+          <t>Você também pode salvar seus Pontos de Talentos se não precisar de nada específico no momento.
+É uma boa estratégia guardá-los para mais tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="32.8" customHeight="1" s="17">
       <c r="A195" s="19" t="n"/>
       <c r="B195" s="19" t="n"/>
       <c r="C195" s="19" t="n"/>
@@ -5644,174 +5652,142 @@
       <c r="F195" s="19" t="n"/>
       <c r="G195" s="19" t="n"/>
       <c r="H195" s="15" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I195" s="19" t="inlineStr">
         <is>
-          <t>フィートポイントは、貯めておくこともできるから
-今自分に足りないと思うものが特になければ
-温存しておくのもいい選択ね。</t>
+          <t>ちなみに、獲得に前提条件のあるフィートもあるからね。
+例えば「美食家」のフィートは
+「料理」スキルを覚えていなければ表示されないの。</t>
         </is>
       </c>
       <c r="J195" s="19" t="inlineStr">
         <is>
-          <t>You can also save your Feat Points
-if you don’t need anything specific right now.
-It’s a good strategy to save them for later.</t>
+          <t>Note that some Feats have prerequisites.
+For example, the “Gourmet” Feat won’t appear
+unless you’ve learned the “Cooking” skill.</t>
         </is>
       </c>
       <c r="K195" s="19" t="inlineStr">
         <is>
-          <t>Você também pode salvar seus Pontos de Talentos se não precisar de nada específico no momento.
-É uma boa estratégia guardá-los para mais tarde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="32.8" customHeight="1" s="17">
+          <t>Observe que alguns Talentos têm pré-requisitos.
+Por exemplo, o Talento “Gourmet” não aparecerá a menos que você tenha aprendido a habilidade “Culinária”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A196" s="19" t="n"/>
-      <c r="B196" s="19" t="n"/>
+      <c r="B196" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C196" s="19" t="n"/>
       <c r="D196" s="19" t="n"/>
       <c r="E196" s="19" t="n"/>
       <c r="F196" s="19" t="n"/>
       <c r="G196" s="19" t="n"/>
-      <c r="H196" s="15" t="n">
-        <v>154</v>
-      </c>
-      <c r="I196" s="19" t="inlineStr">
-        <is>
-          <t>ちなみに、獲得に前提条件のあるフィートもあるからね。
-例えば「美食家」のフィートは
-「料理」スキルを覚えていなければ表示されないの。</t>
-        </is>
-      </c>
-      <c r="J196" s="19" t="inlineStr">
-        <is>
-          <t>Note that some Feats have prerequisites.
-For example, the “Gourmet” Feat won’t appear
-unless you’ve learned the “Cooking” skill.</t>
-        </is>
-      </c>
-      <c r="K196" s="19" t="inlineStr">
-        <is>
-          <t>Observe que alguns Talentos têm pré-requisitos.
-Por exemplo, o Talento “Gourmet” não aparecerá a menos que você tenha aprendido a habilidade “Culinária”.</t>
-        </is>
-      </c>
+      <c r="I196" s="19" t="n"/>
+      <c r="J196" s="19" t="n"/>
+      <c r="K196" s="19" t="n"/>
     </row>
     <row r="197" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A197" s="19" t="n"/>
-      <c r="B197" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="C197" s="19" t="n"/>
-      <c r="D197" s="19" t="n"/>
-      <c r="E197" s="19" t="n"/>
-      <c r="F197" s="19" t="n"/>
-      <c r="G197" s="19" t="n"/>
-      <c r="I197" s="19" t="n"/>
-      <c r="J197" s="19" t="n"/>
-      <c r="K197" s="19" t="n"/>
+      <c r="B197" s="19" t="n"/>
     </row>
     <row r="198" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B198" s="19" t="n"/>
-    </row>
-    <row r="199" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A199" s="19" t="inlineStr">
+      <c r="A198" s="19" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="201" ht="12.8" customFormat="1" customHeight="1" s="15">
+    <row r="199" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="200" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H200" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="I200" s="19" t="inlineStr">
+        <is>
+          <t>よしよし、丸太さんを手に入れたのね。</t>
+        </is>
+      </c>
+      <c r="J200" s="25" t="inlineStr">
+        <is>
+          <t>Alright, you got a log!</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Muito bem, você conseguiu um tronco!</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H201" s="15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I201" s="19" t="inlineStr">
-        <is>
-          <t>よしよし、丸太さんを手に入れたのね。</t>
-        </is>
-      </c>
-      <c r="J201" s="25" t="inlineStr">
-        <is>
-          <t>Alright, you got a log!</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Muito bem, você conseguiu um tronco!</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H202" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="I202" s="19" t="inlineStr">
         <is>
           <t>丸太さん、いえ、丸太先生は最も基本的なクラフト素材で
 焚火などの燃料としても使える優れモノよ。</t>
         </is>
       </c>
-      <c r="J202" s="19" t="inlineStr">
+      <c r="J201" s="19" t="inlineStr">
         <is>
           <t>Logs, or should I say, Mr. Log, are the most basic crafting materials.
 They’re also excellent for things like campfire fuel.</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K201" t="inlineStr">
         <is>
           <t>Os Troncos, ou melhor, o Sr. Tronco, são os materiais de fabricação mais básicos.
 Elas também são excelentes para coisas como combustível para fogueira.</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H203" s="15" t="n">
+    <row r="202" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H202" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="I203" s="19" t="inlineStr">
+      <c r="I202" s="19" t="inlineStr">
         <is>
           <t>でも…それだけじゃない！
 丸太先生は加工することで
 さらに「厚板」へと進化するの。</t>
         </is>
       </c>
-      <c r="J203" s="19" t="inlineStr">
+      <c r="J202" s="19" t="inlineStr">
         <is>
           <t>But... that’s not all!
 By processing Mr. Log, you can upgrade it into "Planks".</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>Mas isso não é tudo!
 Ao processar o Sr. Tronco, você pode transformá-lo em "Tábuas".</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H204" s="15" t="n">
+    <row r="203" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H203" s="15" t="n">
         <v>108</v>
       </c>
-      <c r="I204" s="19" t="inlineStr">
+      <c r="I203" s="19" t="inlineStr">
         <is>
           <t>え…？どうやったら加工できる？
 そうね、丸太先生に聞いてみたらどう？
 ヒントは「加工設備」よ。</t>
         </is>
       </c>
-      <c r="J204" s="19" t="inlineStr">
+      <c r="J203" s="19" t="inlineStr">
         <is>
           <t>Huh...? How do you process it?
 Well, why don't you ask Mr. Log yourself?
 The hint is 'processing equipment'.</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="K203" t="inlineStr">
         <is>
           <t>O quê? Como você processa isso?
 Bem, por que você mesmo não pergunta ao Sr. Tronco?
@@ -5819,114 +5795,114 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H205" s="15" t="n">
+    <row r="204" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H204" s="15" t="n">
         <v>109</v>
       </c>
-      <c r="I205" s="19" t="inlineStr">
+      <c r="I204" s="19" t="inlineStr">
         <is>
           <t>…ちなみに、石も「切り石」に加工できるから
 覚えておいてね。</t>
         </is>
       </c>
-      <c r="J205" s="19" t="inlineStr">
+      <c r="J204" s="19" t="inlineStr">
         <is>
           <t>...Oh, and by the way, you can also process stones
 into "Cut Stone", so keep that in mind too.</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="K204" t="inlineStr">
         <is>
           <t>... Ah, e a propósito, você também pode processar pedras em “Pedra Cortada”, portanto, lembre-se disso também.</t>
         </is>
       </c>
     </row>
+    <row r="205" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B205" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
     <row r="206" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B206" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A207" s="19" t="inlineStr">
+      <c r="A206" s="19" t="inlineStr">
         <is>
           <t>hardness</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="209" ht="12.8" customFormat="1" customHeight="1" s="15">
+    <row r="207" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="208" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H208" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="I208" s="19" t="inlineStr">
+        <is>
+          <t>よしよ～し、道具を作ったのね。</t>
+        </is>
+      </c>
+      <c r="J208" s="25" t="inlineStr">
+        <is>
+          <t>Good, you made a tool!</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Muito bem, você criou uma ferramenta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="H209" s="15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I209" s="19" t="inlineStr">
         <is>
-          <t>よしよ～し、道具を作ったのね。</t>
+          <t>全てのアイテムは、何らかの「素材」からできている。
+そして、「素材」にはそれぞれ特徴があるの。</t>
         </is>
       </c>
       <c r="J209" s="25" t="inlineStr">
         <is>
-          <t>Good, you made a tool!</t>
+          <t>All items are made from some kind of "material".
+And each material has its own characteristics.</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Muito bem, você criou uma ferramenta.</t>
+          <t>Todos os itens são feitos de algum tipo de “material”.
+E cada material tem suas próprias características.</t>
         </is>
       </c>
     </row>
     <row r="210" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="H210" s="15" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I210" s="19" t="inlineStr">
-        <is>
-          <t>全てのアイテムは、何らかの「素材」からできている。
-そして、「素材」にはそれぞれ特徴があるの。</t>
-        </is>
-      </c>
-      <c r="J210" s="25" t="inlineStr">
-        <is>
-          <t>All items are made from some kind of "material".
-And each material has its own characteristics.</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Todos os itens são feitos de algum tipo de “material”.
-E cada material tem suas próprias características.</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H211" s="15" t="n">
-        <v>112</v>
-      </c>
-      <c r="I211" s="19" t="inlineStr">
         <is>
           <t>例えば紙でできたアイテムは軽かったり
 鉄でできたアイテムは、重いけど燃えにくかったりってね。</t>
         </is>
       </c>
-      <c r="J211" s="25" t="inlineStr">
+      <c r="J210" s="25" t="inlineStr">
         <is>
           <t>For example, items made of paper are light,
 while items made of iron are heavy but hard to burn.</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K210" t="inlineStr">
         <is>
           <t>Por exemplo, itens feitos de papel são leves,
 enquanto itens feitos de ferro são pesados, mas difíceis de queimar.</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="46.25" customFormat="1" customHeight="1" s="15">
-      <c r="H212" s="15" t="n">
+    <row r="211" ht="46.25" customFormat="1" customHeight="1" s="15">
+      <c r="H211" s="15" t="n">
         <v>113</v>
       </c>
-      <c r="I212" s="19" t="inlineStr">
+      <c r="I211" s="19" t="inlineStr">
         <is>
           <t>素材の特徴の一つに「硬さ」というものがあって
 特につるはしのような道具では
@@ -5934,7 +5910,7 @@
 この「硬さ」が重要になってくるの。</t>
         </is>
       </c>
-      <c r="J212" s="25" t="inlineStr">
+      <c r="J211" s="25" t="inlineStr">
         <is>
           <t>One of the characteristics of materials is "hardness",
 which is especially important for tools like pickaxes.
@@ -5942,147 +5918,147 @@
 so this "hardness" is very crucial.</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="K211" t="inlineStr">
         <is>
           <t>Uma das características dos materiais é a “dureza”, que é especialmente importante para ferramentas como picaretas.
 A dureza do material determina o tipo de pedra ou minério que você pode minerar, portanto, essa "dureza" é muito importante.</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H213" s="15" t="n">
+    <row r="212" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H212" s="15" t="n">
         <v>114</v>
       </c>
-      <c r="I213" s="19" t="inlineStr">
+      <c r="I212" s="19" t="inlineStr">
         <is>
           <t>もし今のつるはしで掘れない石が出てきたら
 もっと硬い素材でつるはしを作り直してみるといいわ。</t>
         </is>
       </c>
-      <c r="J213" s="25" t="inlineStr">
+      <c r="J212" s="25" t="inlineStr">
         <is>
           <t>If you come across stones that your current pickaxe can’t mine,
 try making a new pickaxe with a harder material.</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="K212" t="inlineStr">
         <is>
           <t>Se você encontrar pedras que sua picareta atual não consegue minerar,
 tente criar uma nova picareta com um material mais duro.</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="23.85" customHeight="1" s="17">
-      <c r="H214" s="15" t="n">
+    <row r="213" ht="23.85" customHeight="1" s="17">
+      <c r="H213" s="15" t="n">
         <v>115</v>
       </c>
-      <c r="I214" s="19" t="inlineStr">
+      <c r="I213" s="19" t="inlineStr">
         <is>
           <t>まあ…採掘のスキルを上げまくって
 力ずくで掘っちゃってもいいんだけどね。</t>
         </is>
       </c>
-      <c r="J214" s="25" t="inlineStr">
+      <c r="J213" s="25" t="inlineStr">
         <is>
           <t>Well... you can actually level up your mining skills a lot and
 just power through it, but anyway, hehe.</t>
         </is>
       </c>
-      <c r="K214" s="15" t="inlineStr">
+      <c r="K213" s="15" t="inlineStr">
         <is>
           <t>Bem... na verdade, você pode aumentar muito o nível de suas habilidades de mineração e simplesmente ignorar isso, mas, de qualquer forma, hehe.</t>
         </is>
       </c>
     </row>
+    <row r="214" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B214" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
     <row r="215" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B215" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B216" s="19" t="n"/>
-    </row>
-    <row r="217" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="A217" s="19" t="inlineStr">
+      <c r="B215" s="19" t="n"/>
+    </row>
+    <row r="216" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="A216" s="19" t="inlineStr">
         <is>
           <t>middle_click</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="219" ht="12.8" customFormat="1" customHeight="1" s="15">
+    <row r="217" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="218" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H218" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="I218" s="19" t="inlineStr">
+        <is>
+          <t>よしよし、作業台を作れたのね。</t>
+        </is>
+      </c>
+      <c r="J218" s="25" t="inlineStr">
+        <is>
+          <t>Good, you've made the workbench.</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Ótimo, você fez a bancada de trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="H219" s="15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I219" s="19" t="inlineStr">
-        <is>
-          <t>よしよし、作業台を作れたのね。</t>
-        </is>
-      </c>
-      <c r="J219" s="25" t="inlineStr">
-        <is>
-          <t>Good, you've made the workbench.</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Ótimo, você fez a bancada de trabalho.</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H220" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="I220" s="19" t="inlineStr">
         <is>
           <t>キミに一つ重要なことを教えてあげる。
 一人前の冒険者になるためには、絶対覚えなきゃいけないこと…
 そう、「ミドルクリック」よ。</t>
         </is>
       </c>
-      <c r="J220" s="19" t="inlineStr">
+      <c r="J219" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Let me tell you something crucial for becoming a seasoned adventurer...
 Yes, it's the 'middle click'. </t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="K219" t="inlineStr">
         <is>
           <t>Vou lhe dizer algo crucial para se tornar um aventureiro experiente...
 Sim, é o “clique do meio”.</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H221" s="15" t="n">
+    <row r="220" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H220" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="I221" s="19" t="inlineStr">
+      <c r="I220" s="19" t="inlineStr">
         <is>
           <t>バックパックのアイテムや、マップ上の生物やアイテムは
 ミドルクリックすることで「干渉」することができるの。</t>
         </is>
       </c>
-      <c r="J221" s="19" t="inlineStr">
+      <c r="J220" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">By middle-clicking, you can 'interact' with items in your backpack,
 creatures, or objects on the map. </t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="K220" t="inlineStr">
         <is>
           <t>Ao clicar com o botão do meio, você pode “interagir” com itens da mochila, criaturas ou objetos no mapa.</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="64.15000000000001" customFormat="1" customHeight="1" s="15">
-      <c r="H222" s="15" t="n">
+    <row r="221" ht="64.15000000000001" customFormat="1" customHeight="1" s="15">
+      <c r="H221" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="I222" s="19" t="inlineStr">
+      <c r="I221" s="19" t="inlineStr">
         <is>
           <t>例えば邪魔な生物を蹴って動かしたり
 機械のスイッチを入れたり
@@ -6091,7 +6067,7 @@
 普段できない色々な行動が、ミドルクリックによって解放されるのよ。</t>
         </is>
       </c>
-      <c r="J222" s="19" t="inlineStr">
+      <c r="J221" s="19" t="inlineStr">
         <is>
           <t>You can do various actions like
 kicking away pesky creatures,
@@ -6101,7 +6077,7 @@
 It unleashes a whole range of actions that you can't usually do.</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>Você pode realizar várias ações, como
 chutar criaturas incômodas,
@@ -6112,25 +6088,25 @@
         </is>
       </c>
     </row>
-    <row r="223" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H223" s="15" t="n">
+    <row r="222" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H222" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="I223" s="19" t="inlineStr">
+      <c r="I222" s="19" t="inlineStr">
         <is>
           <t>さらに、家具や壁などを設置する時も
 ミドルクリックすれば、対象物を回転させることができる…
 これを知らない冒険者は、この世界では生きていけないわ。</t>
         </is>
       </c>
-      <c r="J223" s="19" t="inlineStr">
+      <c r="J222" s="19" t="inlineStr">
         <is>
           <t>Moreover, when placing furniture or walls,
 middle-clicking will also let you rotate them...
 Adventurers who don't know this won't survive in this world.</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="K222" t="inlineStr">
         <is>
           <t>Além disso, ao colocar móveis ou paredes,
 clicar com o botão do meio também permitirá que você os gire...
@@ -6138,334 +6114,334 @@
         </is>
       </c>
     </row>
+    <row r="223" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H223" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="I223" s="19" t="inlineStr">
+        <is>
+          <t>…いい？ ミドルクリック…覚えた？</t>
+        </is>
+      </c>
+      <c r="J223" s="19" t="inlineStr">
+        <is>
+          <t>Middle click... got it...?</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Clique do Meio... Entendeu?
+(Dá pra alterar no menu)</t>
+        </is>
+      </c>
+    </row>
     <row r="224" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H224" s="15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I224" s="19" t="inlineStr">
         <is>
-          <t>…いい？ ミドルクリック…覚えた？</t>
+          <t>…</t>
         </is>
       </c>
       <c r="J224" s="19" t="inlineStr">
         <is>
-          <t>Middle click... got it...?</t>
+          <t>...</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Clique do Meio... Entendeu?
-(Dá pra alterar no menu)</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H225" s="15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I225" s="19" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J225" s="19" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H226" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="I226" s="19" t="inlineStr">
         <is>
           <t>そうそう
 ミドルクリックはキーボードの「R」キーでも代用できるからね。</t>
         </is>
       </c>
-      <c r="J226" s="19" t="inlineStr">
+      <c r="J225" s="19" t="inlineStr">
         <is>
           <t>Yes, you can also use the 'R' key on your keyboard
 as a substitute for middle click...</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="K225" t="inlineStr">
         <is>
           <t>Ah, você também pode usar a tecla "R" do seu teclado
 como substituto do clique do meio...</t>
         </is>
       </c>
     </row>
+    <row r="226" ht="12.8" customHeight="1" s="17">
+      <c r="H226" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="I226" s="19" t="inlineStr">
+        <is>
+          <t>それでは、また…</t>
+        </is>
+      </c>
+      <c r="J226" s="19" t="inlineStr">
+        <is>
+          <t>Well then...I'll see you later...</t>
+        </is>
+      </c>
+      <c r="K226" s="15" t="inlineStr">
+        <is>
+          <t>Bem, então... Até mais tarde…</t>
+        </is>
+      </c>
+    </row>
     <row r="227" ht="12.8" customHeight="1" s="17">
-      <c r="H227" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="I227" s="19" t="inlineStr">
-        <is>
-          <t>それでは、また…</t>
-        </is>
-      </c>
-      <c r="J227" s="19" t="inlineStr">
-        <is>
-          <t>Well then...I'll see you later...</t>
-        </is>
-      </c>
-      <c r="K227" s="15" t="inlineStr">
-        <is>
-          <t>Bem, então... Até mais tarde…</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="12.8" customHeight="1" s="17">
-      <c r="B228" s="19" t="inlineStr">
+      <c r="B227" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K228" s="15" t="n"/>
-    </row>
+      <c r="K227" s="15" t="n"/>
+    </row>
+    <row r="228" ht="15.65" customHeight="1" s="17"/>
     <row r="229" ht="15.65" customHeight="1" s="17"/>
     <row r="230" ht="15.65" customHeight="1" s="17"/>
-    <row r="231" ht="15.65" customHeight="1" s="17"/>
-    <row r="232" ht="12.8" customHeight="1" s="17">
-      <c r="A232" s="15" t="inlineStr">
+    <row r="231" ht="12.8" customHeight="1" s="17">
+      <c r="A231" s="15" t="inlineStr">
         <is>
           <t>food</t>
         </is>
       </c>
     </row>
+    <row r="233" ht="12.8" customHeight="1" s="17">
+      <c r="H233" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="I233" s="19" t="inlineStr">
+        <is>
+          <t>わあ…きのこちょーだい？</t>
+        </is>
+      </c>
+      <c r="J233" s="25" t="inlineStr">
+        <is>
+          <t>Wow... Can I have some mushrooms?</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Nossa! Posso comer alguns cogumelos?</t>
+        </is>
+      </c>
+    </row>
     <row r="234" ht="12.8" customHeight="1" s="17">
+      <c r="B234" s="15" t="inlineStr">
+        <is>
+          <t>food2</t>
+        </is>
+      </c>
+      <c r="D234" s="15" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
       <c r="H234" s="15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I234" s="19" t="inlineStr">
         <is>
-          <t>わあ…きのこちょーだい？</t>
+          <t>ああ</t>
         </is>
       </c>
       <c r="J234" s="25" t="inlineStr">
         <is>
-          <t>Wow... Can I have some mushrooms?</t>
+          <t>Yes.</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Nossa! Posso comer alguns cogumelos?</t>
+          <t>Sim.</t>
         </is>
       </c>
     </row>
     <row r="235" ht="12.8" customHeight="1" s="17">
       <c r="B235" s="15" t="inlineStr">
         <is>
+          <t>food3</t>
+        </is>
+      </c>
+      <c r="D235" s="15" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="H235" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I235" s="19" t="inlineStr">
+        <is>
+          <t>いや</t>
+        </is>
+      </c>
+      <c r="J235" s="25" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Não.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="12.8" customHeight="1" s="17">
+      <c r="I236" s="19" t="n"/>
+      <c r="J236" s="25" t="n"/>
+    </row>
+    <row r="237" ht="12.8" customHeight="1" s="17">
+      <c r="A237" s="15" t="inlineStr">
+        <is>
           <t>food2</t>
         </is>
       </c>
-      <c r="D235" s="15" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="H235" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="I235" s="19" t="inlineStr">
-        <is>
-          <t>ああ</t>
-        </is>
-      </c>
-      <c r="J235" s="25" t="inlineStr">
-        <is>
-          <t>Yes.</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>Sim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="12.8" customHeight="1" s="17">
-      <c r="B236" s="15" t="inlineStr">
-        <is>
-          <t>food3</t>
-        </is>
-      </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="H236" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="I236" s="19" t="inlineStr">
-        <is>
-          <t>いや</t>
-        </is>
-      </c>
-      <c r="J236" s="25" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>Não.</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="12.8" customHeight="1" s="17">
       <c r="I237" s="19" t="n"/>
       <c r="J237" s="25" t="n"/>
     </row>
-    <row r="238" ht="12.8" customHeight="1" s="17">
-      <c r="A238" s="15" t="inlineStr">
-        <is>
-          <t>food2</t>
-        </is>
-      </c>
-      <c r="I238" s="19" t="n"/>
-      <c r="J238" s="25" t="n"/>
-    </row>
-    <row r="239" ht="22.35" customHeight="1" s="17">
-      <c r="H239" s="15" t="n">
+    <row r="238" ht="22.35" customHeight="1" s="17">
+      <c r="H238" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="I239" s="19" t="inlineStr">
+      <c r="I238" s="19" t="inlineStr">
         <is>
           <t>もぐもぐもぐ。おいしい～。
 これ私の大好物なの。覚えておいてね！</t>
         </is>
       </c>
-      <c r="J239" s="19" t="inlineStr">
+      <c r="J238" s="19" t="inlineStr">
         <is>
           <t>Munch munch munch. Yummy.
 These are my favorite! Remember that, okay?</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="K238" t="inlineStr">
         <is>
           <t>Munch munch munch. Que delícia.
 Estes são os meus favoritos! Lembre-se disso, ok?</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H240" s="15" t="n">
+    <row r="239" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H239" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="I240" s="19" t="inlineStr">
+      <c r="I239" s="19" t="inlineStr">
         <is>
           <t>きのこは美味しいけど、腹持ちがよくないし
 時間がたつと腐ってしまうのが難点ね。</t>
         </is>
       </c>
-      <c r="J240" s="19" t="inlineStr">
+      <c r="J239" s="19" t="inlineStr">
         <is>
           <t>Mushrooms are tasty, but they don't keep you full for long
 and the fact that they spoil over time is a downside.</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="K239" t="inlineStr">
         <is>
           <t>Os cogumelos são saborosos, mas não o mantêm saciado por muito tempo
 e o fato de que eles estragam com o tempo é uma desvantagem.</t>
         </is>
       </c>
     </row>
+    <row r="240" ht="22.35" customHeight="1" s="17">
+      <c r="H240" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="I240" s="19" t="inlineStr">
+        <is>
+          <t>そう、食べ物はずっと置いておくと腐ってしまうのよ。
+知らなかった？</t>
+        </is>
+      </c>
+      <c r="J240" s="19" t="inlineStr">
+        <is>
+          <t>Yes, food spoils if you leave it out too long.
+You didn't know that?</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Sim, os alimentos estragam se você os deixar no "chão" ou na "bolsa" por muito tempo.
+Você não sabia disso?</t>
+        </is>
+      </c>
+    </row>
     <row r="241" ht="22.35" customHeight="1" s="17">
       <c r="H241" s="15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I241" s="19" t="inlineStr">
         <is>
-          <t>そう、食べ物はずっと置いておくと腐ってしまうのよ。
-知らなかった？</t>
+          <t>当たり前だけど、腐ったものを食べるとお腹を壊すから
+絶対食べてはだめよ。</t>
         </is>
       </c>
       <c r="J241" s="19" t="inlineStr">
         <is>
-          <t>Yes, food spoils if you leave it out too long.
-You didn't know that?</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Sim, os alimentos estragam se você os deixar no "chão" ou na "bolsa" por muito tempo.
-Você não sabia disso?</t>
+          <t>Of course, eating spoiled food can make you sick
+so you should never eat it.</t>
+        </is>
+      </c>
+      <c r="K241" s="15" t="inlineStr">
+        <is>
+          <t>É claro que comer alimentos estragados pode deixá-lo doente, portanto, você nunca deve comê-los.</t>
         </is>
       </c>
     </row>
     <row r="242" ht="22.35" customHeight="1" s="17">
       <c r="H242" s="15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I242" s="19" t="inlineStr">
-        <is>
-          <t>当たり前だけど、腐ったものを食べるとお腹を壊すから
-絶対食べてはだめよ。</t>
-        </is>
-      </c>
-      <c r="J242" s="19" t="inlineStr">
-        <is>
-          <t>Of course, eating spoiled food can make you sick
-so you should never eat it.</t>
-        </is>
-      </c>
-      <c r="K242" s="15" t="inlineStr">
-        <is>
-          <t>É claro que comer alimentos estragados pode deixá-lo doente, portanto, você nunca deve comê-los.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="22.35" customHeight="1" s="17">
-      <c r="H243" s="15" t="n">
-        <v>42</v>
-      </c>
-      <c r="I243" s="19" t="inlineStr">
         <is>
           <t>魚や生ものは特に腐りやすいわね。
 逆に、木の実や調理した食料はかなり日持ちするの。</t>
         </is>
       </c>
-      <c r="J243" s="19" t="inlineStr">
+      <c r="J242" s="19" t="inlineStr">
         <is>
           <t>Fish and raw food spoil especially easily
 but nuts and cooked food can last quite a while.</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="K242" t="inlineStr">
         <is>
           <t>Peixes e alimentos crus estragam com facilidade,
 mas nozes e comida cozida duram bastante tempo.</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="32.8" customHeight="1" s="17">
-      <c r="H244" s="15" t="n">
+    <row r="243" ht="32.8" customHeight="1" s="17">
+      <c r="H243" s="15" t="n">
         <v>43</v>
       </c>
-      <c r="I244" s="19" t="inlineStr">
+      <c r="I243" s="19" t="inlineStr">
         <is>
           <t>石臼があれば、キブルみたいな全く腐らない料理も作れるのよ。
 長旅の前には、十分な保存食を用意しておくのが
 冒険者の鉄則ね。</t>
         </is>
       </c>
-      <c r="J244" s="19" t="inlineStr">
+      <c r="J243" s="19" t="inlineStr">
         <is>
           <t>With a millstone, you can even make meals like kibble that never spoil.
 Remember to prepare enough non-perishable food before a long journey.
 It's a golden rule for adventurers.</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="K243" t="inlineStr">
         <is>
           <t>Com um Moinho de Pedra, você pode até fazer refeições como ração que nunca estraga.
 Lembre-se de levar comida não perecível suficiente antes de uma longa jornada.
@@ -6473,99 +6449,99 @@
         </is>
       </c>
     </row>
+    <row r="244" ht="12.8" customHeight="1" s="17">
+      <c r="B244" s="15" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="J244" s="19" t="n"/>
+    </row>
     <row r="245" ht="12.8" customHeight="1" s="17">
-      <c r="B245" s="15" t="inlineStr">
+      <c r="A245" s="15" t="inlineStr">
+        <is>
+          <t>food3</t>
+        </is>
+      </c>
+      <c r="J245" s="19" t="n"/>
+    </row>
+    <row r="246" ht="12.8" customHeight="1" s="17">
+      <c r="H246" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="I246" s="19" t="inlineStr">
+        <is>
+          <t>ケチ！</t>
+        </is>
+      </c>
+      <c r="J246" s="25" t="inlineStr">
+        <is>
+          <t>Cheap!</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Que barato!</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B247" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="J245" s="19" t="n"/>
-    </row>
-    <row r="246" ht="12.8" customHeight="1" s="17">
-      <c r="A246" s="15" t="inlineStr">
-        <is>
-          <t>food3</t>
-        </is>
-      </c>
-      <c r="J246" s="19" t="n"/>
-    </row>
-    <row r="247" ht="12.8" customHeight="1" s="17">
-      <c r="H247" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="I247" s="19" t="inlineStr">
-        <is>
-          <t>ケチ！</t>
-        </is>
-      </c>
-      <c r="J247" s="25" t="inlineStr">
-        <is>
-          <t>Cheap!</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>Que barato!</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B248" s="15" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="250" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A250" s="19" t="inlineStr">
+    </row>
+    <row r="248" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="249" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A249" s="19" t="inlineStr">
         <is>
           <t>tinker</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H251" s="15" t="n">
+    <row r="250" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H250" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="I251" s="19" t="inlineStr">
+      <c r="I250" s="19" t="inlineStr">
         <is>
           <t>わぁ、見てみて、行商人達がいっぱい！
 色んなものを売ってるよ！</t>
         </is>
       </c>
-      <c r="J251" s="25" t="inlineStr">
+      <c r="J250" s="25" t="inlineStr">
         <is>
           <t>Wow, look at all the tinkers!
 They're selling all kinds of things!</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K250" t="inlineStr">
         <is>
           <t>Uau, olha quantos mercadores!_x000D_
 Eles estão vendendo todo tipo de coisa!</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H252" s="15" t="n">
+    <row r="251" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H251" s="15" t="n">
         <v>94</v>
       </c>
-      <c r="I252" s="19" t="inlineStr">
+      <c r="I251" s="19" t="inlineStr">
         <is>
           <t>まるで小さな街の一角のようね。
 ほら、あの掲示板
 冒険者向けの依頼も掲載されているみたい。</t>
         </is>
       </c>
-      <c r="J252" s="19" t="inlineStr">
+      <c r="J251" s="19" t="inlineStr">
         <is>
           <t>It's like a little corner of a town.
 Look, that notice board seems to have
 quests for adventurers posted on it.</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="K251" t="inlineStr">
         <is>
           <t>Parece um pequeno canto de uma cidade._x000D_
 Olha, aquele quadro de avisos parece ter_x000D_
@@ -6573,25 +6549,25 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H253" s="15" t="n">
+    <row r="252" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H252" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="I253" s="19" t="inlineStr">
+      <c r="I252" s="19" t="inlineStr">
         <is>
           <t>依頼を達成すると、様々な報酬がもらえるから
 掲示板を見かけたらこまめにチェック！
 ★の数が多い依頼は難しいから気を付けて。</t>
         </is>
       </c>
-      <c r="J253" s="19" t="inlineStr">
+      <c r="J252" s="19" t="inlineStr">
         <is>
           <t>Completing quests earns you various rewards,
 so make sure to check the notice board regularly!
 Be careful with quests that have many ★. They're more difficult.</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="K252" t="inlineStr">
         <is>
           <t>Completar missões rende várias recompensas,_x000D_
 então certifique-se de verificar o quadro de avisos regularmente!_x000D_
@@ -6599,25 +6575,25 @@
         </is>
       </c>
     </row>
-    <row r="254" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H254" s="15" t="n">
+    <row r="253" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H253" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="I254" s="19" t="inlineStr">
+      <c r="I253" s="19" t="inlineStr">
         <is>
           <t>あら、この停泊地、癒し手もいるのね。
 癒し手は状態異常を治療してくれるし、あっちの魔術師は
 未鑑定のアイテムを鑑定してくれるわ…まあ、タダじゃないけどね。</t>
         </is>
       </c>
-      <c r="J254" s="19" t="inlineStr">
+      <c r="J253" s="19" t="inlineStr">
         <is>
           <t>Oh, this camp also has a healer.
 The healer can cure status ailments, and the mage there
 can appraise unidentified items...though it does cost money.</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="K253" t="inlineStr">
         <is>
           <t>Oh, este acampamento também tem um curandeiro.
 O curandeiro pode curar estados negativos, e o mago ali
@@ -6625,65 +6601,65 @@
         </is>
       </c>
     </row>
+    <row r="254" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H254" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="I254" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J254" s="19" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
     <row r="255" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H255" s="15" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I255" s="19" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>あのキャラバンの隊長…</t>
         </is>
       </c>
       <c r="J255" s="19" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>That caravan leader...</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>...</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Aquele líder da caravana...</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="H256" s="15" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I256" s="19" t="inlineStr">
-        <is>
-          <t>あのキャラバンの隊長…</t>
-        </is>
-      </c>
-      <c r="J256" s="19" t="inlineStr">
-        <is>
-          <t>That caravan leader...</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>Aquele líder da caravana...</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H257" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="I257" s="19" t="inlineStr">
         <is>
           <t>か…かわいい！
 猫のかぶりものをかぶってるわ。
 ねえ、ちょっと寄っていこ？</t>
         </is>
       </c>
-      <c r="J257" s="19" t="inlineStr">
+      <c r="J256" s="19" t="inlineStr">
         <is>
           <t>S...so cute!
 He's wearing a cat costume.
 Hey, let's go check him?</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="K256" t="inlineStr">
         <is>
           <t>Tão fofo!
 Ele está vestindo uma fantasia de gato.
@@ -6691,52 +6667,52 @@
         </is>
       </c>
     </row>
+    <row r="257" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="I257" s="19" t="n"/>
+      <c r="J257" s="19" t="n"/>
+    </row>
     <row r="258" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="I258" s="19" t="n"/>
-      <c r="J258" s="19" t="n"/>
+      <c r="B258" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B259" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A260" s="19" t="inlineStr">
+      <c r="A259" s="19" t="inlineStr">
         <is>
           <t>town</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H261" s="15" t="n">
+    <row r="260" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H260" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="I261" s="19" t="inlineStr">
+      <c r="I260" s="19" t="inlineStr">
         <is>
           <t>街だ～！
 人の往来で辺りに活気があるわね。</t>
         </is>
       </c>
-      <c r="J261" s="25" t="inlineStr">
+      <c r="J260" s="25" t="inlineStr">
         <is>
           <t>It's a town!
 So lively with all the people bustling around.</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="K260" t="inlineStr">
         <is>
           <t>É uma cidade!
 Tão animada com todas as pessoas se movimentando.</t>
         </is>
       </c>
     </row>
-    <row r="262" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H262" s="15" t="n">
+    <row r="261" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H261" s="15" t="n">
         <v>101</v>
       </c>
-      <c r="I262" s="19" t="inlineStr">
+      <c r="I261" s="19" t="inlineStr">
         <is>
           <t>アイテムの売買、訓練、交易、賭博、依頼、回復…
 街には色々なサービスが揃ってる。
@@ -6744,7 +6720,7 @@
 ガードに話しかければ、道案内をしてもらえるわ。えへへ。</t>
         </is>
       </c>
-      <c r="J262" s="19" t="inlineStr">
+      <c r="J261" s="19" t="inlineStr">
         <is>
           <t>Buying and selling, training, trading, gambling, quests, healing...
 There are so many services here.
@@ -6752,7 +6728,7 @@
 Just talk to a guard, and they'll guide you. Hehe.</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="K261" t="inlineStr">
         <is>
           <t>Comprar e vender, treinar, negociar, apostar, missões, cura...
 Há tantos serviços aqui.
@@ -6761,25 +6737,25 @@
         </is>
       </c>
     </row>
-    <row r="263" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H263" s="15" t="n">
+    <row r="262" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H262" s="15" t="n">
         <v>102</v>
       </c>
-      <c r="I263" s="19" t="inlineStr">
+      <c r="I262" s="19" t="inlineStr">
         <is>
           <t>当然だけど、ノースティリスにある街は
 街ごとに発展度も違えば、売っている物も
 受けられるサービスも、訓練できるスキルも違うの。</t>
         </is>
       </c>
-      <c r="J263" s="19" t="inlineStr">
+      <c r="J262" s="19" t="inlineStr">
         <is>
           <t>Of course, every town in North Tyris is different.
 They vary in development, the items they sell,
 the services they offer, and the skills you can train.</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K262" t="inlineStr">
         <is>
           <t>Claro, cada cidade em North Tyris é diferente.
 Elas variam no desenvolvimento, nos itens que vendem,
@@ -6787,114 +6763,114 @@
         </is>
       </c>
     </row>
-    <row r="264" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H264" s="15" t="n">
+    <row r="263" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H263" s="15" t="n">
         <v>103</v>
       </c>
-      <c r="I264" s="19" t="inlineStr">
+      <c r="I263" s="19" t="inlineStr">
         <is>
           <t>掲示板に掲載される依頼も、街によって傾向が異なるから
 色んな街を巡ってみるのもいいわね。</t>
         </is>
       </c>
-      <c r="J264" s="19" t="inlineStr">
+      <c r="J263" s="19" t="inlineStr">
         <is>
           <t>The quests posted on the bulletin board also differ from one to another,
 so it will be a good idea to explore various towns.</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>As missões postadas no quadro de avisos também diferem de uma cidade para outra, então pode ser uma boa ideia explorar várias cidades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H264" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I264" s="19" t="inlineStr">
+        <is>
+          <t>今はともかく、この街を探索してみましょ？</t>
+        </is>
+      </c>
+      <c r="J264" s="19" t="inlineStr">
+        <is>
+          <t>But, for now, how about we explore this town?</t>
+        </is>
+      </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>As missões postadas no quadro de avisos também diferem de uma cidade para outra, então pode ser uma boa ideia explorar várias cidades.</t>
+          <t>Mas, por enquanto, que tal explorarmos essa cidade?</t>
         </is>
       </c>
     </row>
     <row r="265" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H265" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="I265" s="19" t="inlineStr">
-        <is>
-          <t>今はともかく、この街を探索してみましょ？</t>
-        </is>
-      </c>
-      <c r="J265" s="19" t="inlineStr">
-        <is>
-          <t>But, for now, how about we explore this town?</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Mas, por enquanto, que tal explorarmos essa cidade?</t>
-        </is>
-      </c>
+      <c r="I265" s="19" t="n"/>
+      <c r="J265" s="19" t="n"/>
     </row>
     <row r="266" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="I266" s="19" t="n"/>
-      <c r="J266" s="19" t="n"/>
+      <c r="B266" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B267" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B267" s="19" t="n"/>
     </row>
     <row r="268" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B268" s="19" t="n"/>
+      <c r="A268" s="19" t="inlineStr">
+        <is>
+          <t>karma</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A269" s="19" t="inlineStr">
-        <is>
-          <t>karma</t>
+      <c r="H269" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="I269" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J269" s="25" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="270" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H270" s="15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I270" s="19" t="inlineStr">
         <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J270" s="25" t="inlineStr">
-        <is>
-          <t>...</t>
+          <t>今、悪いことしたでしょ…？</t>
+        </is>
+      </c>
+      <c r="J270" s="19" t="inlineStr">
+        <is>
+          <t>Did you just do something bad...?</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>...</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Você acabou de fazer algo ruim?</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="43.25" customFormat="1" customHeight="1" s="15">
       <c r="H271" s="15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I271" s="19" t="inlineStr">
-        <is>
-          <t>今、悪いことしたでしょ…？</t>
-        </is>
-      </c>
-      <c r="J271" s="19" t="inlineStr">
-        <is>
-          <t>Did you just do something bad...?</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>Você acabou de fazer algo ruim?</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H272" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="I272" s="19" t="inlineStr">
         <is>
           <t>ええ…キミのカルマが下がるのを感じたのよ。
 この世界では、悪いことをするとカルマが下がって
@@ -6902,7 +6878,7 @@
 …犯罪者になると、生きていくのが大変よ。</t>
         </is>
       </c>
-      <c r="J272" s="19" t="inlineStr">
+      <c r="J271" s="19" t="inlineStr">
         <is>
           <t>Yes... I felt your karma drop.
 In this world, your karma decreases if you do bad things,
@@ -6910,7 +6886,7 @@
 ... Becoming a criminal makes life very difficult.</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="K271" t="inlineStr">
         <is>
           <t>Sim... Eu senti seu carma cair.
 Neste mundo, seu carma diminui se você fizer coisas ruins,
@@ -6919,34 +6895,34 @@
         </is>
       </c>
     </row>
-    <row r="273" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H273" s="15" t="n">
+    <row r="272" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H272" s="15" t="n">
         <v>82</v>
       </c>
-      <c r="I273" s="19" t="inlineStr">
+      <c r="I272" s="19" t="inlineStr">
         <is>
           <t>依頼をこなしたり、落とし物を届けたり
 日ごろから善い行いを心がけて、カルマを高めていってね。</t>
         </is>
       </c>
-      <c r="J273" s="19" t="inlineStr">
+      <c r="J272" s="19" t="inlineStr">
         <is>
           <t>Complete quests, return lost items,
 and always strive to do good deeds to increase your karma.</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K272" t="inlineStr">
         <is>
           <t>Complete missões, devolva itens perdidos,
 e sempre se esforce para fazer boas ações para aumentar seu carma.</t>
         </is>
       </c>
     </row>
-    <row r="274" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H274" s="15" t="n">
+    <row r="273" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H273" s="15" t="n">
         <v>83</v>
       </c>
-      <c r="I274" s="19" t="inlineStr">
+      <c r="I273" s="19" t="inlineStr">
         <is>
           <t>…ちなみに
 この世界で最も重い罪は税金の滞納よ。
@@ -6954,14 +6930,14 @@
 命を狙われるようになるわ。</t>
         </is>
       </c>
-      <c r="J274" s="19" t="inlineStr">
+      <c r="J273" s="19" t="inlineStr">
         <is>
           <t>...By the way, the most serious crime in this world is tax evasion.
 If you don’t pay your taxes for four months,
 you’ll be immediately wanted, and your life will be in danger.</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="K273" t="inlineStr">
         <is>
           <t>... A propósito, o crime mais grave do mundo é a sonegação de impostos.
 Se você não pagar seus impostos por quatro meses,
@@ -6969,129 +6945,129 @@
         </is>
       </c>
     </row>
-    <row r="275" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H275" s="15" t="n">
+    <row r="274" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H274" s="15" t="n">
         <v>84</v>
       </c>
-      <c r="I275" s="19" t="inlineStr">
+      <c r="I274" s="19" t="inlineStr">
         <is>
           <t>くれぐれも気を付けて…</t>
         </is>
       </c>
-      <c r="J275" s="19" t="inlineStr">
+      <c r="J274" s="19" t="inlineStr">
         <is>
           <t>So...be careful, okay?</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="K274" t="inlineStr">
         <is>
           <t>Portanto... Tome cuidado, ok?</t>
         </is>
       </c>
     </row>
+    <row r="275" ht="12.8" customHeight="1" s="17">
+      <c r="I275" s="19" t="n"/>
+      <c r="J275" s="19" t="n"/>
+      <c r="K275" s="15" t="n"/>
+    </row>
     <row r="276" ht="12.8" customHeight="1" s="17">
-      <c r="I276" s="19" t="n"/>
-      <c r="J276" s="19" t="n"/>
+      <c r="B276" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="K276" s="15" t="n"/>
     </row>
     <row r="277" ht="12.8" customHeight="1" s="17">
-      <c r="B277" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B277" s="19" t="n"/>
       <c r="K277" s="15" t="n"/>
     </row>
     <row r="278" ht="12.8" customHeight="1" s="17">
-      <c r="B278" s="19" t="n"/>
+      <c r="A278" s="19" t="inlineStr">
+        <is>
+          <t>criminal</t>
+        </is>
+      </c>
       <c r="K278" s="15" t="n"/>
     </row>
     <row r="279" ht="12.8" customHeight="1" s="17">
-      <c r="A279" s="19" t="inlineStr">
-        <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="K279" s="15" t="n"/>
-    </row>
-    <row r="280" ht="12.8" customHeight="1" s="17">
+      <c r="H279" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="I279" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J279" s="25" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K279" s="15" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="22.35" customHeight="1" s="17">
       <c r="H280" s="15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I280" s="19" t="inlineStr">
         <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J280" s="25" t="inlineStr">
-        <is>
-          <t>...</t>
+          <t>イヤ…！
+近づかないで、変態！</t>
+        </is>
+      </c>
+      <c r="J280" s="19" t="inlineStr">
+        <is>
+          <t>No...!
+Stay away from me, you pervert!</t>
         </is>
       </c>
       <c r="K280" s="15" t="inlineStr">
         <is>
-          <t>...</t>
+          <t xml:space="preserve">Não...!  _x000D_
+Fique longe de mim, seu pervertido!  </t>
         </is>
       </c>
     </row>
     <row r="281" ht="22.35" customHeight="1" s="17">
       <c r="H281" s="15" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I281" s="19" t="inlineStr">
-        <is>
-          <t>イヤ…！
-近づかないで、変態！</t>
-        </is>
-      </c>
-      <c r="J281" s="19" t="inlineStr">
-        <is>
-          <t>No...!
-Stay away from me, you pervert!</t>
-        </is>
-      </c>
-      <c r="K281" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não...!  _x000D_
-Fique longe de mim, seu pervertido!  </t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="22.35" customHeight="1" s="17">
-      <c r="H282" s="15" t="n">
-        <v>87</v>
-      </c>
-      <c r="I282" s="19" t="inlineStr">
         <is>
           <t>犯罪者に身を堕としてしまうなんて、
 キミのことを見損なったわ。</t>
         </is>
       </c>
-      <c r="J282" s="19" t="inlineStr">
+      <c r="J281" s="19" t="inlineStr">
         <is>
           <t>I can't believe you've become a criminal.
 I'm really disappointed in you.</t>
         </is>
       </c>
-      <c r="K282" s="15" t="inlineStr">
+      <c r="K281" s="15" t="inlineStr">
         <is>
           <t>Não acredito que você tenha se tornado um criminoso.
 Estou muito decepcionada com você.</t>
         </is>
       </c>
     </row>
-    <row r="283" ht="43.25" customHeight="1" s="17">
-      <c r="H283" s="15" t="n">
+    <row r="282" ht="43.25" customHeight="1" s="17">
+      <c r="H282" s="15" t="n">
         <v>88</v>
       </c>
-      <c r="I283" s="19" t="inlineStr">
+      <c r="I282" s="19" t="inlineStr">
         <is>
           <t>…そう、カルマが0を下回ると、キミは指名手配されてしまう。
 ガードから追いかけられ、商人との取引も断られ、妹達から白い目で見られ
 社会の敵として、一生みじめに暮らすのよ！</t>
         </is>
       </c>
-      <c r="J283" s="19" t="inlineStr">
+      <c r="J282" s="19" t="inlineStr">
         <is>
           <t>…That's right, if your karma drops below zero, you'll be wanted.
 Guards will come chasing you, merchants will refuse to trade with you,
@@ -7099,7 +7075,7 @@
 You'll live a miserable life as an enemy of society!</t>
         </is>
       </c>
-      <c r="K283" s="15" t="inlineStr">
+      <c r="K282" s="15" t="inlineStr">
         <is>
           <t>... É isso mesmo, se o seu carma cair abaixo de zero, você será procurado.
 Os guardas virão atrás de você, os comerciantes se recusarão a negociar com você,
@@ -7108,25 +7084,25 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="32.8" customHeight="1" s="17">
-      <c r="H284" s="15" t="n">
+    <row r="283" ht="32.8" customHeight="1" s="17">
+      <c r="H283" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="I284" s="19" t="inlineStr">
+      <c r="I283" s="19" t="inlineStr">
         <is>
           <t>はぁ…大丈夫、キミにもまだ、更生の道は残されているわ。
 カルマがマイナスの時、カルマは少しずつ上昇していくの。
 悪事を止めて、大人しく待っていれば、いつかはほとぼりも冷める…</t>
         </is>
       </c>
-      <c r="J284" s="19" t="inlineStr">
+      <c r="J283" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Sigh... It's okay, there's still a path to redemption for you.
 When your karma is negative, it will slowly increase over time.
 If you stop committing crimes and patiently wait, things will eventually calm down. </t>
         </is>
       </c>
-      <c r="K284" s="15" t="inlineStr">
+      <c r="K283" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">*suspiro* - Tudo bem, ainda há um caminho para a redenção.  
 Quando seu carma for negativo, ele aumentará lentamente com o tempo.  
@@ -7134,126 +7110,126 @@
         </is>
       </c>
     </row>
+    <row r="284" ht="22.35" customHeight="1" s="17">
+      <c r="H284" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="I284" s="19" t="inlineStr">
+        <is>
+          <t>法律が存在しない、ならず者たちの街ダルフィなら
+税金を納めることもできるし、商人も取引をしてくれるわ。</t>
+        </is>
+      </c>
+      <c r="J284" s="19" t="inlineStr">
+        <is>
+          <t>In the rogue town of Derphy, where there are no laws,
+you can pay your taxes, and merchants will still trade with you.</t>
+        </is>
+      </c>
+      <c r="K284" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Na cidade dos foras da lei, Derphy, onde não há leis,  _x000D_
+você pode pagar seus impostos, e os mercadores ainda negociarão com você.  </t>
+        </is>
+      </c>
+    </row>
     <row r="285" ht="22.35" customHeight="1" s="17">
       <c r="H285" s="15" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I285" s="19" t="inlineStr">
-        <is>
-          <t>法律が存在しない、ならず者たちの街ダルフィなら
-税金を納めることもできるし、商人も取引をしてくれるわ。</t>
-        </is>
-      </c>
-      <c r="J285" s="19" t="inlineStr">
-        <is>
-          <t>In the rogue town of Derphy, where there are no laws,
-you can pay your taxes, and merchants will still trade with you.</t>
-        </is>
-      </c>
-      <c r="K285" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Na cidade dos foras da lei, Derphy, onde não há leis,  _x000D_
-você pode pagar seus impostos, e os mercadores ainda negociarão com você.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="22.35" customHeight="1" s="17">
-      <c r="H286" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="I286" s="19" t="inlineStr">
         <is>
           <t>大丈夫、キミのこと信じてるから
 しっかり罪を償って戻ってきてね。</t>
         </is>
       </c>
-      <c r="J286" s="19" t="inlineStr">
+      <c r="J285" s="19" t="inlineStr">
         <is>
           <t>Don't worry, I believe in you.
 Make sure you atone for your sins and come back.</t>
         </is>
       </c>
-      <c r="K286" s="15" t="inlineStr">
+      <c r="K285" s="15" t="inlineStr">
         <is>
           <t>Não se preocupe, eu acredito em você.
 Certifique-se de arrepender-se de seus pecados e voltar.</t>
         </is>
       </c>
     </row>
+    <row r="286" ht="12.8" customHeight="1" s="17">
+      <c r="H286" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="I286" s="19" t="inlineStr">
+        <is>
+          <t>それでは…</t>
+        </is>
+      </c>
+      <c r="J286" s="19" t="inlineStr">
+        <is>
+          <t>Until then...</t>
+        </is>
+      </c>
+      <c r="K286" s="15" t="inlineStr">
+        <is>
+          <t>Até lá...</t>
+        </is>
+      </c>
+    </row>
     <row r="287" ht="12.8" customHeight="1" s="17">
-      <c r="H287" s="15" t="n">
-        <v>92</v>
-      </c>
-      <c r="I287" s="19" t="inlineStr">
-        <is>
-          <t>それでは…</t>
-        </is>
-      </c>
-      <c r="J287" s="19" t="inlineStr">
-        <is>
-          <t>Until then...</t>
-        </is>
-      </c>
-      <c r="K287" s="15" t="inlineStr">
-        <is>
-          <t>Até lá...</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="12.8" customHeight="1" s="17">
-      <c r="B288" s="19" t="inlineStr">
+      <c r="B287" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K288" s="15" t="n"/>
+      <c r="K287" s="15" t="n"/>
+    </row>
+    <row r="289" ht="12.8" customHeight="1" s="17">
+      <c r="A289" s="19" t="inlineStr">
+        <is>
+          <t>ether</t>
+        </is>
+      </c>
+      <c r="K289" s="15" t="n"/>
     </row>
     <row r="290" ht="12.8" customHeight="1" s="17">
-      <c r="A290" s="19" t="inlineStr">
-        <is>
-          <t>ether</t>
-        </is>
-      </c>
-      <c r="K290" s="15" t="n"/>
-    </row>
-    <row r="291" ht="12.8" customHeight="1" s="17">
+      <c r="H290" s="15" t="n">
+        <v>74</v>
+      </c>
+      <c r="I290" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">キミもとうとう病におかされてしまったのね… </t>
+        </is>
+      </c>
+      <c r="J290" s="25" t="inlineStr">
+        <is>
+          <t>So, you've finally been afflicted by the illness...</t>
+        </is>
+      </c>
+      <c r="K290" s="15" t="inlineStr">
+        <is>
+          <t>Você finalmente ficou doente...</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="32.8" customHeight="1" s="17">
       <c r="H291" s="15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I291" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">キミもとうとう病におかされてしまったのね… </t>
-        </is>
-      </c>
-      <c r="J291" s="25" t="inlineStr">
-        <is>
-          <t>So, you've finally been afflicted by the illness...</t>
-        </is>
-      </c>
-      <c r="K291" s="15" t="inlineStr">
-        <is>
-          <t>Você finalmente ficou doente...</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="32.8" customHeight="1" s="17">
-      <c r="H292" s="15" t="n">
-        <v>75</v>
-      </c>
-      <c r="I292" s="19" t="inlineStr">
         <is>
           <t>驚かないでいいの。
 何もしないでも、エーテルの侵食は時間と供に緩やかに進んでいくのよ。</t>
         </is>
       </c>
-      <c r="J292" s="19" t="inlineStr">
+      <c r="J291" s="19" t="inlineStr">
         <is>
           <t>Don't be surprised.
 Even if you do nothing, the ether's encroachment
 will gradually progress over time.</t>
         </is>
       </c>
-      <c r="K292" s="15" t="inlineStr">
+      <c r="K291" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Não fique surpreso.  
 Mesmo que você não faça nada, a invasão do éter  
@@ -7261,18 +7237,18 @@
         </is>
       </c>
     </row>
-    <row r="293" ht="43.25" customHeight="1" s="17">
-      <c r="H293" s="15" t="n">
+    <row r="292" ht="43.25" customHeight="1" s="17">
+      <c r="H292" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="I293" s="19" t="inlineStr">
+      <c r="I292" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">キミの症状はまだまだ無視してかまわない程度だけど
 病気を放っておくと、症状はどんどん悪化して最後には死んじゃうの。
 …病を遅らせる何らかの方法を見つけなくてはね。 </t>
         </is>
       </c>
-      <c r="J293" s="19" t="inlineStr">
+      <c r="J292" s="19" t="inlineStr">
         <is>
           <t>Your symptoms are still minor and can be ignored for now,
 but if you leave the illness untreated,
@@ -7280,7 +7256,7 @@
 ...We need to find some way to slow down the disease.</t>
         </is>
       </c>
-      <c r="K293" s="15" t="inlineStr">
+      <c r="K292" s="15" t="inlineStr">
         <is>
           <t>Seus sintomas ainda são leves e podem ser ignorados por enquanto,
 mas se você deixar a doença sem tratamento,
@@ -7289,308 +7265,308 @@
         </is>
       </c>
     </row>
-    <row r="294" ht="22.35" customHeight="1" s="17">
-      <c r="H294" s="15" t="n">
+    <row r="293" ht="22.35" customHeight="1" s="17">
+      <c r="H293" s="15" t="n">
         <v>77</v>
       </c>
-      <c r="I294" s="19" t="inlineStr">
+      <c r="I293" s="19" t="inlineStr">
         <is>
           <t>えへへ、そんなに心配しなくても大丈夫よ。
 時間はたっぷりあるんだから、何か解決策を見つけましょ？</t>
         </is>
       </c>
-      <c r="J294" s="19" t="inlineStr">
+      <c r="J293" s="19" t="inlineStr">
         <is>
           <t>Hehe, don't make that serious face.
 We have plenty of time, so let's find a solution, okay?</t>
         </is>
       </c>
-      <c r="K294" s="15" t="inlineStr">
+      <c r="K293" s="15" t="inlineStr">
         <is>
           <t>Heh heh, não se preocupe tanto.
 Temos muito tempo para encontrar uma solução.</t>
         </is>
       </c>
     </row>
-    <row r="295" ht="32.8" customHeight="1" s="17">
-      <c r="H295" s="15" t="n">
+    <row r="294" ht="32.8" customHeight="1" s="17">
+      <c r="H294" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="I295" s="19" t="inlineStr">
+      <c r="I294" s="19" t="inlineStr">
         <is>
           <t>そういえば、ノイエル南にある雪原の工房で
 奇妙なアイテムを収集している丘の民がいたわね。
 彼ならもしかしたら…</t>
         </is>
       </c>
-      <c r="J295" s="19" t="inlineStr">
+      <c r="J294" s="19" t="inlineStr">
         <is>
           <t>Come to think of it...
 There was a hillfolk in a workshop south of Noyel
 who was collecting strange items. Maybe he could...</t>
         </is>
       </c>
-      <c r="K295" s="15" t="inlineStr">
+      <c r="K294" s="15" t="inlineStr">
         <is>
           <t>Pensando bem...
 Havia um habitante da colina em uma oficina ao sul de Noyel
 que estava coletando itens estranhos. Talvez ele pudesse…</t>
         </is>
       </c>
+    </row>
+    <row r="295" ht="12.8" customHeight="1" s="17">
+      <c r="I295" s="19" t="n"/>
+      <c r="J295" s="19" t="n"/>
+      <c r="K295" s="15" t="n"/>
     </row>
     <row r="296" ht="12.8" customHeight="1" s="17">
       <c r="I296" s="19" t="n"/>
       <c r="J296" s="19" t="n"/>
       <c r="K296" s="15" t="n"/>
     </row>
-    <row r="297" ht="12.8" customHeight="1" s="17">
-      <c r="I297" s="19" t="n"/>
-      <c r="J297" s="19" t="n"/>
-      <c r="K297" s="15" t="n"/>
-    </row>
-    <row r="298" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B298" s="19" t="inlineStr">
+    <row r="297" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B297" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="300" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A300" s="19" t="inlineStr">
+    <row r="298" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="299" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A299" s="19" t="inlineStr">
         <is>
           <t>faith</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H301" s="15" t="n">
+    <row r="300" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H300" s="15" t="n">
         <v>66</v>
       </c>
-      <c r="I301" s="19" t="inlineStr">
+      <c r="I300" s="19" t="inlineStr">
         <is>
           <t>え、神を信仰した…？
 うふふ…</t>
         </is>
       </c>
-      <c r="J301" s="25" t="inlineStr">
+      <c r="J300" s="25" t="inlineStr">
         <is>
           <t>Oh, did you start worshipping a god?
 Hehe...</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
+      <c r="K300" t="inlineStr">
         <is>
           <t>O quê, você acreditava em Deus...?
 Uh-huh…</t>
         </is>
       </c>
     </row>
-    <row r="302" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H302" s="15" t="n">
+    <row r="301" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H301" s="15" t="n">
         <v>67</v>
       </c>
-      <c r="I302" s="19" t="inlineStr">
+      <c r="I301" s="19" t="inlineStr">
         <is>
           <t>ねえ、教えてよ！誰を信仰したの？
 キミの初信仰の相手は誰？ふふふ。</t>
         </is>
       </c>
-      <c r="J302" s="19" t="inlineStr">
+      <c r="J301" s="19" t="inlineStr">
         <is>
           <t>Come on, tell me! Who did you choose to worship?
 Who's your first god? Hehe.</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="K301" t="inlineStr">
         <is>
           <t>Vamos lá, conte-me! Quem você escolheu para adorar?
 Quem é seu primeiro Deus? Hehe.</t>
         </is>
       </c>
     </row>
-    <row r="303" ht="12.8" customFormat="1" customHeight="1" s="15">
+    <row r="302" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H302" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="I302" s="19" t="inlineStr">
+        <is>
+          <t>…#god。</t>
+        </is>
+      </c>
+      <c r="J302" s="19" t="inlineStr">
+        <is>
+          <t>...#god.</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...#god.  </t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H303" s="15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I303" s="19" t="inlineStr">
-        <is>
-          <t>…#god。</t>
-        </is>
-      </c>
-      <c r="J303" s="19" t="inlineStr">
-        <is>
-          <t>...#god.</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...#god.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H304" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="I304" s="19" t="inlineStr">
         <is>
           <t>キミって、やっぱりそういう趣味をしてたのね。
 ふ～ん…</t>
         </is>
       </c>
-      <c r="J304" s="19" t="inlineStr">
+      <c r="J303" s="19" t="inlineStr">
         <is>
           <t>I see, so that's your thing, huh?
 Huh...</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
+      <c r="K303" t="inlineStr">
         <is>
           <t xml:space="preserve">Entendo, então é isso que te interessa, hein?  
 Huh...  </t>
         </is>
       </c>
     </row>
-    <row r="305" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H305" s="15" t="n">
+    <row r="304" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H304" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="I305" s="19" t="inlineStr">
+      <c r="I304" s="19" t="inlineStr">
         <is>
           <t>神を信仰すると、信仰の深さによって様々な恩恵が与えられるわ。
 信仰は、捧げものをしたり、時間が経つことで深まっていくの。</t>
         </is>
       </c>
-      <c r="J305" s="19" t="inlineStr">
+      <c r="J304" s="19" t="inlineStr">
         <is>
           <t>When you worship a god, you'll receive various blessings
 depending on the depth of your faith.
 Your faith deepens through offerings and the passage of time.</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="K304" t="inlineStr">
         <is>
           <t>Ao adorar um Deus, você receberá várias bênçãos, dependendo da profundidade de sua fé.
 Sua fé se aprofunda com as oferendas e a passagem do tempo.</t>
         </is>
       </c>
     </row>
-    <row r="306" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H306" s="15" t="n">
+    <row r="305" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H305" s="15" t="n">
         <v>71</v>
       </c>
-      <c r="I306" s="19" t="inlineStr">
+      <c r="I305" s="19" t="inlineStr">
         <is>
           <t>また、一日に一度だけ、神に「祈る」アビリティを使うこともできる。
 体力が回復したり、神様の機嫌にもよるけど、贈り物を賜ることもあるわ。</t>
         </is>
       </c>
-      <c r="J306" s="19" t="inlineStr">
+      <c r="J305" s="19" t="inlineStr">
         <is>
           <t>Once a day, you can use the "Pray" ability to your god.
 It can restore your health, and depending on the god's mood,
 you might receive a gift.</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
+      <c r="K305" t="inlineStr">
         <is>
           <t xml:space="preserve">Uma vez por dia, você pode usar a habilidade "Orar" para seu Deus.  
 Ela pode restaurar sua saúde e, dependendo do humor do Deus, você pode receber um presente.  </t>
         </is>
       </c>
     </row>
+    <row r="306" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H306" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="I306" s="19" t="inlineStr">
+        <is>
+          <t>「祈る」ことで、キミの信仰スキルも鍛えられるから
+一日に一度は祈ってみるといいわね。</t>
+        </is>
+      </c>
+      <c r="J306" s="19" t="inlineStr">
+        <is>
+          <t>Praying also helps you develop your faith skill,
+so try to pray at least once a day.</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>A oração também o ajuda a desenvolver sua habilidade de fé,
+portanto, tente orar pelo menos uma vez por dia.</t>
+        </is>
+      </c>
+    </row>
     <row r="307" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H307" s="15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I307" s="19" t="inlineStr">
         <is>
-          <t>「祈る」ことで、キミの信仰スキルも鍛えられるから
-一日に一度は祈ってみるといいわね。</t>
+          <t>じゃあ、#godを怒らせないように気を付けてね。</t>
         </is>
       </c>
       <c r="J307" s="19" t="inlineStr">
-        <is>
-          <t>Praying also helps you develop your faith skill,
-so try to pray at least once a day.</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>A oração também o ajuda a desenvolver sua habilidade de fé,
-portanto, tente orar pelo menos uma vez por dia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="308" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H308" s="15" t="n">
-        <v>73</v>
-      </c>
-      <c r="I308" s="19" t="inlineStr">
-        <is>
-          <t>じゃあ、#godを怒らせないように気を付けてね。</t>
-        </is>
-      </c>
-      <c r="J308" s="19" t="inlineStr">
         <is>
           <t>Well, that's it for now.
 Just be careful not to anger #god.</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
+      <c r="K307" t="inlineStr">
         <is>
           <t>Bem, por enquanto é isso.
 Apenas tome cuidado para não irritar #god.</t>
         </is>
       </c>
     </row>
+    <row r="308" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B308" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
     <row r="309" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B309" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
+      <c r="A309" s="19" t="inlineStr">
+        <is>
+          <t>healer</t>
         </is>
       </c>
     </row>
     <row r="310" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A310" s="19" t="inlineStr">
-        <is>
-          <t>healer</t>
-        </is>
-      </c>
-    </row>
-    <row r="311" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H310" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="I310" s="19" t="inlineStr">
+        <is>
+          <t>あ…キミ、弱くなっちゃったの？</t>
+        </is>
+      </c>
+      <c r="J310" s="25" t="inlineStr">
+        <is>
+          <t>Oh... Have you become weaker?</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Oh... Você ficou mais fraco?</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="43.25" customFormat="1" customHeight="1" s="15">
       <c r="H311" s="15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I311" s="19" t="inlineStr">
-        <is>
-          <t>あ…キミ、弱くなっちゃったの？</t>
-        </is>
-      </c>
-      <c r="J311" s="25" t="inlineStr">
-        <is>
-          <t>Oh... Have you become weaker?</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Oh... Você ficou mais fraco?</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H312" s="15" t="n">
-        <v>61</v>
-      </c>
-      <c r="I312" s="19" t="inlineStr">
         <is>
           <t>え？どういうことって…
 ちょっと自分の主能力を確認してみてね？
 普段より能力が低下してるでしょ？</t>
         </is>
       </c>
-      <c r="J312" s="19" t="inlineStr">
+      <c r="J311" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">
 What? What do I mean by that... 
@@ -7598,7 +7574,7 @@
 You'll notice they're lower than usual, right?</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
+      <c r="K311" t="inlineStr">
         <is>
           <t xml:space="preserve">  
 O quê? O que quero dizer com isso...  
@@ -7607,92 +7583,92 @@
         </is>
       </c>
     </row>
+    <row r="312" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H312" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="I312" s="19" t="inlineStr">
+        <is>
+          <t>一部の敵は、キミの能力を弱体化させる攻撃をしてくるの。
+弱体は、最初は問題ないけど、積み重なってくると厄介よ。</t>
+        </is>
+      </c>
+      <c r="J312" s="19" t="inlineStr">
+        <is>
+          <t>Some enemies can weaken your attributes with their attacks.
+At first, it's not a big deal, but if it piles up, it can become troublesome.</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Alguns inimigos podem enfraquecer seus atributos com os ataques deles.
+No início, isso não é um grande problema, mas se acumular, pode se tornar incômodo.</t>
+        </is>
+      </c>
+    </row>
     <row r="313" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H313" s="15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I313" s="19" t="inlineStr">
         <is>
-          <t>一部の敵は、キミの能力を弱体化させる攻撃をしてくるの。
-弱体は、最初は問題ないけど、積み重なってくると厄介よ。</t>
+          <t>もし肉体復活か精神復活のポーションを持ってるなら
+それを飲めば弱体を回復することができるわ。</t>
         </is>
       </c>
       <c r="J313" s="19" t="inlineStr">
         <is>
-          <t>Some enemies can weaken your attributes with their attacks.
-At first, it's not a big deal, but if it piles up, it can become troublesome.</t>
+          <t>If you have a Potion of Restore Body or a Potion of Restore Mind,
+drinking one of those can restore your weakened attributes.</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Alguns inimigos podem enfraquecer seus atributos com os ataques deles.
-No início, isso não é um grande problema, mas se acumular, pode se tornar incômodo.</t>
+          <t>Se você tiver uma Potion of Restore Body (Poção de Restauração do Corpo) ou uma Potion of Restore Mind (Poção de Restauração da Mente), beber uma delas pode restaurar seus atributos enfraquecidos.</t>
         </is>
       </c>
     </row>
     <row r="314" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H314" s="15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I314" s="19" t="inlineStr">
-        <is>
-          <t>もし肉体復活か精神復活のポーションを持ってるなら
-それを飲めば弱体を回復することができるわ。</t>
-        </is>
-      </c>
-      <c r="J314" s="19" t="inlineStr">
-        <is>
-          <t>If you have a Potion of Restore Body or a Potion of Restore Mind,
-drinking one of those can restore your weakened attributes.</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Se você tiver uma Potion of Restore Body (Poção de Restauração do Corpo) ou uma Potion of Restore Mind (Poção de Restauração da Mente), beber uma delas pode restaurar seus atributos enfraquecidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H315" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="I315" s="19" t="inlineStr">
         <is>
           <t>回復の手段がない時は、街にいる癒し手に頼めば
 治療費と引き換えに治してもらえるけど…</t>
         </is>
       </c>
-      <c r="J315" s="19" t="inlineStr">
+      <c r="J314" s="19" t="inlineStr">
         <is>
           <t>If you don't have a way to recover, you can ask a healer in town.
 It will cost you some money, but they can treat you...</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
+      <c r="K314" t="inlineStr">
         <is>
           <t>Se você não tiver uma maneira de se recuperar, pode pedir a um curandeiro da cidade.
 Isso lhe custará algum dinheiro, mas ele poderá tratá-lo…</t>
         </is>
       </c>
     </row>
-    <row r="316" ht="32.8" customHeight="1" s="17">
-      <c r="H316" s="15" t="n">
+    <row r="315" ht="32.8" customHeight="1" s="17">
+      <c r="H315" s="15" t="n">
         <v>65</v>
       </c>
-      <c r="I316" s="19" t="inlineStr">
+      <c r="I315" s="19" t="inlineStr">
         <is>
           <t>まあ、攻撃を受けないのが一番ね。
 近づくと厄介な敵には、遠隔から攻撃するといいわ。</t>
         </is>
       </c>
-      <c r="J316" s="19" t="inlineStr">
+      <c r="J315" s="19" t="inlineStr">
         <is>
           <t>Well, it's best not to get hit in the first place.
 For enemies that are troublesome up close,
 it's always better to attack them from a distance.</t>
         </is>
       </c>
-      <c r="K316" s="15" t="inlineStr">
+      <c r="K315" s="15" t="inlineStr">
         <is>
           <t>Bem, é melhor não ser atingido em primeiro lugar.
 Para inimigos que são problemáticos de perto,
@@ -7700,154 +7676,154 @@
         </is>
       </c>
     </row>
-    <row r="317" ht="12.8" customHeight="1" s="17">
-      <c r="B317" s="19" t="inlineStr">
+    <row r="316" ht="12.8" customHeight="1" s="17">
+      <c r="B316" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K317" s="15" t="n"/>
-    </row>
+      <c r="K316" s="15" t="n"/>
+    </row>
+    <row r="317" ht="12.8" customFormat="1" customHeight="1" s="15"/>
     <row r="318" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="319" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="320" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A320" s="19" t="inlineStr">
+    <row r="319" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A319" s="19" t="inlineStr">
         <is>
           <t>fame</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H320" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="I320" s="19" t="inlineStr">
+        <is>
+          <t>わあ、名声を獲得したのね！
+おめでと～！</t>
+        </is>
+      </c>
+      <c r="J320" s="25" t="inlineStr">
+        <is>
+          <t>Wow, you’ve gained fame!
+Congratulations!</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uau, você ganhou fama!  _x000D_
+Parabéns!  </t>
         </is>
       </c>
     </row>
     <row r="321" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="H321" s="15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I321" s="19" t="inlineStr">
         <is>
-          <t>わあ、名声を獲得したのね！
-おめでと～！</t>
+          <t>名声は、依頼を達成したり
+ネフィアを踏破することで獲得できるわ。</t>
         </is>
       </c>
       <c r="J321" s="25" t="inlineStr">
         <is>
-          <t>Wow, you’ve gained fame!
-Congratulations!</t>
+          <t>You can earn fame by completing quests
+and exploring Nefia.</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uau, você ganhou fama!  _x000D_
-Parabéns!  </t>
+          <t xml:space="preserve">Você pode ganhar fama completando missões  _x000D_
+e explorando Nefia.  </t>
         </is>
       </c>
     </row>
     <row r="322" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="H322" s="15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I322" s="19" t="inlineStr">
         <is>
-          <t>名声は、依頼を達成したり
-ネフィアを踏破することで獲得できるわ。</t>
+          <t>名声が上がると、より難易度の高い依頼を頼まれたり
+危険度の高いネフィアが出現するようになるの。</t>
         </is>
       </c>
       <c r="J322" s="25" t="inlineStr">
         <is>
-          <t>You can earn fame by completing quests
-and exploring Nefia.</t>
+          <t>As your fame increases, you’ll be asked to take on more challenging quests,
+and more dangerous Nefia will appear.</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você pode ganhar fama completando missões  _x000D_
-e explorando Nefia.  </t>
+          <t>À medida que sua fama aumenta, você será solicitado a participar de missões mais desafiadoras,
+e a Nefia, mais perigosa, aparecerá.</t>
         </is>
       </c>
     </row>
     <row r="323" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="H323" s="15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I323" s="19" t="inlineStr">
-        <is>
-          <t>名声が上がると、より難易度の高い依頼を頼まれたり
-危険度の高いネフィアが出現するようになるの。</t>
-        </is>
-      </c>
-      <c r="J323" s="25" t="inlineStr">
-        <is>
-          <t>As your fame increases, you’ll be asked to take on more challenging quests,
-and more dangerous Nefia will appear.</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>À medida que sua fama aumenta, você será solicitado a participar de missões mais desafiadoras,
-e a Nefia, mais perigosa, aparecerá.</t>
-        </is>
-      </c>
-    </row>
-    <row r="324" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H324" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="I324" s="19" t="inlineStr">
         <is>
           <t>いっぱい名声を稼いで
 早く立派な冒険者になってね！</t>
         </is>
       </c>
-      <c r="J324" s="25" t="inlineStr">
+      <c r="J323" s="25" t="inlineStr">
         <is>
           <t>Earn lots of fame and
 become a renowned adventurer soon!</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
+      <c r="K323" t="inlineStr">
         <is>
           <t>Ganhe muita fama e 
 torne-se rapidamente um grande aventureiro!</t>
         </is>
       </c>
     </row>
-    <row r="325" ht="12.8" customFormat="1" customHeight="1" s="15">
+    <row r="324" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H324" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="I324" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J324" s="19" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...  </t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="H325" s="15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I325" s="19" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J325" s="19" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="35.05" customFormat="1" customHeight="1" s="15">
-      <c r="H326" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="I326" s="19" t="inlineStr">
         <is>
           <t>ちなみに…
 もし名声が高すぎて冒険がきつくなったら
 街の情報屋に名声を売るという手段もあるわ…</t>
         </is>
       </c>
-      <c r="J326" s="25" t="inlineStr">
+      <c r="J325" s="25" t="inlineStr">
         <is>
           <t>By the way...
 if your fame gets too high and the adventures become too tough,
 you can sell your fame to the town’s informant...</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
+      <c r="K325" t="inlineStr">
         <is>
           <t xml:space="preserve">A propósito...  _x000D_
 se sua fama ficar muito alta e as aventuras se tornarem difíceis demais,  _x000D_
@@ -7855,129 +7831,129 @@
         </is>
       </c>
     </row>
+    <row r="326" ht="12.8" customHeight="1" s="17">
+      <c r="H326" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I326" s="19" t="inlineStr">
+        <is>
+          <t>それでは…</t>
+        </is>
+      </c>
+      <c r="J326" s="25" t="inlineStr">
+        <is>
+          <t>Well then...</t>
+        </is>
+      </c>
+      <c r="K326" s="15" t="inlineStr">
+        <is>
+          <t>Então, bem…</t>
+        </is>
+      </c>
+    </row>
     <row r="327" ht="12.8" customHeight="1" s="17">
-      <c r="H327" s="15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I327" s="19" t="inlineStr">
-        <is>
-          <t>それでは…</t>
-        </is>
-      </c>
-      <c r="J327" s="25" t="inlineStr">
-        <is>
-          <t>Well then...</t>
-        </is>
-      </c>
-      <c r="K327" s="15" t="inlineStr">
-        <is>
-          <t>Então, bem…</t>
-        </is>
-      </c>
-    </row>
-    <row r="328" ht="12.8" customHeight="1" s="17">
-      <c r="B328" s="19" t="inlineStr">
+      <c r="B327" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K328" s="15" t="n"/>
-    </row>
+      <c r="K327" s="15" t="n"/>
+    </row>
+    <row r="329" ht="12.8" customFormat="1" customHeight="1" s="15"/>
     <row r="330" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="331" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="331" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A331" s="19" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+    </row>
     <row r="332" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A332" s="19" t="inlineStr">
-        <is>
-          <t>sleep</t>
-        </is>
-      </c>
-    </row>
-    <row r="333" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H332" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="I332" s="19" t="inlineStr">
+        <is>
+          <t>疲れた顔してるけど大丈夫…？</t>
+        </is>
+      </c>
+      <c r="J332" s="25" t="inlineStr">
+        <is>
+          <t>You look tired, are you okay?</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Você parece cansado. Está bem?</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H333" s="15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I333" s="19" t="inlineStr">
-        <is>
-          <t>疲れた顔してるけど大丈夫…？</t>
-        </is>
-      </c>
-      <c r="J333" s="25" t="inlineStr">
-        <is>
-          <t>You look tired, are you okay?</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>Você parece cansado. Está bem?</t>
-        </is>
-      </c>
-    </row>
-    <row r="334" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H334" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="I334" s="19" t="inlineStr">
         <is>
           <t>疲れをとるには、ふかふかのベッドで
 ぐっすり眠るのが一番。</t>
         </is>
       </c>
-      <c r="J334" s="19" t="inlineStr">
+      <c r="J333" s="19" t="inlineStr">
         <is>
           <t>The best way to recover from fatigue is
 to get a good night's sleep in a comfy bed.</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
+      <c r="K333" t="inlineStr">
         <is>
           <t>A melhor maneira de se recuperar da fadiga é
 ter uma boa noite de sono em uma cama confortável.</t>
         </is>
       </c>
     </row>
-    <row r="335" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H335" s="15" t="n">
+    <row r="334" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H334" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I335" s="19" t="inlineStr">
+      <c r="I334" s="19" t="inlineStr">
         <is>
           <t>しっかり睡眠をとれば
 レシピを閃いたり、潜在能力が鍛えられたり
 夢で魔法を覚えられたり、いいことがあるかも。</t>
         </is>
       </c>
-      <c r="J335" s="19" t="inlineStr">
+      <c r="J334" s="19" t="inlineStr">
         <is>
           <t>When you get enough sleep,
 you might get new recipe ideas, train your potentials,
 or even learn magic in your dreams.</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
+      <c r="K334" t="inlineStr">
         <is>
           <t>Quando você dorme o suficiente, pode ter novas ideias de receitas, treinar seus talentos ou até mesmo aprender magia em seus sonhos.</t>
         </is>
       </c>
     </row>
-    <row r="336" ht="35.05" customFormat="1" customHeight="1" s="15">
-      <c r="H336" s="15" t="n">
+    <row r="335" ht="35.05" customFormat="1" customHeight="1" s="15">
+      <c r="H335" s="15" t="n">
         <v>47</v>
       </c>
-      <c r="I336" s="19" t="inlineStr">
+      <c r="I335" s="19" t="inlineStr">
         <is>
           <t>まだベッドを作っていないなら
 「休憩」のアビリティを使うことで眠ることもできるわ。
 ベッドで眠るより効果はおちるけどね。</t>
         </is>
       </c>
-      <c r="J336" s="25" t="inlineStr">
+      <c r="J335" s="25" t="inlineStr">
         <is>
           <t>If you haven't made a bed yet,
 you can use the "Rest" ability to sleep.
 It's not as effective as sleeping in a bed, though.</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
+      <c r="K335" t="inlineStr">
         <is>
           <t xml:space="preserve">Se você ainda não fez uma cama,  
 pode usar a habilidade "Descansar" para dormir.  
@@ -7985,11 +7961,11 @@
         </is>
       </c>
     </row>
-    <row r="337" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H337" s="15" t="n">
+    <row r="336" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H336" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="I337" s="19" t="inlineStr">
+      <c r="I336" s="19" t="inlineStr">
         <is>
           <t>休憩中は体力や魔力の自然回復量も上がるから
 戦いの後は休憩するのもありね。
@@ -7997,7 +7973,7 @@
 自然回復自体止まってしまうから気を付けて。</t>
         </is>
       </c>
-      <c r="J337" s="19" t="inlineStr">
+      <c r="J336" s="19" t="inlineStr">
         <is>
           <t>When resting, your natural recovery of health and magic power increases,
 so it's good to rest after a battle.
@@ -8005,127 +7981,127 @@
 natural recovery stops altogether.</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
+      <c r="K336" t="inlineStr">
         <is>
           <t>Ao descansar, sua recuperação natural de saúde e poder mágico aumenta, portanto, é bom descansar depois de uma batalha.
 Mas tome cuidado, pois se você estiver sobrecarregado ou faminto, a recuperação natural será interrompida completamente.</t>
         </is>
       </c>
     </row>
-    <row r="338" ht="22.35" customHeight="1" s="17">
-      <c r="H338" s="15" t="n">
+    <row r="337" ht="22.35" customHeight="1" s="17">
+      <c r="H337" s="15" t="n">
         <v>49</v>
       </c>
-      <c r="I338" s="19" t="inlineStr">
+      <c r="I337" s="19" t="inlineStr">
         <is>
           <t>じゃあ、しっかり睡眠をとるのよ！</t>
         </is>
       </c>
-      <c r="J338" s="19" t="inlineStr">
+      <c r="J337" s="19" t="inlineStr">
         <is>
           <t>Okay that's it for now.
 Make sure to get plenty of sleep!</t>
         </is>
       </c>
-      <c r="K338" s="15" t="inlineStr">
+      <c r="K337" s="15" t="inlineStr">
         <is>
           <t>Por enquanto é isso.
 Não deixe de dormir bastante!</t>
         </is>
       </c>
     </row>
-    <row r="339" ht="12.8" customHeight="1" s="17">
-      <c r="B339" s="19" t="inlineStr">
+    <row r="338" ht="12.8" customHeight="1" s="17">
+      <c r="B338" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K339" s="15" t="n"/>
-    </row>
+      <c r="K338" s="15" t="n"/>
+    </row>
+    <row r="339" ht="12.8" customFormat="1" customHeight="1" s="15"/>
     <row r="340" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="341" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="342" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A342" s="19" t="inlineStr">
+    <row r="341" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A341" s="19" t="inlineStr">
         <is>
           <t>region</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H342" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I342" s="19" t="inlineStr">
+        <is>
+          <t>おーい、ちょっとまって。
+…走るなコラ！</t>
+        </is>
+      </c>
+      <c r="J342" s="19" t="inlineStr">
+        <is>
+          <t>Hey, wait a minute.
+...don't... don't run!</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ei, espere um minuto.  
+E não, não corra!  </t>
         </is>
       </c>
     </row>
     <row r="343" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="H343" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I343" s="19" t="inlineStr">
         <is>
-          <t>おーい、ちょっとまって。
-…走るなコラ！</t>
+          <t>はぁはぁ…コホン</t>
         </is>
       </c>
       <c r="J343" s="19" t="inlineStr">
-        <is>
-          <t>Hey, wait a minute.
-...don't... don't run!</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ei, espere um minuto.  
-E não, não corra!  </t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H344" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I344" s="19" t="inlineStr">
-        <is>
-          <t>はぁはぁ…コホン</t>
-        </is>
-      </c>
-      <c r="J344" s="19" t="inlineStr">
         <is>
           <t>*huff* *puff*
 ...*cough*</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
+      <c r="K343" t="inlineStr">
         <is>
           <t xml:space="preserve">*huff* *puff*  
 ...*cof*  </t>
         </is>
       </c>
     </row>
-    <row r="345" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H345" s="15" t="n">
+    <row r="344" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H344" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I345" s="19" t="inlineStr">
+      <c r="I344" s="19" t="inlineStr">
         <is>
           <t>キミが今いるのは「グローバルマップ」よ。
 ワールドマップでは大距離を移動できるかわりに
 時間がとても早く経過するの。</t>
         </is>
       </c>
-      <c r="J345" s="19" t="inlineStr">
+      <c r="J344" s="19" t="inlineStr">
         <is>
           <t>You are now in the "Global Map".
 In the global map, you can travel great distances
 but time also passes very quickly.</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
+      <c r="K344" t="inlineStr">
         <is>
           <t>Agora você está no “Mapa Global”.
 No Mapa Global, você pode viajar grandes distâncias, mas o tempo também passa muito rápido.</t>
         </is>
       </c>
     </row>
-    <row r="346" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H346" s="15" t="n">
+    <row r="345" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H345" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I346" s="19" t="inlineStr">
+      <c r="I345" s="19" t="inlineStr">
         <is>
           <t>食料を十分に持っていないと
 すぐ餓死するから気をつけてね。
@@ -8133,25 +8109,25 @@
 毒にかかってる時に移動なんかしないこと！</t>
         </is>
       </c>
-      <c r="J346" s="19" t="inlineStr">
+      <c r="J345" s="19" t="inlineStr">
         <is>
           <t>You will starve to death if you don't have enough food
 and conditions such as poison progress rapidly.
 So be careful when you move.</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr">
+      <c r="K345" t="inlineStr">
         <is>
           <t>Você morrerá de fome se não tiver comida suficiente, e doenças como o veneno progridem rapidamente.
 Portanto, tenha cuidado ao se deslocar.</t>
         </is>
       </c>
     </row>
-    <row r="347" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H347" s="15" t="n">
+    <row r="346" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H346" s="15" t="n">
         <v>212</v>
       </c>
-      <c r="I347" s="19" t="inlineStr">
+      <c r="I346" s="19" t="inlineStr">
         <is>
           <t>食べるものがなくてどうしようもない時は
 自分のいる場所をクリックしてみて。
@@ -8159,7 +8135,7 @@
 森や平野なら、野生の食材も豊富にあるはず。</t>
         </is>
       </c>
-      <c r="J347" s="19" t="inlineStr">
+      <c r="J346" s="19" t="inlineStr">
         <is>
           <t>When you have nothing to eat, try clicking on yourself.
 You’ll be able to enter an “Outdoor Map” corresponding
@@ -8167,7 +8143,7 @@
 If you’re in a forest or plains, there should be plenty of wild food available.</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
+      <c r="K346" t="inlineStr">
         <is>
           <t>Se você estiver sem comida e sem opções, tente abrir o "Mapa Global".
 Você vai ver um mapa relativo ao seu local atual.
@@ -8176,33 +8152,33 @@
         </is>
       </c>
     </row>
-    <row r="348" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H348" s="15" t="n">
+    <row r="347" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H347" s="15" t="n">
         <v>52</v>
       </c>
-      <c r="I348" s="19" t="inlineStr">
+      <c r="I347" s="19" t="inlineStr">
         <is>
           <t>そうそう、グローバルマップを移動していると
 モンスターに襲撃されることがあるわ。</t>
         </is>
       </c>
-      <c r="J348" s="19" t="inlineStr">
+      <c r="J347" s="19" t="inlineStr">
         <is>
           <t>Oh, and when you're traveling on the global map
 you might get attacked by monsters.</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr">
+      <c r="K347" t="inlineStr">
         <is>
           <t>Ah, e quando você estiver viajando no mapa global, poderá ser atacado por monstros.</t>
         </is>
       </c>
     </row>
-    <row r="349" ht="74.59999999999999" customFormat="1" customHeight="1" s="15">
-      <c r="H349" s="15" t="n">
+    <row r="348" ht="74.59999999999999" customFormat="1" customHeight="1" s="15">
+      <c r="H348" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="I349" s="19" t="inlineStr">
+      <c r="I348" s="19" t="inlineStr">
         <is>
           <t>右手に街道が見えるでしょ？
 街道の上は襲撃が少なくて比較的安全。
@@ -8210,7 +8186,7 @@
 駆け出しのうちは、街道を利用するといいわ。</t>
         </is>
       </c>
-      <c r="J349" s="19" t="inlineStr">
+      <c r="J348" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">See that road to your right?
 Attacks are less frequent on the road
@@ -8219,7 +8195,7 @@
 So, for beginners, sticking to the road is a good idea. </t>
         </is>
       </c>
-      <c r="K349" t="inlineStr">
+      <c r="K348" t="inlineStr">
         <is>
           <t>Está vendo a estrada da cidade à sua direita?
 A estrada é relativamente segura, com menos ataques.
@@ -8227,81 +8203,81 @@
         </is>
       </c>
     </row>
+    <row r="349" ht="12.8" customHeight="1" s="17">
+      <c r="H349" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I349" s="19" t="inlineStr">
+        <is>
+          <t>それでは…</t>
+        </is>
+      </c>
+      <c r="J349" s="25" t="inlineStr">
+        <is>
+          <t>Well then...</t>
+        </is>
+      </c>
+      <c r="K349" s="15" t="inlineStr">
+        <is>
+          <t>Então, bem…</t>
+        </is>
+      </c>
+    </row>
     <row r="350" ht="12.8" customHeight="1" s="17">
-      <c r="H350" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="I350" s="19" t="inlineStr">
-        <is>
-          <t>それでは…</t>
-        </is>
-      </c>
-      <c r="J350" s="25" t="inlineStr">
-        <is>
-          <t>Well then...</t>
-        </is>
-      </c>
-      <c r="K350" s="15" t="inlineStr">
-        <is>
-          <t>Então, bem…</t>
-        </is>
-      </c>
-    </row>
-    <row r="351" ht="12.8" customHeight="1" s="17">
-      <c r="B351" s="19" t="inlineStr">
+      <c r="B350" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K351" s="15" t="n"/>
+      <c r="K350" s="15" t="n"/>
+    </row>
+    <row r="352" ht="12.8" customHeight="1" s="17">
+      <c r="A352" s="15" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="12.8" customHeight="1" s="17">
-      <c r="A353" s="15" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="12.8" customHeight="1" s="17">
-      <c r="D354" s="15" t="inlineStr">
+      <c r="D353" s="15" t="inlineStr">
         <is>
           <t>hideUI</t>
         </is>
       </c>
-      <c r="E354" s="15" t="inlineStr">
+      <c r="E353" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="355" ht="22.35" customHeight="1" s="17">
-      <c r="H355" s="15" t="n">
+    <row r="354" ht="22.35" customHeight="1" s="17">
+      <c r="H354" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I355" s="19" t="inlineStr">
+      <c r="I354" s="19" t="inlineStr">
         <is>
           <t>そうそう
 Demoはこれでおしまいよ。</t>
         </is>
       </c>
-      <c r="J355" s="19" t="inlineStr">
+      <c r="J354" s="19" t="inlineStr">
         <is>
           <t>Oh yes.
 This is the end of the Demo.</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
+      <c r="K354" t="inlineStr">
         <is>
           <t xml:space="preserve">Oh, sim.  _x000D_
 Este é o fim da Demo.  </t>
         </is>
       </c>
     </row>
-    <row r="356" ht="43.25" customHeight="1" s="17">
-      <c r="H356" s="15" t="n">
+    <row r="355" ht="43.25" customHeight="1" s="17">
+      <c r="H355" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I356" s="19" t="inlineStr">
+      <c r="I355" s="19" t="inlineStr">
         <is>
           <t>この先の街や色々な場所を訪れることもできるけど
 まだ未実装の部分も多いし
@@ -8309,7 +8285,7 @@
 あまりオススメはしないわ。</t>
         </is>
       </c>
-      <c r="J356" s="19" t="inlineStr">
+      <c r="J355" s="19" t="inlineStr">
         <is>
           <t>You can still visit cities and places down the road
 but I don't recommend it as there are
@@ -8317,63 +8293,93 @@
 and it will spoil the fun and surprises later on.</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
+      <c r="K355" t="inlineStr">
         <is>
           <t xml:space="preserve">Você ainda pode visitar cidades e lugares adiante,  
 mas não recomendo, pois há  muitos aspectos não implementados e isso estragaria a diversão e as surpresas futuras.  </t>
         </is>
       </c>
     </row>
-    <row r="357" ht="22.35" customHeight="1" s="17">
-      <c r="B357" s="15" t="inlineStr">
+    <row r="356" ht="22.35" customHeight="1" s="17">
+      <c r="B356" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="H357" s="15" t="n">
+      <c r="H356" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I357" s="19" t="inlineStr">
+      <c r="I356" s="19" t="inlineStr">
         <is>
           <t>少し観光したら
 そっとゲームを閉じていってね。</t>
         </is>
       </c>
-      <c r="J357" s="19" t="inlineStr">
+      <c r="J356" s="19" t="inlineStr">
         <is>
           <t>After a little sightseeing
 please close the game gently.</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr">
+      <c r="K356" t="inlineStr">
         <is>
           <t xml:space="preserve">Depois de um pequeno passeio,  
 por favor, feche o jogo com cuidado.  </t>
         </is>
       </c>
     </row>
+    <row r="359" ht="12.8" customHeight="1" s="17">
+      <c r="A359" s="15" t="inlineStr">
+        <is>
+          <t>9-1</t>
+        </is>
+      </c>
+      <c r="H359" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="I359" s="15" t="inlineStr">
+        <is>
+          <t>なになに？</t>
+        </is>
+      </c>
+      <c r="J359" s="15" t="inlineStr">
+        <is>
+          <t>What?</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O quê?  </t>
+        </is>
+      </c>
+    </row>
     <row r="360" ht="12.8" customHeight="1" s="17">
-      <c r="A360" s="15" t="inlineStr">
-        <is>
-          <t>9-1</t>
+      <c r="B360" s="15" t="inlineStr">
+        <is>
+          <t>9-2</t>
+        </is>
+      </c>
+      <c r="D360" s="15" t="inlineStr">
+        <is>
+          <t>choice</t>
         </is>
       </c>
       <c r="H360" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I360" s="15" t="inlineStr">
         <is>
-          <t>なになに？</t>
+          <t>明日の天気は？</t>
         </is>
       </c>
       <c r="J360" s="15" t="inlineStr">
         <is>
-          <t>What?</t>
+          <t>What will the weather be tomorrow?</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">O quê?  </t>
+          <t>Como estará o tempo amanhã?</t>
         </is>
       </c>
     </row>
@@ -8389,28 +8395,28 @@
         </is>
       </c>
       <c r="H361" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I361" s="15" t="inlineStr">
         <is>
-          <t>明日の天気は？</t>
+          <t>今日の運勢は？</t>
         </is>
       </c>
       <c r="J361" s="15" t="inlineStr">
         <is>
-          <t>What will the weather be tomorrow?</t>
+          <t>How is my fortune today?</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Como estará o tempo amanhã?</t>
+          <t xml:space="preserve">Qual é a minha sorte hoje?  </t>
         </is>
       </c>
     </row>
     <row r="362" ht="12.8" customHeight="1" s="17">
       <c r="B362" s="15" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="D362" s="15" t="inlineStr">
@@ -8419,127 +8425,97 @@
         </is>
       </c>
       <c r="H362" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I362" s="15" t="inlineStr">
         <is>
-          <t>今日の運勢は？</t>
+          <t>なんでもない</t>
         </is>
       </c>
       <c r="J362" s="15" t="inlineStr">
         <is>
-          <t>How is my fortune today?</t>
+          <t>Nothing</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qual é a minha sorte hoje?  </t>
+          <t xml:space="preserve">Nada  </t>
         </is>
       </c>
     </row>
     <row r="363" ht="12.8" customHeight="1" s="17">
       <c r="B363" s="15" t="inlineStr">
         <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="D363" s="15" t="inlineStr">
+        <is>
+          <t>cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="12.8" customHeight="1" s="17">
+      <c r="A367" s="15" t="inlineStr">
+        <is>
+          <t>9-2</t>
+        </is>
+      </c>
+      <c r="H367" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I367" s="15" t="inlineStr">
+        <is>
+          <t>…さあ？</t>
+        </is>
+      </c>
+      <c r="J367" s="15" t="inlineStr">
+        <is>
+          <t>...who knows?</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>... E então?</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="12.8" customHeight="1" s="17">
+      <c r="B368" s="15" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="12.8" customHeight="1" s="17">
+      <c r="A371" s="15" t="inlineStr">
+        <is>
           <t>9-3</t>
         </is>
       </c>
-      <c r="D363" s="15" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="H363" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="I363" s="15" t="inlineStr">
-        <is>
-          <t>なんでもない</t>
-        </is>
-      </c>
-      <c r="J363" s="15" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nada  </t>
-        </is>
-      </c>
-    </row>
-    <row r="364" ht="12.8" customHeight="1" s="17">
-      <c r="B364" s="15" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="D364" s="15" t="inlineStr">
-        <is>
-          <t>cancel</t>
-        </is>
-      </c>
-    </row>
-    <row r="368" ht="12.8" customHeight="1" s="17">
-      <c r="A368" s="15" t="inlineStr">
-        <is>
-          <t>9-2</t>
-        </is>
-      </c>
-      <c r="H368" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="I368" s="15" t="inlineStr">
-        <is>
-          <t>…さあ？</t>
-        </is>
-      </c>
-      <c r="J368" s="15" t="inlineStr">
-        <is>
-          <t>...who knows?</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>... E então?</t>
-        </is>
-      </c>
-    </row>
-    <row r="369" ht="12.8" customHeight="1" s="17">
-      <c r="B369" s="15" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
     </row>
     <row r="372" ht="12.8" customHeight="1" s="17">
-      <c r="A372" s="15" t="inlineStr">
-        <is>
-          <t>9-3</t>
+      <c r="H372" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I372" s="15" t="inlineStr">
+        <is>
+          <t>用事もないのに呼ばないで。</t>
+        </is>
+      </c>
+      <c r="J372" s="15" t="inlineStr">
+        <is>
+          <t>Don't disturb me for nothing.</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Não me incomode por nada.  </t>
         </is>
       </c>
     </row>
     <row r="373" ht="12.8" customHeight="1" s="17">
-      <c r="H373" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="I373" s="15" t="inlineStr">
-        <is>
-          <t>用事もないのに呼ばないで。</t>
-        </is>
-      </c>
-      <c r="J373" s="15" t="inlineStr">
-        <is>
-          <t>Don't disturb me for nothing.</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não me incomode por nada.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="374" ht="12.8" customHeight="1" s="17">
-      <c r="B374" s="15" t="inlineStr">
+      <c r="B373" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
